--- a/template_estimate.xlsx
+++ b/template_estimate.xlsx
@@ -1,13 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="見積1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="内訳" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="見積1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="内訳" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="内訳2" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="内訳3" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="内訳4" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="内訳5" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="内訳6" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="タイトル">#REF!</definedName>
@@ -17,6 +22,11 @@
     <definedName name="品名">#REF!</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'見積1'!$B$1:$M$47</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'内訳'!$B$1:$M$46</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'内訳2'!$B$1:$M$46</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'内訳3'!$B$1:$M$46</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'内訳4'!$B$1:$M$46</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'内訳5'!$B$1:$M$46</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'内訳6'!$B$1:$M$46</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -2573,4 +2583,3739 @@
   <pageMargins left="0.7868055555555555" right="0.5902777777777778" top="0.9840277777777777" bottom="0.9840277777777777" header="0.5111111111111111" footer="0.5111111111111111"/>
   <pageSetup orientation="portrait" paperSize="9" scale="90"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:L46"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.2"/>
+  <cols>
+    <col width="13" customWidth="1" style="32" min="1" max="1"/>
+    <col width="0.88671875" customWidth="1" style="32" min="2" max="2"/>
+    <col width="11.109375" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
+    <col width="6.5546875" customWidth="1" style="32" min="4" max="4"/>
+    <col width="18.77734375" customWidth="1" style="32" min="5" max="5"/>
+    <col width="8.44140625" bestFit="1" customWidth="1" style="32" min="6" max="6"/>
+    <col width="8.77734375" customWidth="1" style="32" min="7" max="7"/>
+    <col width="6.21875" customWidth="1" style="32" min="8" max="8"/>
+    <col width="5.6640625" customWidth="1" style="32" min="9" max="9"/>
+    <col width="11.77734375" customWidth="1" style="32" min="10" max="10"/>
+    <col width="8.6640625" customWidth="1" style="32" min="11" max="12"/>
+    <col width="0.88671875" customWidth="1" style="32" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" customHeight="1" s="32">
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>NO.　{{No}}</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="49" t="inlineStr">
+        <is>
+          <t>内訳明細</t>
+        </is>
+      </c>
+      <c r="J1" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P.　　　3 </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1" s="32">
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1" s="32">
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="n"/>
+      <c r="I3" s="1" t="n"/>
+      <c r="J3" s="1" t="n"/>
+      <c r="K3" s="1" t="n"/>
+      <c r="L3" s="1" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1" s="32">
+      <c r="B4" s="1" t="n"/>
+      <c r="C4" s="46" t="inlineStr">
+        <is>
+          <t>品　　　名</t>
+        </is>
+      </c>
+      <c r="D4" s="47" t="n"/>
+      <c r="E4" s="47" t="n"/>
+      <c r="F4" s="47" t="n"/>
+      <c r="G4" s="48" t="n"/>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>数　量</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>単位</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>単　価</t>
+        </is>
+      </c>
+      <c r="K4" s="29" t="inlineStr">
+        <is>
+          <t>金　　額</t>
+        </is>
+      </c>
+      <c r="L4" s="30" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1" s="32">
+      <c r="B5" s="1" t="n"/>
+      <c r="C5" s="38" t="n"/>
+      <c r="D5" s="39" t="n"/>
+      <c r="E5" s="39" t="n"/>
+      <c r="F5" s="39" t="n"/>
+      <c r="G5" s="40" t="n"/>
+      <c r="H5" s="68" t="n"/>
+      <c r="I5" s="22" t="n"/>
+      <c r="J5" s="23" t="n"/>
+      <c r="K5" s="41" t="n"/>
+      <c r="L5" s="42" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1" s="32">
+      <c r="B6" s="1" t="n"/>
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="39" t="n"/>
+      <c r="E6" s="39" t="n"/>
+      <c r="F6" s="39" t="n"/>
+      <c r="G6" s="40" t="n"/>
+      <c r="H6" s="68" t="n"/>
+      <c r="I6" s="22" t="n"/>
+      <c r="J6" s="23" t="n"/>
+      <c r="K6" s="41" t="n"/>
+      <c r="L6" s="42" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1" s="32">
+      <c r="B7" s="1" t="n"/>
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="39" t="n"/>
+      <c r="E7" s="39" t="n"/>
+      <c r="F7" s="39" t="n"/>
+      <c r="G7" s="40" t="n"/>
+      <c r="H7" s="68" t="n"/>
+      <c r="I7" s="22" t="n"/>
+      <c r="J7" s="23" t="n"/>
+      <c r="K7" s="41" t="n"/>
+      <c r="L7" s="42" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1" s="32">
+      <c r="B8" s="1" t="n"/>
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="39" t="n"/>
+      <c r="E8" s="39" t="n"/>
+      <c r="F8" s="39" t="n"/>
+      <c r="G8" s="40" t="n"/>
+      <c r="H8" s="68" t="n"/>
+      <c r="I8" s="22" t="n"/>
+      <c r="J8" s="23" t="n"/>
+      <c r="K8" s="41" t="n"/>
+      <c r="L8" s="42" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1" s="32">
+      <c r="B9" s="1" t="n"/>
+      <c r="C9" s="38" t="n"/>
+      <c r="D9" s="39" t="n"/>
+      <c r="E9" s="39" t="n"/>
+      <c r="F9" s="39" t="n"/>
+      <c r="G9" s="40" t="n"/>
+      <c r="H9" s="68" t="n"/>
+      <c r="I9" s="22" t="n"/>
+      <c r="J9" s="23" t="n"/>
+      <c r="K9" s="41" t="n"/>
+      <c r="L9" s="42" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1" s="32">
+      <c r="B10" s="1" t="n"/>
+      <c r="C10" s="38" t="n"/>
+      <c r="D10" s="39" t="n"/>
+      <c r="E10" s="39" t="n"/>
+      <c r="F10" s="39" t="n"/>
+      <c r="G10" s="40" t="n"/>
+      <c r="H10" s="68" t="n"/>
+      <c r="I10" s="22" t="n"/>
+      <c r="J10" s="23" t="n"/>
+      <c r="K10" s="41" t="n"/>
+      <c r="L10" s="42" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1" s="32">
+      <c r="B11" s="1" t="n"/>
+      <c r="C11" s="38" t="n"/>
+      <c r="D11" s="39" t="n"/>
+      <c r="E11" s="39" t="n"/>
+      <c r="F11" s="39" t="n"/>
+      <c r="G11" s="40" t="n"/>
+      <c r="H11" s="68" t="n"/>
+      <c r="I11" s="22" t="n"/>
+      <c r="J11" s="23" t="n"/>
+      <c r="K11" s="41" t="n"/>
+      <c r="L11" s="42" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1" s="32">
+      <c r="B12" s="1" t="n"/>
+      <c r="C12" s="38" t="n"/>
+      <c r="D12" s="39" t="n"/>
+      <c r="E12" s="39" t="n"/>
+      <c r="F12" s="39" t="n"/>
+      <c r="G12" s="40" t="n"/>
+      <c r="H12" s="68" t="n"/>
+      <c r="I12" s="22" t="n"/>
+      <c r="J12" s="23" t="n"/>
+      <c r="K12" s="41" t="n"/>
+      <c r="L12" s="42" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1" s="32">
+      <c r="B13" s="1" t="n"/>
+      <c r="C13" s="38" t="n"/>
+      <c r="D13" s="39" t="n"/>
+      <c r="E13" s="39" t="n"/>
+      <c r="F13" s="39" t="n"/>
+      <c r="G13" s="40" t="n"/>
+      <c r="H13" s="68" t="n"/>
+      <c r="I13" s="22" t="n"/>
+      <c r="J13" s="23" t="n"/>
+      <c r="K13" s="41" t="n"/>
+      <c r="L13" s="42" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1" s="32">
+      <c r="B14" s="1" t="n"/>
+      <c r="C14" s="38" t="n"/>
+      <c r="D14" s="39" t="n"/>
+      <c r="E14" s="39" t="n"/>
+      <c r="F14" s="39" t="n"/>
+      <c r="G14" s="40" t="n"/>
+      <c r="H14" s="68" t="n"/>
+      <c r="I14" s="22" t="n"/>
+      <c r="J14" s="23" t="n"/>
+      <c r="K14" s="41" t="n"/>
+      <c r="L14" s="42" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1" s="32">
+      <c r="B15" s="1" t="n"/>
+      <c r="C15" s="38" t="n"/>
+      <c r="D15" s="39" t="n"/>
+      <c r="E15" s="39" t="n"/>
+      <c r="F15" s="39" t="n"/>
+      <c r="G15" s="40" t="n"/>
+      <c r="H15" s="68" t="n"/>
+      <c r="I15" s="22" t="n"/>
+      <c r="J15" s="23" t="n"/>
+      <c r="K15" s="41" t="n"/>
+      <c r="L15" s="42" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1" s="32">
+      <c r="B16" s="1" t="n"/>
+      <c r="C16" s="38" t="n"/>
+      <c r="D16" s="39" t="n"/>
+      <c r="E16" s="39" t="n"/>
+      <c r="F16" s="39" t="n"/>
+      <c r="G16" s="40" t="n"/>
+      <c r="H16" s="68" t="n"/>
+      <c r="I16" s="22" t="n"/>
+      <c r="J16" s="23" t="n"/>
+      <c r="K16" s="41" t="n"/>
+      <c r="L16" s="42" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1" s="32">
+      <c r="B17" s="1" t="n"/>
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="39" t="n"/>
+      <c r="E17" s="39" t="n"/>
+      <c r="F17" s="39" t="n"/>
+      <c r="G17" s="40" t="n"/>
+      <c r="H17" s="68" t="n"/>
+      <c r="I17" s="22" t="n"/>
+      <c r="J17" s="23" t="n"/>
+      <c r="K17" s="41" t="n"/>
+      <c r="L17" s="42" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1" s="32">
+      <c r="B18" s="1" t="n"/>
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="39" t="n"/>
+      <c r="E18" s="39" t="n"/>
+      <c r="F18" s="39" t="n"/>
+      <c r="G18" s="40" t="n"/>
+      <c r="H18" s="68" t="n"/>
+      <c r="I18" s="22" t="n"/>
+      <c r="J18" s="23" t="n"/>
+      <c r="K18" s="41" t="n"/>
+      <c r="L18" s="42" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1" s="32">
+      <c r="B19" s="1" t="n"/>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="39" t="n"/>
+      <c r="E19" s="39" t="n"/>
+      <c r="F19" s="39" t="n"/>
+      <c r="G19" s="40" t="n"/>
+      <c r="H19" s="68" t="n"/>
+      <c r="I19" s="22" t="n"/>
+      <c r="J19" s="23" t="n"/>
+      <c r="K19" s="41" t="n"/>
+      <c r="L19" s="42" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1" s="32">
+      <c r="B20" s="1" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="39" t="n"/>
+      <c r="E20" s="39" t="n"/>
+      <c r="F20" s="39" t="n"/>
+      <c r="G20" s="40" t="n"/>
+      <c r="H20" s="68" t="n"/>
+      <c r="I20" s="22" t="n"/>
+      <c r="J20" s="23" t="n"/>
+      <c r="K20" s="41" t="n"/>
+      <c r="L20" s="42" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1" s="32">
+      <c r="B21" s="1" t="n"/>
+      <c r="C21" s="38" t="n"/>
+      <c r="D21" s="39" t="n"/>
+      <c r="E21" s="39" t="n"/>
+      <c r="F21" s="39" t="n"/>
+      <c r="G21" s="40" t="n"/>
+      <c r="H21" s="68" t="n"/>
+      <c r="I21" s="22" t="n"/>
+      <c r="J21" s="23" t="n"/>
+      <c r="K21" s="41" t="n"/>
+      <c r="L21" s="42" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1" s="32">
+      <c r="B22" s="1" t="n"/>
+      <c r="C22" s="38" t="n"/>
+      <c r="D22" s="39" t="n"/>
+      <c r="E22" s="39" t="n"/>
+      <c r="F22" s="39" t="n"/>
+      <c r="G22" s="40" t="n"/>
+      <c r="H22" s="68" t="n"/>
+      <c r="I22" s="22" t="n"/>
+      <c r="J22" s="23" t="n"/>
+      <c r="K22" s="41" t="n"/>
+      <c r="L22" s="42" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1" s="32">
+      <c r="B23" s="1" t="n"/>
+      <c r="C23" s="38" t="n"/>
+      <c r="D23" s="39" t="n"/>
+      <c r="E23" s="39" t="n"/>
+      <c r="F23" s="39" t="n"/>
+      <c r="G23" s="40" t="n"/>
+      <c r="H23" s="68" t="n"/>
+      <c r="I23" s="22" t="n"/>
+      <c r="J23" s="23" t="n"/>
+      <c r="K23" s="41" t="n"/>
+      <c r="L23" s="42" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1" s="32">
+      <c r="B24" s="1" t="n"/>
+      <c r="C24" s="38" t="n"/>
+      <c r="D24" s="39" t="n"/>
+      <c r="E24" s="39" t="n"/>
+      <c r="F24" s="39" t="n"/>
+      <c r="G24" s="40" t="n"/>
+      <c r="H24" s="68" t="n"/>
+      <c r="I24" s="22" t="n"/>
+      <c r="J24" s="23" t="n"/>
+      <c r="K24" s="41" t="n"/>
+      <c r="L24" s="42" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1" s="32">
+      <c r="B25" s="1" t="n"/>
+      <c r="C25" s="38" t="n"/>
+      <c r="D25" s="39" t="n"/>
+      <c r="E25" s="39" t="n"/>
+      <c r="F25" s="39" t="n"/>
+      <c r="G25" s="40" t="n"/>
+      <c r="H25" s="68" t="n"/>
+      <c r="I25" s="22" t="n"/>
+      <c r="J25" s="23" t="n"/>
+      <c r="K25" s="41" t="n"/>
+      <c r="L25" s="42" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1" s="32">
+      <c r="B26" s="1" t="n"/>
+      <c r="C26" s="38" t="n"/>
+      <c r="D26" s="39" t="n"/>
+      <c r="E26" s="39" t="n"/>
+      <c r="F26" s="39" t="n"/>
+      <c r="G26" s="40" t="n"/>
+      <c r="H26" s="68" t="n"/>
+      <c r="I26" s="22" t="n"/>
+      <c r="J26" s="23" t="n"/>
+      <c r="K26" s="41" t="n"/>
+      <c r="L26" s="42" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1" s="32">
+      <c r="B27" s="1" t="n"/>
+      <c r="C27" s="38" t="n"/>
+      <c r="D27" s="39" t="n"/>
+      <c r="E27" s="39" t="n"/>
+      <c r="F27" s="39" t="n"/>
+      <c r="G27" s="40" t="n"/>
+      <c r="H27" s="68" t="n"/>
+      <c r="I27" s="22" t="n"/>
+      <c r="J27" s="23" t="n"/>
+      <c r="K27" s="41" t="n"/>
+      <c r="L27" s="42" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1" s="32">
+      <c r="B28" s="1" t="n"/>
+      <c r="C28" s="38" t="n"/>
+      <c r="D28" s="39" t="n"/>
+      <c r="E28" s="39" t="n"/>
+      <c r="F28" s="39" t="n"/>
+      <c r="G28" s="40" t="n"/>
+      <c r="H28" s="68" t="n"/>
+      <c r="I28" s="22" t="n"/>
+      <c r="J28" s="23" t="n"/>
+      <c r="K28" s="41" t="n"/>
+      <c r="L28" s="42" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1" s="32">
+      <c r="B29" s="1" t="n"/>
+      <c r="C29" s="67" t="n"/>
+      <c r="D29" s="39" t="n"/>
+      <c r="E29" s="39" t="n"/>
+      <c r="F29" s="39" t="n"/>
+      <c r="G29" s="40" t="n"/>
+      <c r="H29" s="68" t="n"/>
+      <c r="I29" s="22" t="n"/>
+      <c r="J29" s="23" t="n"/>
+      <c r="K29" s="41" t="n"/>
+      <c r="L29" s="42" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1" s="32">
+      <c r="B30" s="1" t="n"/>
+      <c r="C30" s="67" t="n"/>
+      <c r="D30" s="39" t="n"/>
+      <c r="E30" s="39" t="n"/>
+      <c r="F30" s="39" t="n"/>
+      <c r="G30" s="40" t="n"/>
+      <c r="H30" s="68" t="n"/>
+      <c r="I30" s="22" t="n"/>
+      <c r="J30" s="23" t="n"/>
+      <c r="K30" s="41" t="n"/>
+      <c r="L30" s="42" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1" s="32">
+      <c r="B31" s="1" t="n"/>
+      <c r="C31" s="67" t="n"/>
+      <c r="D31" s="39" t="n"/>
+      <c r="E31" s="39" t="n"/>
+      <c r="F31" s="39" t="n"/>
+      <c r="G31" s="40" t="n"/>
+      <c r="H31" s="68" t="n"/>
+      <c r="I31" s="22" t="n"/>
+      <c r="J31" s="23" t="n"/>
+      <c r="K31" s="41" t="n"/>
+      <c r="L31" s="42" t="n"/>
+    </row>
+    <row r="32" ht="18" customHeight="1" s="32">
+      <c r="B32" s="1" t="n"/>
+      <c r="C32" s="67" t="n"/>
+      <c r="D32" s="39" t="n"/>
+      <c r="E32" s="39" t="n"/>
+      <c r="F32" s="39" t="n"/>
+      <c r="G32" s="40" t="n"/>
+      <c r="H32" s="68" t="n"/>
+      <c r="I32" s="22" t="n"/>
+      <c r="J32" s="23" t="n"/>
+      <c r="K32" s="41" t="n"/>
+      <c r="L32" s="42" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1" s="32">
+      <c r="B33" s="1" t="n"/>
+      <c r="C33" s="67" t="n"/>
+      <c r="D33" s="39" t="n"/>
+      <c r="E33" s="39" t="n"/>
+      <c r="F33" s="39" t="n"/>
+      <c r="G33" s="40" t="n"/>
+      <c r="H33" s="68" t="n"/>
+      <c r="I33" s="22" t="n"/>
+      <c r="J33" s="23" t="n"/>
+      <c r="K33" s="41" t="n"/>
+      <c r="L33" s="42" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1" s="32">
+      <c r="B34" s="1" t="n"/>
+      <c r="C34" s="67" t="n"/>
+      <c r="D34" s="39" t="n"/>
+      <c r="E34" s="39" t="n"/>
+      <c r="F34" s="39" t="n"/>
+      <c r="G34" s="40" t="n"/>
+      <c r="H34" s="68" t="n"/>
+      <c r="I34" s="22" t="n"/>
+      <c r="J34" s="23" t="n"/>
+      <c r="K34" s="41" t="n"/>
+      <c r="L34" s="42" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1" s="32">
+      <c r="B35" s="1" t="n"/>
+      <c r="C35" s="38" t="n"/>
+      <c r="D35" s="39" t="n"/>
+      <c r="E35" s="39" t="n"/>
+      <c r="F35" s="39" t="n"/>
+      <c r="G35" s="40" t="n"/>
+      <c r="H35" s="68" t="n"/>
+      <c r="I35" s="22" t="n"/>
+      <c r="J35" s="23" t="n"/>
+      <c r="K35" s="41" t="n"/>
+      <c r="L35" s="42" t="n"/>
+    </row>
+    <row r="36" ht="18" customHeight="1" s="32">
+      <c r="B36" s="1" t="n"/>
+      <c r="C36" s="38" t="n"/>
+      <c r="D36" s="39" t="n"/>
+      <c r="E36" s="39" t="n"/>
+      <c r="F36" s="39" t="n"/>
+      <c r="G36" s="40" t="n"/>
+      <c r="H36" s="68" t="n"/>
+      <c r="I36" s="22" t="n"/>
+      <c r="J36" s="23" t="n"/>
+      <c r="K36" s="41" t="n"/>
+      <c r="L36" s="42" t="n"/>
+    </row>
+    <row r="37" ht="18" customHeight="1" s="32">
+      <c r="B37" s="1" t="n"/>
+      <c r="C37" s="38" t="n"/>
+      <c r="D37" s="39" t="n"/>
+      <c r="E37" s="39" t="n"/>
+      <c r="F37" s="39" t="n"/>
+      <c r="G37" s="40" t="n"/>
+      <c r="H37" s="68" t="n"/>
+      <c r="I37" s="22" t="n"/>
+      <c r="J37" s="23" t="n"/>
+      <c r="K37" s="41" t="n"/>
+      <c r="L37" s="42" t="n"/>
+    </row>
+    <row r="38" ht="18" customHeight="1" s="32">
+      <c r="B38" s="1" t="n"/>
+      <c r="C38" s="38" t="n"/>
+      <c r="D38" s="39" t="n"/>
+      <c r="E38" s="39" t="n"/>
+      <c r="F38" s="39" t="n"/>
+      <c r="G38" s="40" t="n"/>
+      <c r="H38" s="68" t="n"/>
+      <c r="I38" s="22" t="n"/>
+      <c r="J38" s="23" t="n"/>
+      <c r="K38" s="41" t="n"/>
+      <c r="L38" s="42" t="n"/>
+    </row>
+    <row r="39" ht="18" customHeight="1" s="32">
+      <c r="B39" s="1" t="n"/>
+      <c r="C39" s="38" t="n"/>
+      <c r="D39" s="39" t="n"/>
+      <c r="E39" s="39" t="n"/>
+      <c r="F39" s="39" t="n"/>
+      <c r="G39" s="40" t="n"/>
+      <c r="H39" s="68" t="n"/>
+      <c r="I39" s="22" t="n"/>
+      <c r="J39" s="23" t="n"/>
+      <c r="K39" s="41" t="n"/>
+      <c r="L39" s="42" t="n"/>
+    </row>
+    <row r="40" ht="18" customHeight="1" s="32">
+      <c r="B40" s="1" t="n"/>
+      <c r="C40" s="38" t="n"/>
+      <c r="D40" s="39" t="n"/>
+      <c r="E40" s="39" t="n"/>
+      <c r="F40" s="39" t="n"/>
+      <c r="G40" s="40" t="n"/>
+      <c r="H40" s="68" t="n"/>
+      <c r="I40" s="22" t="n"/>
+      <c r="J40" s="23" t="n"/>
+      <c r="K40" s="41" t="n"/>
+      <c r="L40" s="42" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1" s="32">
+      <c r="B41" s="1" t="n"/>
+      <c r="C41" s="38" t="n"/>
+      <c r="D41" s="39" t="n"/>
+      <c r="E41" s="39" t="n"/>
+      <c r="F41" s="39" t="n"/>
+      <c r="G41" s="40" t="n"/>
+      <c r="H41" s="68" t="n"/>
+      <c r="I41" s="22" t="n"/>
+      <c r="J41" s="23" t="n"/>
+      <c r="K41" s="41" t="n"/>
+      <c r="L41" s="42" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1" s="32">
+      <c r="B42" s="1" t="n"/>
+      <c r="C42" s="38" t="n"/>
+      <c r="D42" s="39" t="n"/>
+      <c r="E42" s="39" t="n"/>
+      <c r="F42" s="39" t="n"/>
+      <c r="G42" s="40" t="n"/>
+      <c r="H42" s="68" t="n"/>
+      <c r="I42" s="22" t="n"/>
+      <c r="J42" s="23" t="n"/>
+      <c r="K42" s="41" t="n"/>
+      <c r="L42" s="42" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1" s="32">
+      <c r="B43" s="1" t="n"/>
+      <c r="C43" s="38" t="n"/>
+      <c r="D43" s="39" t="n"/>
+      <c r="E43" s="39" t="n"/>
+      <c r="F43" s="39" t="n"/>
+      <c r="G43" s="40" t="n"/>
+      <c r="H43" s="68" t="n"/>
+      <c r="I43" s="27" t="n"/>
+      <c r="J43" s="26" t="n"/>
+      <c r="K43" s="41" t="n"/>
+      <c r="L43" s="42" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1" s="32">
+      <c r="B44" s="1" t="n"/>
+      <c r="C44" s="38" t="n"/>
+      <c r="D44" s="39" t="n"/>
+      <c r="E44" s="39" t="n"/>
+      <c r="F44" s="39" t="n"/>
+      <c r="G44" s="40" t="n"/>
+      <c r="H44" s="68" t="n"/>
+      <c r="I44" s="22" t="n"/>
+      <c r="J44" s="23" t="n"/>
+      <c r="K44" s="41" t="n"/>
+      <c r="L44" s="42" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1" s="32">
+      <c r="B45" s="1" t="n"/>
+      <c r="C45" s="38" t="n"/>
+      <c r="D45" s="39" t="n"/>
+      <c r="E45" s="39" t="n"/>
+      <c r="F45" s="39" t="n"/>
+      <c r="G45" s="40" t="n"/>
+      <c r="H45" s="68" t="n"/>
+      <c r="I45" s="22" t="n"/>
+      <c r="J45" s="23" t="n"/>
+      <c r="K45" s="41" t="n"/>
+      <c r="L45" s="42" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1" s="32">
+      <c r="B46" s="1" t="n"/>
+      <c r="C46" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合  計  </t>
+        </is>
+      </c>
+      <c r="D46" s="47" t="n"/>
+      <c r="E46" s="47" t="n"/>
+      <c r="F46" s="47" t="n"/>
+      <c r="G46" s="47" t="n"/>
+      <c r="H46" s="47" t="n"/>
+      <c r="I46" s="47" t="n"/>
+      <c r="J46" s="48" t="n"/>
+      <c r="K46" s="45">
+        <f>SUM(K5:L45)</f>
+        <v/>
+      </c>
+      <c r="L46" s="30" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="88">
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C46:J46"/>
+    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="F1:I2"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="K41:L41"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="K45:L45"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="K36:L36"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="K4:L4"/>
+  </mergeCells>
+  <pageMargins left="0.7868055555555555" right="0.5902777777777778" top="0.9840277777777777" bottom="0.9840277777777777" header="0.5111111111111111" footer="0.5111111111111111"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="90"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:L46"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.2"/>
+  <cols>
+    <col width="13" customWidth="1" style="32" min="1" max="1"/>
+    <col width="0.88671875" customWidth="1" style="32" min="2" max="2"/>
+    <col width="11.109375" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
+    <col width="6.5546875" customWidth="1" style="32" min="4" max="4"/>
+    <col width="18.77734375" customWidth="1" style="32" min="5" max="5"/>
+    <col width="8.44140625" bestFit="1" customWidth="1" style="32" min="6" max="6"/>
+    <col width="8.77734375" customWidth="1" style="32" min="7" max="7"/>
+    <col width="6.21875" customWidth="1" style="32" min="8" max="8"/>
+    <col width="5.6640625" customWidth="1" style="32" min="9" max="9"/>
+    <col width="11.77734375" customWidth="1" style="32" min="10" max="10"/>
+    <col width="8.6640625" customWidth="1" style="32" min="11" max="12"/>
+    <col width="0.88671875" customWidth="1" style="32" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" customHeight="1" s="32">
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>NO.　{{No}}</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="49" t="inlineStr">
+        <is>
+          <t>内訳明細</t>
+        </is>
+      </c>
+      <c r="J1" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P.　　　4 </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1" s="32">
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1" s="32">
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="n"/>
+      <c r="I3" s="1" t="n"/>
+      <c r="J3" s="1" t="n"/>
+      <c r="K3" s="1" t="n"/>
+      <c r="L3" s="1" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1" s="32">
+      <c r="B4" s="1" t="n"/>
+      <c r="C4" s="46" t="inlineStr">
+        <is>
+          <t>品　　　名</t>
+        </is>
+      </c>
+      <c r="D4" s="47" t="n"/>
+      <c r="E4" s="47" t="n"/>
+      <c r="F4" s="47" t="n"/>
+      <c r="G4" s="48" t="n"/>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>数　量</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>単位</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>単　価</t>
+        </is>
+      </c>
+      <c r="K4" s="29" t="inlineStr">
+        <is>
+          <t>金　　額</t>
+        </is>
+      </c>
+      <c r="L4" s="30" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1" s="32">
+      <c r="B5" s="1" t="n"/>
+      <c r="C5" s="38" t="n"/>
+      <c r="D5" s="39" t="n"/>
+      <c r="E5" s="39" t="n"/>
+      <c r="F5" s="39" t="n"/>
+      <c r="G5" s="40" t="n"/>
+      <c r="H5" s="68" t="n"/>
+      <c r="I5" s="22" t="n"/>
+      <c r="J5" s="23" t="n"/>
+      <c r="K5" s="41" t="n"/>
+      <c r="L5" s="42" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1" s="32">
+      <c r="B6" s="1" t="n"/>
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="39" t="n"/>
+      <c r="E6" s="39" t="n"/>
+      <c r="F6" s="39" t="n"/>
+      <c r="G6" s="40" t="n"/>
+      <c r="H6" s="68" t="n"/>
+      <c r="I6" s="22" t="n"/>
+      <c r="J6" s="23" t="n"/>
+      <c r="K6" s="41" t="n"/>
+      <c r="L6" s="42" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1" s="32">
+      <c r="B7" s="1" t="n"/>
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="39" t="n"/>
+      <c r="E7" s="39" t="n"/>
+      <c r="F7" s="39" t="n"/>
+      <c r="G7" s="40" t="n"/>
+      <c r="H7" s="68" t="n"/>
+      <c r="I7" s="22" t="n"/>
+      <c r="J7" s="23" t="n"/>
+      <c r="K7" s="41" t="n"/>
+      <c r="L7" s="42" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1" s="32">
+      <c r="B8" s="1" t="n"/>
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="39" t="n"/>
+      <c r="E8" s="39" t="n"/>
+      <c r="F8" s="39" t="n"/>
+      <c r="G8" s="40" t="n"/>
+      <c r="H8" s="68" t="n"/>
+      <c r="I8" s="22" t="n"/>
+      <c r="J8" s="23" t="n"/>
+      <c r="K8" s="41" t="n"/>
+      <c r="L8" s="42" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1" s="32">
+      <c r="B9" s="1" t="n"/>
+      <c r="C9" s="38" t="n"/>
+      <c r="D9" s="39" t="n"/>
+      <c r="E9" s="39" t="n"/>
+      <c r="F9" s="39" t="n"/>
+      <c r="G9" s="40" t="n"/>
+      <c r="H9" s="68" t="n"/>
+      <c r="I9" s="22" t="n"/>
+      <c r="J9" s="23" t="n"/>
+      <c r="K9" s="41" t="n"/>
+      <c r="L9" s="42" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1" s="32">
+      <c r="B10" s="1" t="n"/>
+      <c r="C10" s="38" t="n"/>
+      <c r="D10" s="39" t="n"/>
+      <c r="E10" s="39" t="n"/>
+      <c r="F10" s="39" t="n"/>
+      <c r="G10" s="40" t="n"/>
+      <c r="H10" s="68" t="n"/>
+      <c r="I10" s="22" t="n"/>
+      <c r="J10" s="23" t="n"/>
+      <c r="K10" s="41" t="n"/>
+      <c r="L10" s="42" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1" s="32">
+      <c r="B11" s="1" t="n"/>
+      <c r="C11" s="38" t="n"/>
+      <c r="D11" s="39" t="n"/>
+      <c r="E11" s="39" t="n"/>
+      <c r="F11" s="39" t="n"/>
+      <c r="G11" s="40" t="n"/>
+      <c r="H11" s="68" t="n"/>
+      <c r="I11" s="22" t="n"/>
+      <c r="J11" s="23" t="n"/>
+      <c r="K11" s="41" t="n"/>
+      <c r="L11" s="42" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1" s="32">
+      <c r="B12" s="1" t="n"/>
+      <c r="C12" s="38" t="n"/>
+      <c r="D12" s="39" t="n"/>
+      <c r="E12" s="39" t="n"/>
+      <c r="F12" s="39" t="n"/>
+      <c r="G12" s="40" t="n"/>
+      <c r="H12" s="68" t="n"/>
+      <c r="I12" s="22" t="n"/>
+      <c r="J12" s="23" t="n"/>
+      <c r="K12" s="41" t="n"/>
+      <c r="L12" s="42" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1" s="32">
+      <c r="B13" s="1" t="n"/>
+      <c r="C13" s="38" t="n"/>
+      <c r="D13" s="39" t="n"/>
+      <c r="E13" s="39" t="n"/>
+      <c r="F13" s="39" t="n"/>
+      <c r="G13" s="40" t="n"/>
+      <c r="H13" s="68" t="n"/>
+      <c r="I13" s="22" t="n"/>
+      <c r="J13" s="23" t="n"/>
+      <c r="K13" s="41" t="n"/>
+      <c r="L13" s="42" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1" s="32">
+      <c r="B14" s="1" t="n"/>
+      <c r="C14" s="38" t="n"/>
+      <c r="D14" s="39" t="n"/>
+      <c r="E14" s="39" t="n"/>
+      <c r="F14" s="39" t="n"/>
+      <c r="G14" s="40" t="n"/>
+      <c r="H14" s="68" t="n"/>
+      <c r="I14" s="22" t="n"/>
+      <c r="J14" s="23" t="n"/>
+      <c r="K14" s="41" t="n"/>
+      <c r="L14" s="42" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1" s="32">
+      <c r="B15" s="1" t="n"/>
+      <c r="C15" s="38" t="n"/>
+      <c r="D15" s="39" t="n"/>
+      <c r="E15" s="39" t="n"/>
+      <c r="F15" s="39" t="n"/>
+      <c r="G15" s="40" t="n"/>
+      <c r="H15" s="68" t="n"/>
+      <c r="I15" s="22" t="n"/>
+      <c r="J15" s="23" t="n"/>
+      <c r="K15" s="41" t="n"/>
+      <c r="L15" s="42" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1" s="32">
+      <c r="B16" s="1" t="n"/>
+      <c r="C16" s="38" t="n"/>
+      <c r="D16" s="39" t="n"/>
+      <c r="E16" s="39" t="n"/>
+      <c r="F16" s="39" t="n"/>
+      <c r="G16" s="40" t="n"/>
+      <c r="H16" s="68" t="n"/>
+      <c r="I16" s="22" t="n"/>
+      <c r="J16" s="23" t="n"/>
+      <c r="K16" s="41" t="n"/>
+      <c r="L16" s="42" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1" s="32">
+      <c r="B17" s="1" t="n"/>
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="39" t="n"/>
+      <c r="E17" s="39" t="n"/>
+      <c r="F17" s="39" t="n"/>
+      <c r="G17" s="40" t="n"/>
+      <c r="H17" s="68" t="n"/>
+      <c r="I17" s="22" t="n"/>
+      <c r="J17" s="23" t="n"/>
+      <c r="K17" s="41" t="n"/>
+      <c r="L17" s="42" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1" s="32">
+      <c r="B18" s="1" t="n"/>
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="39" t="n"/>
+      <c r="E18" s="39" t="n"/>
+      <c r="F18" s="39" t="n"/>
+      <c r="G18" s="40" t="n"/>
+      <c r="H18" s="68" t="n"/>
+      <c r="I18" s="22" t="n"/>
+      <c r="J18" s="23" t="n"/>
+      <c r="K18" s="41" t="n"/>
+      <c r="L18" s="42" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1" s="32">
+      <c r="B19" s="1" t="n"/>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="39" t="n"/>
+      <c r="E19" s="39" t="n"/>
+      <c r="F19" s="39" t="n"/>
+      <c r="G19" s="40" t="n"/>
+      <c r="H19" s="68" t="n"/>
+      <c r="I19" s="22" t="n"/>
+      <c r="J19" s="23" t="n"/>
+      <c r="K19" s="41" t="n"/>
+      <c r="L19" s="42" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1" s="32">
+      <c r="B20" s="1" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="39" t="n"/>
+      <c r="E20" s="39" t="n"/>
+      <c r="F20" s="39" t="n"/>
+      <c r="G20" s="40" t="n"/>
+      <c r="H20" s="68" t="n"/>
+      <c r="I20" s="22" t="n"/>
+      <c r="J20" s="23" t="n"/>
+      <c r="K20" s="41" t="n"/>
+      <c r="L20" s="42" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1" s="32">
+      <c r="B21" s="1" t="n"/>
+      <c r="C21" s="38" t="n"/>
+      <c r="D21" s="39" t="n"/>
+      <c r="E21" s="39" t="n"/>
+      <c r="F21" s="39" t="n"/>
+      <c r="G21" s="40" t="n"/>
+      <c r="H21" s="68" t="n"/>
+      <c r="I21" s="22" t="n"/>
+      <c r="J21" s="23" t="n"/>
+      <c r="K21" s="41" t="n"/>
+      <c r="L21" s="42" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1" s="32">
+      <c r="B22" s="1" t="n"/>
+      <c r="C22" s="38" t="n"/>
+      <c r="D22" s="39" t="n"/>
+      <c r="E22" s="39" t="n"/>
+      <c r="F22" s="39" t="n"/>
+      <c r="G22" s="40" t="n"/>
+      <c r="H22" s="68" t="n"/>
+      <c r="I22" s="22" t="n"/>
+      <c r="J22" s="23" t="n"/>
+      <c r="K22" s="41" t="n"/>
+      <c r="L22" s="42" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1" s="32">
+      <c r="B23" s="1" t="n"/>
+      <c r="C23" s="38" t="n"/>
+      <c r="D23" s="39" t="n"/>
+      <c r="E23" s="39" t="n"/>
+      <c r="F23" s="39" t="n"/>
+      <c r="G23" s="40" t="n"/>
+      <c r="H23" s="68" t="n"/>
+      <c r="I23" s="22" t="n"/>
+      <c r="J23" s="23" t="n"/>
+      <c r="K23" s="41" t="n"/>
+      <c r="L23" s="42" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1" s="32">
+      <c r="B24" s="1" t="n"/>
+      <c r="C24" s="38" t="n"/>
+      <c r="D24" s="39" t="n"/>
+      <c r="E24" s="39" t="n"/>
+      <c r="F24" s="39" t="n"/>
+      <c r="G24" s="40" t="n"/>
+      <c r="H24" s="68" t="n"/>
+      <c r="I24" s="22" t="n"/>
+      <c r="J24" s="23" t="n"/>
+      <c r="K24" s="41" t="n"/>
+      <c r="L24" s="42" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1" s="32">
+      <c r="B25" s="1" t="n"/>
+      <c r="C25" s="38" t="n"/>
+      <c r="D25" s="39" t="n"/>
+      <c r="E25" s="39" t="n"/>
+      <c r="F25" s="39" t="n"/>
+      <c r="G25" s="40" t="n"/>
+      <c r="H25" s="68" t="n"/>
+      <c r="I25" s="22" t="n"/>
+      <c r="J25" s="23" t="n"/>
+      <c r="K25" s="41" t="n"/>
+      <c r="L25" s="42" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1" s="32">
+      <c r="B26" s="1" t="n"/>
+      <c r="C26" s="38" t="n"/>
+      <c r="D26" s="39" t="n"/>
+      <c r="E26" s="39" t="n"/>
+      <c r="F26" s="39" t="n"/>
+      <c r="G26" s="40" t="n"/>
+      <c r="H26" s="68" t="n"/>
+      <c r="I26" s="22" t="n"/>
+      <c r="J26" s="23" t="n"/>
+      <c r="K26" s="41" t="n"/>
+      <c r="L26" s="42" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1" s="32">
+      <c r="B27" s="1" t="n"/>
+      <c r="C27" s="38" t="n"/>
+      <c r="D27" s="39" t="n"/>
+      <c r="E27" s="39" t="n"/>
+      <c r="F27" s="39" t="n"/>
+      <c r="G27" s="40" t="n"/>
+      <c r="H27" s="68" t="n"/>
+      <c r="I27" s="22" t="n"/>
+      <c r="J27" s="23" t="n"/>
+      <c r="K27" s="41" t="n"/>
+      <c r="L27" s="42" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1" s="32">
+      <c r="B28" s="1" t="n"/>
+      <c r="C28" s="38" t="n"/>
+      <c r="D28" s="39" t="n"/>
+      <c r="E28" s="39" t="n"/>
+      <c r="F28" s="39" t="n"/>
+      <c r="G28" s="40" t="n"/>
+      <c r="H28" s="68" t="n"/>
+      <c r="I28" s="22" t="n"/>
+      <c r="J28" s="23" t="n"/>
+      <c r="K28" s="41" t="n"/>
+      <c r="L28" s="42" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1" s="32">
+      <c r="B29" s="1" t="n"/>
+      <c r="C29" s="67" t="n"/>
+      <c r="D29" s="39" t="n"/>
+      <c r="E29" s="39" t="n"/>
+      <c r="F29" s="39" t="n"/>
+      <c r="G29" s="40" t="n"/>
+      <c r="H29" s="68" t="n"/>
+      <c r="I29" s="22" t="n"/>
+      <c r="J29" s="23" t="n"/>
+      <c r="K29" s="41" t="n"/>
+      <c r="L29" s="42" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1" s="32">
+      <c r="B30" s="1" t="n"/>
+      <c r="C30" s="67" t="n"/>
+      <c r="D30" s="39" t="n"/>
+      <c r="E30" s="39" t="n"/>
+      <c r="F30" s="39" t="n"/>
+      <c r="G30" s="40" t="n"/>
+      <c r="H30" s="68" t="n"/>
+      <c r="I30" s="22" t="n"/>
+      <c r="J30" s="23" t="n"/>
+      <c r="K30" s="41" t="n"/>
+      <c r="L30" s="42" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1" s="32">
+      <c r="B31" s="1" t="n"/>
+      <c r="C31" s="67" t="n"/>
+      <c r="D31" s="39" t="n"/>
+      <c r="E31" s="39" t="n"/>
+      <c r="F31" s="39" t="n"/>
+      <c r="G31" s="40" t="n"/>
+      <c r="H31" s="68" t="n"/>
+      <c r="I31" s="22" t="n"/>
+      <c r="J31" s="23" t="n"/>
+      <c r="K31" s="41" t="n"/>
+      <c r="L31" s="42" t="n"/>
+    </row>
+    <row r="32" ht="18" customHeight="1" s="32">
+      <c r="B32" s="1" t="n"/>
+      <c r="C32" s="67" t="n"/>
+      <c r="D32" s="39" t="n"/>
+      <c r="E32" s="39" t="n"/>
+      <c r="F32" s="39" t="n"/>
+      <c r="G32" s="40" t="n"/>
+      <c r="H32" s="68" t="n"/>
+      <c r="I32" s="22" t="n"/>
+      <c r="J32" s="23" t="n"/>
+      <c r="K32" s="41" t="n"/>
+      <c r="L32" s="42" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1" s="32">
+      <c r="B33" s="1" t="n"/>
+      <c r="C33" s="67" t="n"/>
+      <c r="D33" s="39" t="n"/>
+      <c r="E33" s="39" t="n"/>
+      <c r="F33" s="39" t="n"/>
+      <c r="G33" s="40" t="n"/>
+      <c r="H33" s="68" t="n"/>
+      <c r="I33" s="22" t="n"/>
+      <c r="J33" s="23" t="n"/>
+      <c r="K33" s="41" t="n"/>
+      <c r="L33" s="42" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1" s="32">
+      <c r="B34" s="1" t="n"/>
+      <c r="C34" s="67" t="n"/>
+      <c r="D34" s="39" t="n"/>
+      <c r="E34" s="39" t="n"/>
+      <c r="F34" s="39" t="n"/>
+      <c r="G34" s="40" t="n"/>
+      <c r="H34" s="68" t="n"/>
+      <c r="I34" s="22" t="n"/>
+      <c r="J34" s="23" t="n"/>
+      <c r="K34" s="41" t="n"/>
+      <c r="L34" s="42" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1" s="32">
+      <c r="B35" s="1" t="n"/>
+      <c r="C35" s="38" t="n"/>
+      <c r="D35" s="39" t="n"/>
+      <c r="E35" s="39" t="n"/>
+      <c r="F35" s="39" t="n"/>
+      <c r="G35" s="40" t="n"/>
+      <c r="H35" s="68" t="n"/>
+      <c r="I35" s="22" t="n"/>
+      <c r="J35" s="23" t="n"/>
+      <c r="K35" s="41" t="n"/>
+      <c r="L35" s="42" t="n"/>
+    </row>
+    <row r="36" ht="18" customHeight="1" s="32">
+      <c r="B36" s="1" t="n"/>
+      <c r="C36" s="38" t="n"/>
+      <c r="D36" s="39" t="n"/>
+      <c r="E36" s="39" t="n"/>
+      <c r="F36" s="39" t="n"/>
+      <c r="G36" s="40" t="n"/>
+      <c r="H36" s="68" t="n"/>
+      <c r="I36" s="22" t="n"/>
+      <c r="J36" s="23" t="n"/>
+      <c r="K36" s="41" t="n"/>
+      <c r="L36" s="42" t="n"/>
+    </row>
+    <row r="37" ht="18" customHeight="1" s="32">
+      <c r="B37" s="1" t="n"/>
+      <c r="C37" s="38" t="n"/>
+      <c r="D37" s="39" t="n"/>
+      <c r="E37" s="39" t="n"/>
+      <c r="F37" s="39" t="n"/>
+      <c r="G37" s="40" t="n"/>
+      <c r="H37" s="68" t="n"/>
+      <c r="I37" s="22" t="n"/>
+      <c r="J37" s="23" t="n"/>
+      <c r="K37" s="41" t="n"/>
+      <c r="L37" s="42" t="n"/>
+    </row>
+    <row r="38" ht="18" customHeight="1" s="32">
+      <c r="B38" s="1" t="n"/>
+      <c r="C38" s="38" t="n"/>
+      <c r="D38" s="39" t="n"/>
+      <c r="E38" s="39" t="n"/>
+      <c r="F38" s="39" t="n"/>
+      <c r="G38" s="40" t="n"/>
+      <c r="H38" s="68" t="n"/>
+      <c r="I38" s="22" t="n"/>
+      <c r="J38" s="23" t="n"/>
+      <c r="K38" s="41" t="n"/>
+      <c r="L38" s="42" t="n"/>
+    </row>
+    <row r="39" ht="18" customHeight="1" s="32">
+      <c r="B39" s="1" t="n"/>
+      <c r="C39" s="38" t="n"/>
+      <c r="D39" s="39" t="n"/>
+      <c r="E39" s="39" t="n"/>
+      <c r="F39" s="39" t="n"/>
+      <c r="G39" s="40" t="n"/>
+      <c r="H39" s="68" t="n"/>
+      <c r="I39" s="22" t="n"/>
+      <c r="J39" s="23" t="n"/>
+      <c r="K39" s="41" t="n"/>
+      <c r="L39" s="42" t="n"/>
+    </row>
+    <row r="40" ht="18" customHeight="1" s="32">
+      <c r="B40" s="1" t="n"/>
+      <c r="C40" s="38" t="n"/>
+      <c r="D40" s="39" t="n"/>
+      <c r="E40" s="39" t="n"/>
+      <c r="F40" s="39" t="n"/>
+      <c r="G40" s="40" t="n"/>
+      <c r="H40" s="68" t="n"/>
+      <c r="I40" s="22" t="n"/>
+      <c r="J40" s="23" t="n"/>
+      <c r="K40" s="41" t="n"/>
+      <c r="L40" s="42" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1" s="32">
+      <c r="B41" s="1" t="n"/>
+      <c r="C41" s="38" t="n"/>
+      <c r="D41" s="39" t="n"/>
+      <c r="E41" s="39" t="n"/>
+      <c r="F41" s="39" t="n"/>
+      <c r="G41" s="40" t="n"/>
+      <c r="H41" s="68" t="n"/>
+      <c r="I41" s="22" t="n"/>
+      <c r="J41" s="23" t="n"/>
+      <c r="K41" s="41" t="n"/>
+      <c r="L41" s="42" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1" s="32">
+      <c r="B42" s="1" t="n"/>
+      <c r="C42" s="38" t="n"/>
+      <c r="D42" s="39" t="n"/>
+      <c r="E42" s="39" t="n"/>
+      <c r="F42" s="39" t="n"/>
+      <c r="G42" s="40" t="n"/>
+      <c r="H42" s="68" t="n"/>
+      <c r="I42" s="22" t="n"/>
+      <c r="J42" s="23" t="n"/>
+      <c r="K42" s="41" t="n"/>
+      <c r="L42" s="42" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1" s="32">
+      <c r="B43" s="1" t="n"/>
+      <c r="C43" s="38" t="n"/>
+      <c r="D43" s="39" t="n"/>
+      <c r="E43" s="39" t="n"/>
+      <c r="F43" s="39" t="n"/>
+      <c r="G43" s="40" t="n"/>
+      <c r="H43" s="68" t="n"/>
+      <c r="I43" s="27" t="n"/>
+      <c r="J43" s="26" t="n"/>
+      <c r="K43" s="41" t="n"/>
+      <c r="L43" s="42" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1" s="32">
+      <c r="B44" s="1" t="n"/>
+      <c r="C44" s="38" t="n"/>
+      <c r="D44" s="39" t="n"/>
+      <c r="E44" s="39" t="n"/>
+      <c r="F44" s="39" t="n"/>
+      <c r="G44" s="40" t="n"/>
+      <c r="H44" s="68" t="n"/>
+      <c r="I44" s="22" t="n"/>
+      <c r="J44" s="23" t="n"/>
+      <c r="K44" s="41" t="n"/>
+      <c r="L44" s="42" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1" s="32">
+      <c r="B45" s="1" t="n"/>
+      <c r="C45" s="38" t="n"/>
+      <c r="D45" s="39" t="n"/>
+      <c r="E45" s="39" t="n"/>
+      <c r="F45" s="39" t="n"/>
+      <c r="G45" s="40" t="n"/>
+      <c r="H45" s="68" t="n"/>
+      <c r="I45" s="22" t="n"/>
+      <c r="J45" s="23" t="n"/>
+      <c r="K45" s="41" t="n"/>
+      <c r="L45" s="42" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1" s="32">
+      <c r="B46" s="1" t="n"/>
+      <c r="C46" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合  計  </t>
+        </is>
+      </c>
+      <c r="D46" s="47" t="n"/>
+      <c r="E46" s="47" t="n"/>
+      <c r="F46" s="47" t="n"/>
+      <c r="G46" s="47" t="n"/>
+      <c r="H46" s="47" t="n"/>
+      <c r="I46" s="47" t="n"/>
+      <c r="J46" s="48" t="n"/>
+      <c r="K46" s="45">
+        <f>SUM(K5:L45)</f>
+        <v/>
+      </c>
+      <c r="L46" s="30" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="88">
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C46:J46"/>
+    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="F1:I2"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="K41:L41"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="K45:L45"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="K36:L36"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="K4:L4"/>
+  </mergeCells>
+  <pageMargins left="0.7868055555555555" right="0.5902777777777778" top="0.9840277777777777" bottom="0.9840277777777777" header="0.5111111111111111" footer="0.5111111111111111"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="90"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:L46"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.2"/>
+  <cols>
+    <col width="13" customWidth="1" style="32" min="1" max="1"/>
+    <col width="0.88671875" customWidth="1" style="32" min="2" max="2"/>
+    <col width="11.109375" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
+    <col width="6.5546875" customWidth="1" style="32" min="4" max="4"/>
+    <col width="18.77734375" customWidth="1" style="32" min="5" max="5"/>
+    <col width="8.44140625" bestFit="1" customWidth="1" style="32" min="6" max="6"/>
+    <col width="8.77734375" customWidth="1" style="32" min="7" max="7"/>
+    <col width="6.21875" customWidth="1" style="32" min="8" max="8"/>
+    <col width="5.6640625" customWidth="1" style="32" min="9" max="9"/>
+    <col width="11.77734375" customWidth="1" style="32" min="10" max="10"/>
+    <col width="8.6640625" customWidth="1" style="32" min="11" max="12"/>
+    <col width="0.88671875" customWidth="1" style="32" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" customHeight="1" s="32">
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>NO.　{{No}}</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="49" t="inlineStr">
+        <is>
+          <t>内訳明細</t>
+        </is>
+      </c>
+      <c r="J1" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P.　　　5 </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1" s="32">
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1" s="32">
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="n"/>
+      <c r="I3" s="1" t="n"/>
+      <c r="J3" s="1" t="n"/>
+      <c r="K3" s="1" t="n"/>
+      <c r="L3" s="1" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1" s="32">
+      <c r="B4" s="1" t="n"/>
+      <c r="C4" s="46" t="inlineStr">
+        <is>
+          <t>品　　　名</t>
+        </is>
+      </c>
+      <c r="D4" s="47" t="n"/>
+      <c r="E4" s="47" t="n"/>
+      <c r="F4" s="47" t="n"/>
+      <c r="G4" s="48" t="n"/>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>数　量</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>単位</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>単　価</t>
+        </is>
+      </c>
+      <c r="K4" s="29" t="inlineStr">
+        <is>
+          <t>金　　額</t>
+        </is>
+      </c>
+      <c r="L4" s="30" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1" s="32">
+      <c r="B5" s="1" t="n"/>
+      <c r="C5" s="38" t="n"/>
+      <c r="D5" s="39" t="n"/>
+      <c r="E5" s="39" t="n"/>
+      <c r="F5" s="39" t="n"/>
+      <c r="G5" s="40" t="n"/>
+      <c r="H5" s="68" t="n"/>
+      <c r="I5" s="22" t="n"/>
+      <c r="J5" s="23" t="n"/>
+      <c r="K5" s="41" t="n"/>
+      <c r="L5" s="42" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1" s="32">
+      <c r="B6" s="1" t="n"/>
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="39" t="n"/>
+      <c r="E6" s="39" t="n"/>
+      <c r="F6" s="39" t="n"/>
+      <c r="G6" s="40" t="n"/>
+      <c r="H6" s="68" t="n"/>
+      <c r="I6" s="22" t="n"/>
+      <c r="J6" s="23" t="n"/>
+      <c r="K6" s="41" t="n"/>
+      <c r="L6" s="42" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1" s="32">
+      <c r="B7" s="1" t="n"/>
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="39" t="n"/>
+      <c r="E7" s="39" t="n"/>
+      <c r="F7" s="39" t="n"/>
+      <c r="G7" s="40" t="n"/>
+      <c r="H7" s="68" t="n"/>
+      <c r="I7" s="22" t="n"/>
+      <c r="J7" s="23" t="n"/>
+      <c r="K7" s="41" t="n"/>
+      <c r="L7" s="42" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1" s="32">
+      <c r="B8" s="1" t="n"/>
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="39" t="n"/>
+      <c r="E8" s="39" t="n"/>
+      <c r="F8" s="39" t="n"/>
+      <c r="G8" s="40" t="n"/>
+      <c r="H8" s="68" t="n"/>
+      <c r="I8" s="22" t="n"/>
+      <c r="J8" s="23" t="n"/>
+      <c r="K8" s="41" t="n"/>
+      <c r="L8" s="42" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1" s="32">
+      <c r="B9" s="1" t="n"/>
+      <c r="C9" s="38" t="n"/>
+      <c r="D9" s="39" t="n"/>
+      <c r="E9" s="39" t="n"/>
+      <c r="F9" s="39" t="n"/>
+      <c r="G9" s="40" t="n"/>
+      <c r="H9" s="68" t="n"/>
+      <c r="I9" s="22" t="n"/>
+      <c r="J9" s="23" t="n"/>
+      <c r="K9" s="41" t="n"/>
+      <c r="L9" s="42" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1" s="32">
+      <c r="B10" s="1" t="n"/>
+      <c r="C10" s="38" t="n"/>
+      <c r="D10" s="39" t="n"/>
+      <c r="E10" s="39" t="n"/>
+      <c r="F10" s="39" t="n"/>
+      <c r="G10" s="40" t="n"/>
+      <c r="H10" s="68" t="n"/>
+      <c r="I10" s="22" t="n"/>
+      <c r="J10" s="23" t="n"/>
+      <c r="K10" s="41" t="n"/>
+      <c r="L10" s="42" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1" s="32">
+      <c r="B11" s="1" t="n"/>
+      <c r="C11" s="38" t="n"/>
+      <c r="D11" s="39" t="n"/>
+      <c r="E11" s="39" t="n"/>
+      <c r="F11" s="39" t="n"/>
+      <c r="G11" s="40" t="n"/>
+      <c r="H11" s="68" t="n"/>
+      <c r="I11" s="22" t="n"/>
+      <c r="J11" s="23" t="n"/>
+      <c r="K11" s="41" t="n"/>
+      <c r="L11" s="42" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1" s="32">
+      <c r="B12" s="1" t="n"/>
+      <c r="C12" s="38" t="n"/>
+      <c r="D12" s="39" t="n"/>
+      <c r="E12" s="39" t="n"/>
+      <c r="F12" s="39" t="n"/>
+      <c r="G12" s="40" t="n"/>
+      <c r="H12" s="68" t="n"/>
+      <c r="I12" s="22" t="n"/>
+      <c r="J12" s="23" t="n"/>
+      <c r="K12" s="41" t="n"/>
+      <c r="L12" s="42" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1" s="32">
+      <c r="B13" s="1" t="n"/>
+      <c r="C13" s="38" t="n"/>
+      <c r="D13" s="39" t="n"/>
+      <c r="E13" s="39" t="n"/>
+      <c r="F13" s="39" t="n"/>
+      <c r="G13" s="40" t="n"/>
+      <c r="H13" s="68" t="n"/>
+      <c r="I13" s="22" t="n"/>
+      <c r="J13" s="23" t="n"/>
+      <c r="K13" s="41" t="n"/>
+      <c r="L13" s="42" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1" s="32">
+      <c r="B14" s="1" t="n"/>
+      <c r="C14" s="38" t="n"/>
+      <c r="D14" s="39" t="n"/>
+      <c r="E14" s="39" t="n"/>
+      <c r="F14" s="39" t="n"/>
+      <c r="G14" s="40" t="n"/>
+      <c r="H14" s="68" t="n"/>
+      <c r="I14" s="22" t="n"/>
+      <c r="J14" s="23" t="n"/>
+      <c r="K14" s="41" t="n"/>
+      <c r="L14" s="42" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1" s="32">
+      <c r="B15" s="1" t="n"/>
+      <c r="C15" s="38" t="n"/>
+      <c r="D15" s="39" t="n"/>
+      <c r="E15" s="39" t="n"/>
+      <c r="F15" s="39" t="n"/>
+      <c r="G15" s="40" t="n"/>
+      <c r="H15" s="68" t="n"/>
+      <c r="I15" s="22" t="n"/>
+      <c r="J15" s="23" t="n"/>
+      <c r="K15" s="41" t="n"/>
+      <c r="L15" s="42" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1" s="32">
+      <c r="B16" s="1" t="n"/>
+      <c r="C16" s="38" t="n"/>
+      <c r="D16" s="39" t="n"/>
+      <c r="E16" s="39" t="n"/>
+      <c r="F16" s="39" t="n"/>
+      <c r="G16" s="40" t="n"/>
+      <c r="H16" s="68" t="n"/>
+      <c r="I16" s="22" t="n"/>
+      <c r="J16" s="23" t="n"/>
+      <c r="K16" s="41" t="n"/>
+      <c r="L16" s="42" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1" s="32">
+      <c r="B17" s="1" t="n"/>
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="39" t="n"/>
+      <c r="E17" s="39" t="n"/>
+      <c r="F17" s="39" t="n"/>
+      <c r="G17" s="40" t="n"/>
+      <c r="H17" s="68" t="n"/>
+      <c r="I17" s="22" t="n"/>
+      <c r="J17" s="23" t="n"/>
+      <c r="K17" s="41" t="n"/>
+      <c r="L17" s="42" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1" s="32">
+      <c r="B18" s="1" t="n"/>
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="39" t="n"/>
+      <c r="E18" s="39" t="n"/>
+      <c r="F18" s="39" t="n"/>
+      <c r="G18" s="40" t="n"/>
+      <c r="H18" s="68" t="n"/>
+      <c r="I18" s="22" t="n"/>
+      <c r="J18" s="23" t="n"/>
+      <c r="K18" s="41" t="n"/>
+      <c r="L18" s="42" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1" s="32">
+      <c r="B19" s="1" t="n"/>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="39" t="n"/>
+      <c r="E19" s="39" t="n"/>
+      <c r="F19" s="39" t="n"/>
+      <c r="G19" s="40" t="n"/>
+      <c r="H19" s="68" t="n"/>
+      <c r="I19" s="22" t="n"/>
+      <c r="J19" s="23" t="n"/>
+      <c r="K19" s="41" t="n"/>
+      <c r="L19" s="42" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1" s="32">
+      <c r="B20" s="1" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="39" t="n"/>
+      <c r="E20" s="39" t="n"/>
+      <c r="F20" s="39" t="n"/>
+      <c r="G20" s="40" t="n"/>
+      <c r="H20" s="68" t="n"/>
+      <c r="I20" s="22" t="n"/>
+      <c r="J20" s="23" t="n"/>
+      <c r="K20" s="41" t="n"/>
+      <c r="L20" s="42" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1" s="32">
+      <c r="B21" s="1" t="n"/>
+      <c r="C21" s="38" t="n"/>
+      <c r="D21" s="39" t="n"/>
+      <c r="E21" s="39" t="n"/>
+      <c r="F21" s="39" t="n"/>
+      <c r="G21" s="40" t="n"/>
+      <c r="H21" s="68" t="n"/>
+      <c r="I21" s="22" t="n"/>
+      <c r="J21" s="23" t="n"/>
+      <c r="K21" s="41" t="n"/>
+      <c r="L21" s="42" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1" s="32">
+      <c r="B22" s="1" t="n"/>
+      <c r="C22" s="38" t="n"/>
+      <c r="D22" s="39" t="n"/>
+      <c r="E22" s="39" t="n"/>
+      <c r="F22" s="39" t="n"/>
+      <c r="G22" s="40" t="n"/>
+      <c r="H22" s="68" t="n"/>
+      <c r="I22" s="22" t="n"/>
+      <c r="J22" s="23" t="n"/>
+      <c r="K22" s="41" t="n"/>
+      <c r="L22" s="42" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1" s="32">
+      <c r="B23" s="1" t="n"/>
+      <c r="C23" s="38" t="n"/>
+      <c r="D23" s="39" t="n"/>
+      <c r="E23" s="39" t="n"/>
+      <c r="F23" s="39" t="n"/>
+      <c r="G23" s="40" t="n"/>
+      <c r="H23" s="68" t="n"/>
+      <c r="I23" s="22" t="n"/>
+      <c r="J23" s="23" t="n"/>
+      <c r="K23" s="41" t="n"/>
+      <c r="L23" s="42" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1" s="32">
+      <c r="B24" s="1" t="n"/>
+      <c r="C24" s="38" t="n"/>
+      <c r="D24" s="39" t="n"/>
+      <c r="E24" s="39" t="n"/>
+      <c r="F24" s="39" t="n"/>
+      <c r="G24" s="40" t="n"/>
+      <c r="H24" s="68" t="n"/>
+      <c r="I24" s="22" t="n"/>
+      <c r="J24" s="23" t="n"/>
+      <c r="K24" s="41" t="n"/>
+      <c r="L24" s="42" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1" s="32">
+      <c r="B25" s="1" t="n"/>
+      <c r="C25" s="38" t="n"/>
+      <c r="D25" s="39" t="n"/>
+      <c r="E25" s="39" t="n"/>
+      <c r="F25" s="39" t="n"/>
+      <c r="G25" s="40" t="n"/>
+      <c r="H25" s="68" t="n"/>
+      <c r="I25" s="22" t="n"/>
+      <c r="J25" s="23" t="n"/>
+      <c r="K25" s="41" t="n"/>
+      <c r="L25" s="42" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1" s="32">
+      <c r="B26" s="1" t="n"/>
+      <c r="C26" s="38" t="n"/>
+      <c r="D26" s="39" t="n"/>
+      <c r="E26" s="39" t="n"/>
+      <c r="F26" s="39" t="n"/>
+      <c r="G26" s="40" t="n"/>
+      <c r="H26" s="68" t="n"/>
+      <c r="I26" s="22" t="n"/>
+      <c r="J26" s="23" t="n"/>
+      <c r="K26" s="41" t="n"/>
+      <c r="L26" s="42" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1" s="32">
+      <c r="B27" s="1" t="n"/>
+      <c r="C27" s="38" t="n"/>
+      <c r="D27" s="39" t="n"/>
+      <c r="E27" s="39" t="n"/>
+      <c r="F27" s="39" t="n"/>
+      <c r="G27" s="40" t="n"/>
+      <c r="H27" s="68" t="n"/>
+      <c r="I27" s="22" t="n"/>
+      <c r="J27" s="23" t="n"/>
+      <c r="K27" s="41" t="n"/>
+      <c r="L27" s="42" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1" s="32">
+      <c r="B28" s="1" t="n"/>
+      <c r="C28" s="38" t="n"/>
+      <c r="D28" s="39" t="n"/>
+      <c r="E28" s="39" t="n"/>
+      <c r="F28" s="39" t="n"/>
+      <c r="G28" s="40" t="n"/>
+      <c r="H28" s="68" t="n"/>
+      <c r="I28" s="22" t="n"/>
+      <c r="J28" s="23" t="n"/>
+      <c r="K28" s="41" t="n"/>
+      <c r="L28" s="42" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1" s="32">
+      <c r="B29" s="1" t="n"/>
+      <c r="C29" s="67" t="n"/>
+      <c r="D29" s="39" t="n"/>
+      <c r="E29" s="39" t="n"/>
+      <c r="F29" s="39" t="n"/>
+      <c r="G29" s="40" t="n"/>
+      <c r="H29" s="68" t="n"/>
+      <c r="I29" s="22" t="n"/>
+      <c r="J29" s="23" t="n"/>
+      <c r="K29" s="41" t="n"/>
+      <c r="L29" s="42" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1" s="32">
+      <c r="B30" s="1" t="n"/>
+      <c r="C30" s="67" t="n"/>
+      <c r="D30" s="39" t="n"/>
+      <c r="E30" s="39" t="n"/>
+      <c r="F30" s="39" t="n"/>
+      <c r="G30" s="40" t="n"/>
+      <c r="H30" s="68" t="n"/>
+      <c r="I30" s="22" t="n"/>
+      <c r="J30" s="23" t="n"/>
+      <c r="K30" s="41" t="n"/>
+      <c r="L30" s="42" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1" s="32">
+      <c r="B31" s="1" t="n"/>
+      <c r="C31" s="67" t="n"/>
+      <c r="D31" s="39" t="n"/>
+      <c r="E31" s="39" t="n"/>
+      <c r="F31" s="39" t="n"/>
+      <c r="G31" s="40" t="n"/>
+      <c r="H31" s="68" t="n"/>
+      <c r="I31" s="22" t="n"/>
+      <c r="J31" s="23" t="n"/>
+      <c r="K31" s="41" t="n"/>
+      <c r="L31" s="42" t="n"/>
+    </row>
+    <row r="32" ht="18" customHeight="1" s="32">
+      <c r="B32" s="1" t="n"/>
+      <c r="C32" s="67" t="n"/>
+      <c r="D32" s="39" t="n"/>
+      <c r="E32" s="39" t="n"/>
+      <c r="F32" s="39" t="n"/>
+      <c r="G32" s="40" t="n"/>
+      <c r="H32" s="68" t="n"/>
+      <c r="I32" s="22" t="n"/>
+      <c r="J32" s="23" t="n"/>
+      <c r="K32" s="41" t="n"/>
+      <c r="L32" s="42" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1" s="32">
+      <c r="B33" s="1" t="n"/>
+      <c r="C33" s="67" t="n"/>
+      <c r="D33" s="39" t="n"/>
+      <c r="E33" s="39" t="n"/>
+      <c r="F33" s="39" t="n"/>
+      <c r="G33" s="40" t="n"/>
+      <c r="H33" s="68" t="n"/>
+      <c r="I33" s="22" t="n"/>
+      <c r="J33" s="23" t="n"/>
+      <c r="K33" s="41" t="n"/>
+      <c r="L33" s="42" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1" s="32">
+      <c r="B34" s="1" t="n"/>
+      <c r="C34" s="67" t="n"/>
+      <c r="D34" s="39" t="n"/>
+      <c r="E34" s="39" t="n"/>
+      <c r="F34" s="39" t="n"/>
+      <c r="G34" s="40" t="n"/>
+      <c r="H34" s="68" t="n"/>
+      <c r="I34" s="22" t="n"/>
+      <c r="J34" s="23" t="n"/>
+      <c r="K34" s="41" t="n"/>
+      <c r="L34" s="42" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1" s="32">
+      <c r="B35" s="1" t="n"/>
+      <c r="C35" s="38" t="n"/>
+      <c r="D35" s="39" t="n"/>
+      <c r="E35" s="39" t="n"/>
+      <c r="F35" s="39" t="n"/>
+      <c r="G35" s="40" t="n"/>
+      <c r="H35" s="68" t="n"/>
+      <c r="I35" s="22" t="n"/>
+      <c r="J35" s="23" t="n"/>
+      <c r="K35" s="41" t="n"/>
+      <c r="L35" s="42" t="n"/>
+    </row>
+    <row r="36" ht="18" customHeight="1" s="32">
+      <c r="B36" s="1" t="n"/>
+      <c r="C36" s="38" t="n"/>
+      <c r="D36" s="39" t="n"/>
+      <c r="E36" s="39" t="n"/>
+      <c r="F36" s="39" t="n"/>
+      <c r="G36" s="40" t="n"/>
+      <c r="H36" s="68" t="n"/>
+      <c r="I36" s="22" t="n"/>
+      <c r="J36" s="23" t="n"/>
+      <c r="K36" s="41" t="n"/>
+      <c r="L36" s="42" t="n"/>
+    </row>
+    <row r="37" ht="18" customHeight="1" s="32">
+      <c r="B37" s="1" t="n"/>
+      <c r="C37" s="38" t="n"/>
+      <c r="D37" s="39" t="n"/>
+      <c r="E37" s="39" t="n"/>
+      <c r="F37" s="39" t="n"/>
+      <c r="G37" s="40" t="n"/>
+      <c r="H37" s="68" t="n"/>
+      <c r="I37" s="22" t="n"/>
+      <c r="J37" s="23" t="n"/>
+      <c r="K37" s="41" t="n"/>
+      <c r="L37" s="42" t="n"/>
+    </row>
+    <row r="38" ht="18" customHeight="1" s="32">
+      <c r="B38" s="1" t="n"/>
+      <c r="C38" s="38" t="n"/>
+      <c r="D38" s="39" t="n"/>
+      <c r="E38" s="39" t="n"/>
+      <c r="F38" s="39" t="n"/>
+      <c r="G38" s="40" t="n"/>
+      <c r="H38" s="68" t="n"/>
+      <c r="I38" s="22" t="n"/>
+      <c r="J38" s="23" t="n"/>
+      <c r="K38" s="41" t="n"/>
+      <c r="L38" s="42" t="n"/>
+    </row>
+    <row r="39" ht="18" customHeight="1" s="32">
+      <c r="B39" s="1" t="n"/>
+      <c r="C39" s="38" t="n"/>
+      <c r="D39" s="39" t="n"/>
+      <c r="E39" s="39" t="n"/>
+      <c r="F39" s="39" t="n"/>
+      <c r="G39" s="40" t="n"/>
+      <c r="H39" s="68" t="n"/>
+      <c r="I39" s="22" t="n"/>
+      <c r="J39" s="23" t="n"/>
+      <c r="K39" s="41" t="n"/>
+      <c r="L39" s="42" t="n"/>
+    </row>
+    <row r="40" ht="18" customHeight="1" s="32">
+      <c r="B40" s="1" t="n"/>
+      <c r="C40" s="38" t="n"/>
+      <c r="D40" s="39" t="n"/>
+      <c r="E40" s="39" t="n"/>
+      <c r="F40" s="39" t="n"/>
+      <c r="G40" s="40" t="n"/>
+      <c r="H40" s="68" t="n"/>
+      <c r="I40" s="22" t="n"/>
+      <c r="J40" s="23" t="n"/>
+      <c r="K40" s="41" t="n"/>
+      <c r="L40" s="42" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1" s="32">
+      <c r="B41" s="1" t="n"/>
+      <c r="C41" s="38" t="n"/>
+      <c r="D41" s="39" t="n"/>
+      <c r="E41" s="39" t="n"/>
+      <c r="F41" s="39" t="n"/>
+      <c r="G41" s="40" t="n"/>
+      <c r="H41" s="68" t="n"/>
+      <c r="I41" s="22" t="n"/>
+      <c r="J41" s="23" t="n"/>
+      <c r="K41" s="41" t="n"/>
+      <c r="L41" s="42" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1" s="32">
+      <c r="B42" s="1" t="n"/>
+      <c r="C42" s="38" t="n"/>
+      <c r="D42" s="39" t="n"/>
+      <c r="E42" s="39" t="n"/>
+      <c r="F42" s="39" t="n"/>
+      <c r="G42" s="40" t="n"/>
+      <c r="H42" s="68" t="n"/>
+      <c r="I42" s="22" t="n"/>
+      <c r="J42" s="23" t="n"/>
+      <c r="K42" s="41" t="n"/>
+      <c r="L42" s="42" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1" s="32">
+      <c r="B43" s="1" t="n"/>
+      <c r="C43" s="38" t="n"/>
+      <c r="D43" s="39" t="n"/>
+      <c r="E43" s="39" t="n"/>
+      <c r="F43" s="39" t="n"/>
+      <c r="G43" s="40" t="n"/>
+      <c r="H43" s="68" t="n"/>
+      <c r="I43" s="27" t="n"/>
+      <c r="J43" s="26" t="n"/>
+      <c r="K43" s="41" t="n"/>
+      <c r="L43" s="42" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1" s="32">
+      <c r="B44" s="1" t="n"/>
+      <c r="C44" s="38" t="n"/>
+      <c r="D44" s="39" t="n"/>
+      <c r="E44" s="39" t="n"/>
+      <c r="F44" s="39" t="n"/>
+      <c r="G44" s="40" t="n"/>
+      <c r="H44" s="68" t="n"/>
+      <c r="I44" s="22" t="n"/>
+      <c r="J44" s="23" t="n"/>
+      <c r="K44" s="41" t="n"/>
+      <c r="L44" s="42" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1" s="32">
+      <c r="B45" s="1" t="n"/>
+      <c r="C45" s="38" t="n"/>
+      <c r="D45" s="39" t="n"/>
+      <c r="E45" s="39" t="n"/>
+      <c r="F45" s="39" t="n"/>
+      <c r="G45" s="40" t="n"/>
+      <c r="H45" s="68" t="n"/>
+      <c r="I45" s="22" t="n"/>
+      <c r="J45" s="23" t="n"/>
+      <c r="K45" s="41" t="n"/>
+      <c r="L45" s="42" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1" s="32">
+      <c r="B46" s="1" t="n"/>
+      <c r="C46" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合  計  </t>
+        </is>
+      </c>
+      <c r="D46" s="47" t="n"/>
+      <c r="E46" s="47" t="n"/>
+      <c r="F46" s="47" t="n"/>
+      <c r="G46" s="47" t="n"/>
+      <c r="H46" s="47" t="n"/>
+      <c r="I46" s="47" t="n"/>
+      <c r="J46" s="48" t="n"/>
+      <c r="K46" s="45">
+        <f>SUM(K5:L45)</f>
+        <v/>
+      </c>
+      <c r="L46" s="30" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="88">
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C46:J46"/>
+    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="F1:I2"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="K41:L41"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="K45:L45"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="K36:L36"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="K4:L4"/>
+  </mergeCells>
+  <pageMargins left="0.7868055555555555" right="0.5902777777777778" top="0.9840277777777777" bottom="0.9840277777777777" header="0.5111111111111111" footer="0.5111111111111111"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="90"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:L46"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.2"/>
+  <cols>
+    <col width="13" customWidth="1" style="32" min="1" max="1"/>
+    <col width="0.88671875" customWidth="1" style="32" min="2" max="2"/>
+    <col width="11.109375" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
+    <col width="6.5546875" customWidth="1" style="32" min="4" max="4"/>
+    <col width="18.77734375" customWidth="1" style="32" min="5" max="5"/>
+    <col width="8.44140625" bestFit="1" customWidth="1" style="32" min="6" max="6"/>
+    <col width="8.77734375" customWidth="1" style="32" min="7" max="7"/>
+    <col width="6.21875" customWidth="1" style="32" min="8" max="8"/>
+    <col width="5.6640625" customWidth="1" style="32" min="9" max="9"/>
+    <col width="11.77734375" customWidth="1" style="32" min="10" max="10"/>
+    <col width="8.6640625" customWidth="1" style="32" min="11" max="12"/>
+    <col width="0.88671875" customWidth="1" style="32" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" customHeight="1" s="32">
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>NO.　{{No}}</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="49" t="inlineStr">
+        <is>
+          <t>内訳明細</t>
+        </is>
+      </c>
+      <c r="J1" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P.　　　6 </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1" s="32">
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1" s="32">
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="n"/>
+      <c r="I3" s="1" t="n"/>
+      <c r="J3" s="1" t="n"/>
+      <c r="K3" s="1" t="n"/>
+      <c r="L3" s="1" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1" s="32">
+      <c r="B4" s="1" t="n"/>
+      <c r="C4" s="46" t="inlineStr">
+        <is>
+          <t>品　　　名</t>
+        </is>
+      </c>
+      <c r="D4" s="47" t="n"/>
+      <c r="E4" s="47" t="n"/>
+      <c r="F4" s="47" t="n"/>
+      <c r="G4" s="48" t="n"/>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>数　量</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>単位</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>単　価</t>
+        </is>
+      </c>
+      <c r="K4" s="29" t="inlineStr">
+        <is>
+          <t>金　　額</t>
+        </is>
+      </c>
+      <c r="L4" s="30" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1" s="32">
+      <c r="B5" s="1" t="n"/>
+      <c r="C5" s="38" t="n"/>
+      <c r="D5" s="39" t="n"/>
+      <c r="E5" s="39" t="n"/>
+      <c r="F5" s="39" t="n"/>
+      <c r="G5" s="40" t="n"/>
+      <c r="H5" s="68" t="n"/>
+      <c r="I5" s="22" t="n"/>
+      <c r="J5" s="23" t="n"/>
+      <c r="K5" s="41" t="n"/>
+      <c r="L5" s="42" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1" s="32">
+      <c r="B6" s="1" t="n"/>
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="39" t="n"/>
+      <c r="E6" s="39" t="n"/>
+      <c r="F6" s="39" t="n"/>
+      <c r="G6" s="40" t="n"/>
+      <c r="H6" s="68" t="n"/>
+      <c r="I6" s="22" t="n"/>
+      <c r="J6" s="23" t="n"/>
+      <c r="K6" s="41" t="n"/>
+      <c r="L6" s="42" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1" s="32">
+      <c r="B7" s="1" t="n"/>
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="39" t="n"/>
+      <c r="E7" s="39" t="n"/>
+      <c r="F7" s="39" t="n"/>
+      <c r="G7" s="40" t="n"/>
+      <c r="H7" s="68" t="n"/>
+      <c r="I7" s="22" t="n"/>
+      <c r="J7" s="23" t="n"/>
+      <c r="K7" s="41" t="n"/>
+      <c r="L7" s="42" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1" s="32">
+      <c r="B8" s="1" t="n"/>
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="39" t="n"/>
+      <c r="E8" s="39" t="n"/>
+      <c r="F8" s="39" t="n"/>
+      <c r="G8" s="40" t="n"/>
+      <c r="H8" s="68" t="n"/>
+      <c r="I8" s="22" t="n"/>
+      <c r="J8" s="23" t="n"/>
+      <c r="K8" s="41" t="n"/>
+      <c r="L8" s="42" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1" s="32">
+      <c r="B9" s="1" t="n"/>
+      <c r="C9" s="38" t="n"/>
+      <c r="D9" s="39" t="n"/>
+      <c r="E9" s="39" t="n"/>
+      <c r="F9" s="39" t="n"/>
+      <c r="G9" s="40" t="n"/>
+      <c r="H9" s="68" t="n"/>
+      <c r="I9" s="22" t="n"/>
+      <c r="J9" s="23" t="n"/>
+      <c r="K9" s="41" t="n"/>
+      <c r="L9" s="42" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1" s="32">
+      <c r="B10" s="1" t="n"/>
+      <c r="C10" s="38" t="n"/>
+      <c r="D10" s="39" t="n"/>
+      <c r="E10" s="39" t="n"/>
+      <c r="F10" s="39" t="n"/>
+      <c r="G10" s="40" t="n"/>
+      <c r="H10" s="68" t="n"/>
+      <c r="I10" s="22" t="n"/>
+      <c r="J10" s="23" t="n"/>
+      <c r="K10" s="41" t="n"/>
+      <c r="L10" s="42" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1" s="32">
+      <c r="B11" s="1" t="n"/>
+      <c r="C11" s="38" t="n"/>
+      <c r="D11" s="39" t="n"/>
+      <c r="E11" s="39" t="n"/>
+      <c r="F11" s="39" t="n"/>
+      <c r="G11" s="40" t="n"/>
+      <c r="H11" s="68" t="n"/>
+      <c r="I11" s="22" t="n"/>
+      <c r="J11" s="23" t="n"/>
+      <c r="K11" s="41" t="n"/>
+      <c r="L11" s="42" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1" s="32">
+      <c r="B12" s="1" t="n"/>
+      <c r="C12" s="38" t="n"/>
+      <c r="D12" s="39" t="n"/>
+      <c r="E12" s="39" t="n"/>
+      <c r="F12" s="39" t="n"/>
+      <c r="G12" s="40" t="n"/>
+      <c r="H12" s="68" t="n"/>
+      <c r="I12" s="22" t="n"/>
+      <c r="J12" s="23" t="n"/>
+      <c r="K12" s="41" t="n"/>
+      <c r="L12" s="42" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1" s="32">
+      <c r="B13" s="1" t="n"/>
+      <c r="C13" s="38" t="n"/>
+      <c r="D13" s="39" t="n"/>
+      <c r="E13" s="39" t="n"/>
+      <c r="F13" s="39" t="n"/>
+      <c r="G13" s="40" t="n"/>
+      <c r="H13" s="68" t="n"/>
+      <c r="I13" s="22" t="n"/>
+      <c r="J13" s="23" t="n"/>
+      <c r="K13" s="41" t="n"/>
+      <c r="L13" s="42" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1" s="32">
+      <c r="B14" s="1" t="n"/>
+      <c r="C14" s="38" t="n"/>
+      <c r="D14" s="39" t="n"/>
+      <c r="E14" s="39" t="n"/>
+      <c r="F14" s="39" t="n"/>
+      <c r="G14" s="40" t="n"/>
+      <c r="H14" s="68" t="n"/>
+      <c r="I14" s="22" t="n"/>
+      <c r="J14" s="23" t="n"/>
+      <c r="K14" s="41" t="n"/>
+      <c r="L14" s="42" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1" s="32">
+      <c r="B15" s="1" t="n"/>
+      <c r="C15" s="38" t="n"/>
+      <c r="D15" s="39" t="n"/>
+      <c r="E15" s="39" t="n"/>
+      <c r="F15" s="39" t="n"/>
+      <c r="G15" s="40" t="n"/>
+      <c r="H15" s="68" t="n"/>
+      <c r="I15" s="22" t="n"/>
+      <c r="J15" s="23" t="n"/>
+      <c r="K15" s="41" t="n"/>
+      <c r="L15" s="42" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1" s="32">
+      <c r="B16" s="1" t="n"/>
+      <c r="C16" s="38" t="n"/>
+      <c r="D16" s="39" t="n"/>
+      <c r="E16" s="39" t="n"/>
+      <c r="F16" s="39" t="n"/>
+      <c r="G16" s="40" t="n"/>
+      <c r="H16" s="68" t="n"/>
+      <c r="I16" s="22" t="n"/>
+      <c r="J16" s="23" t="n"/>
+      <c r="K16" s="41" t="n"/>
+      <c r="L16" s="42" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1" s="32">
+      <c r="B17" s="1" t="n"/>
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="39" t="n"/>
+      <c r="E17" s="39" t="n"/>
+      <c r="F17" s="39" t="n"/>
+      <c r="G17" s="40" t="n"/>
+      <c r="H17" s="68" t="n"/>
+      <c r="I17" s="22" t="n"/>
+      <c r="J17" s="23" t="n"/>
+      <c r="K17" s="41" t="n"/>
+      <c r="L17" s="42" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1" s="32">
+      <c r="B18" s="1" t="n"/>
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="39" t="n"/>
+      <c r="E18" s="39" t="n"/>
+      <c r="F18" s="39" t="n"/>
+      <c r="G18" s="40" t="n"/>
+      <c r="H18" s="68" t="n"/>
+      <c r="I18" s="22" t="n"/>
+      <c r="J18" s="23" t="n"/>
+      <c r="K18" s="41" t="n"/>
+      <c r="L18" s="42" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1" s="32">
+      <c r="B19" s="1" t="n"/>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="39" t="n"/>
+      <c r="E19" s="39" t="n"/>
+      <c r="F19" s="39" t="n"/>
+      <c r="G19" s="40" t="n"/>
+      <c r="H19" s="68" t="n"/>
+      <c r="I19" s="22" t="n"/>
+      <c r="J19" s="23" t="n"/>
+      <c r="K19" s="41" t="n"/>
+      <c r="L19" s="42" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1" s="32">
+      <c r="B20" s="1" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="39" t="n"/>
+      <c r="E20" s="39" t="n"/>
+      <c r="F20" s="39" t="n"/>
+      <c r="G20" s="40" t="n"/>
+      <c r="H20" s="68" t="n"/>
+      <c r="I20" s="22" t="n"/>
+      <c r="J20" s="23" t="n"/>
+      <c r="K20" s="41" t="n"/>
+      <c r="L20" s="42" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1" s="32">
+      <c r="B21" s="1" t="n"/>
+      <c r="C21" s="38" t="n"/>
+      <c r="D21" s="39" t="n"/>
+      <c r="E21" s="39" t="n"/>
+      <c r="F21" s="39" t="n"/>
+      <c r="G21" s="40" t="n"/>
+      <c r="H21" s="68" t="n"/>
+      <c r="I21" s="22" t="n"/>
+      <c r="J21" s="23" t="n"/>
+      <c r="K21" s="41" t="n"/>
+      <c r="L21" s="42" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1" s="32">
+      <c r="B22" s="1" t="n"/>
+      <c r="C22" s="38" t="n"/>
+      <c r="D22" s="39" t="n"/>
+      <c r="E22" s="39" t="n"/>
+      <c r="F22" s="39" t="n"/>
+      <c r="G22" s="40" t="n"/>
+      <c r="H22" s="68" t="n"/>
+      <c r="I22" s="22" t="n"/>
+      <c r="J22" s="23" t="n"/>
+      <c r="K22" s="41" t="n"/>
+      <c r="L22" s="42" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1" s="32">
+      <c r="B23" s="1" t="n"/>
+      <c r="C23" s="38" t="n"/>
+      <c r="D23" s="39" t="n"/>
+      <c r="E23" s="39" t="n"/>
+      <c r="F23" s="39" t="n"/>
+      <c r="G23" s="40" t="n"/>
+      <c r="H23" s="68" t="n"/>
+      <c r="I23" s="22" t="n"/>
+      <c r="J23" s="23" t="n"/>
+      <c r="K23" s="41" t="n"/>
+      <c r="L23" s="42" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1" s="32">
+      <c r="B24" s="1" t="n"/>
+      <c r="C24" s="38" t="n"/>
+      <c r="D24" s="39" t="n"/>
+      <c r="E24" s="39" t="n"/>
+      <c r="F24" s="39" t="n"/>
+      <c r="G24" s="40" t="n"/>
+      <c r="H24" s="68" t="n"/>
+      <c r="I24" s="22" t="n"/>
+      <c r="J24" s="23" t="n"/>
+      <c r="K24" s="41" t="n"/>
+      <c r="L24" s="42" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1" s="32">
+      <c r="B25" s="1" t="n"/>
+      <c r="C25" s="38" t="n"/>
+      <c r="D25" s="39" t="n"/>
+      <c r="E25" s="39" t="n"/>
+      <c r="F25" s="39" t="n"/>
+      <c r="G25" s="40" t="n"/>
+      <c r="H25" s="68" t="n"/>
+      <c r="I25" s="22" t="n"/>
+      <c r="J25" s="23" t="n"/>
+      <c r="K25" s="41" t="n"/>
+      <c r="L25" s="42" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1" s="32">
+      <c r="B26" s="1" t="n"/>
+      <c r="C26" s="38" t="n"/>
+      <c r="D26" s="39" t="n"/>
+      <c r="E26" s="39" t="n"/>
+      <c r="F26" s="39" t="n"/>
+      <c r="G26" s="40" t="n"/>
+      <c r="H26" s="68" t="n"/>
+      <c r="I26" s="22" t="n"/>
+      <c r="J26" s="23" t="n"/>
+      <c r="K26" s="41" t="n"/>
+      <c r="L26" s="42" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1" s="32">
+      <c r="B27" s="1" t="n"/>
+      <c r="C27" s="38" t="n"/>
+      <c r="D27" s="39" t="n"/>
+      <c r="E27" s="39" t="n"/>
+      <c r="F27" s="39" t="n"/>
+      <c r="G27" s="40" t="n"/>
+      <c r="H27" s="68" t="n"/>
+      <c r="I27" s="22" t="n"/>
+      <c r="J27" s="23" t="n"/>
+      <c r="K27" s="41" t="n"/>
+      <c r="L27" s="42" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1" s="32">
+      <c r="B28" s="1" t="n"/>
+      <c r="C28" s="38" t="n"/>
+      <c r="D28" s="39" t="n"/>
+      <c r="E28" s="39" t="n"/>
+      <c r="F28" s="39" t="n"/>
+      <c r="G28" s="40" t="n"/>
+      <c r="H28" s="68" t="n"/>
+      <c r="I28" s="22" t="n"/>
+      <c r="J28" s="23" t="n"/>
+      <c r="K28" s="41" t="n"/>
+      <c r="L28" s="42" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1" s="32">
+      <c r="B29" s="1" t="n"/>
+      <c r="C29" s="67" t="n"/>
+      <c r="D29" s="39" t="n"/>
+      <c r="E29" s="39" t="n"/>
+      <c r="F29" s="39" t="n"/>
+      <c r="G29" s="40" t="n"/>
+      <c r="H29" s="68" t="n"/>
+      <c r="I29" s="22" t="n"/>
+      <c r="J29" s="23" t="n"/>
+      <c r="K29" s="41" t="n"/>
+      <c r="L29" s="42" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1" s="32">
+      <c r="B30" s="1" t="n"/>
+      <c r="C30" s="67" t="n"/>
+      <c r="D30" s="39" t="n"/>
+      <c r="E30" s="39" t="n"/>
+      <c r="F30" s="39" t="n"/>
+      <c r="G30" s="40" t="n"/>
+      <c r="H30" s="68" t="n"/>
+      <c r="I30" s="22" t="n"/>
+      <c r="J30" s="23" t="n"/>
+      <c r="K30" s="41" t="n"/>
+      <c r="L30" s="42" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1" s="32">
+      <c r="B31" s="1" t="n"/>
+      <c r="C31" s="67" t="n"/>
+      <c r="D31" s="39" t="n"/>
+      <c r="E31" s="39" t="n"/>
+      <c r="F31" s="39" t="n"/>
+      <c r="G31" s="40" t="n"/>
+      <c r="H31" s="68" t="n"/>
+      <c r="I31" s="22" t="n"/>
+      <c r="J31" s="23" t="n"/>
+      <c r="K31" s="41" t="n"/>
+      <c r="L31" s="42" t="n"/>
+    </row>
+    <row r="32" ht="18" customHeight="1" s="32">
+      <c r="B32" s="1" t="n"/>
+      <c r="C32" s="67" t="n"/>
+      <c r="D32" s="39" t="n"/>
+      <c r="E32" s="39" t="n"/>
+      <c r="F32" s="39" t="n"/>
+      <c r="G32" s="40" t="n"/>
+      <c r="H32" s="68" t="n"/>
+      <c r="I32" s="22" t="n"/>
+      <c r="J32" s="23" t="n"/>
+      <c r="K32" s="41" t="n"/>
+      <c r="L32" s="42" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1" s="32">
+      <c r="B33" s="1" t="n"/>
+      <c r="C33" s="67" t="n"/>
+      <c r="D33" s="39" t="n"/>
+      <c r="E33" s="39" t="n"/>
+      <c r="F33" s="39" t="n"/>
+      <c r="G33" s="40" t="n"/>
+      <c r="H33" s="68" t="n"/>
+      <c r="I33" s="22" t="n"/>
+      <c r="J33" s="23" t="n"/>
+      <c r="K33" s="41" t="n"/>
+      <c r="L33" s="42" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1" s="32">
+      <c r="B34" s="1" t="n"/>
+      <c r="C34" s="67" t="n"/>
+      <c r="D34" s="39" t="n"/>
+      <c r="E34" s="39" t="n"/>
+      <c r="F34" s="39" t="n"/>
+      <c r="G34" s="40" t="n"/>
+      <c r="H34" s="68" t="n"/>
+      <c r="I34" s="22" t="n"/>
+      <c r="J34" s="23" t="n"/>
+      <c r="K34" s="41" t="n"/>
+      <c r="L34" s="42" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1" s="32">
+      <c r="B35" s="1" t="n"/>
+      <c r="C35" s="38" t="n"/>
+      <c r="D35" s="39" t="n"/>
+      <c r="E35" s="39" t="n"/>
+      <c r="F35" s="39" t="n"/>
+      <c r="G35" s="40" t="n"/>
+      <c r="H35" s="68" t="n"/>
+      <c r="I35" s="22" t="n"/>
+      <c r="J35" s="23" t="n"/>
+      <c r="K35" s="41" t="n"/>
+      <c r="L35" s="42" t="n"/>
+    </row>
+    <row r="36" ht="18" customHeight="1" s="32">
+      <c r="B36" s="1" t="n"/>
+      <c r="C36" s="38" t="n"/>
+      <c r="D36" s="39" t="n"/>
+      <c r="E36" s="39" t="n"/>
+      <c r="F36" s="39" t="n"/>
+      <c r="G36" s="40" t="n"/>
+      <c r="H36" s="68" t="n"/>
+      <c r="I36" s="22" t="n"/>
+      <c r="J36" s="23" t="n"/>
+      <c r="K36" s="41" t="n"/>
+      <c r="L36" s="42" t="n"/>
+    </row>
+    <row r="37" ht="18" customHeight="1" s="32">
+      <c r="B37" s="1" t="n"/>
+      <c r="C37" s="38" t="n"/>
+      <c r="D37" s="39" t="n"/>
+      <c r="E37" s="39" t="n"/>
+      <c r="F37" s="39" t="n"/>
+      <c r="G37" s="40" t="n"/>
+      <c r="H37" s="68" t="n"/>
+      <c r="I37" s="22" t="n"/>
+      <c r="J37" s="23" t="n"/>
+      <c r="K37" s="41" t="n"/>
+      <c r="L37" s="42" t="n"/>
+    </row>
+    <row r="38" ht="18" customHeight="1" s="32">
+      <c r="B38" s="1" t="n"/>
+      <c r="C38" s="38" t="n"/>
+      <c r="D38" s="39" t="n"/>
+      <c r="E38" s="39" t="n"/>
+      <c r="F38" s="39" t="n"/>
+      <c r="G38" s="40" t="n"/>
+      <c r="H38" s="68" t="n"/>
+      <c r="I38" s="22" t="n"/>
+      <c r="J38" s="23" t="n"/>
+      <c r="K38" s="41" t="n"/>
+      <c r="L38" s="42" t="n"/>
+    </row>
+    <row r="39" ht="18" customHeight="1" s="32">
+      <c r="B39" s="1" t="n"/>
+      <c r="C39" s="38" t="n"/>
+      <c r="D39" s="39" t="n"/>
+      <c r="E39" s="39" t="n"/>
+      <c r="F39" s="39" t="n"/>
+      <c r="G39" s="40" t="n"/>
+      <c r="H39" s="68" t="n"/>
+      <c r="I39" s="22" t="n"/>
+      <c r="J39" s="23" t="n"/>
+      <c r="K39" s="41" t="n"/>
+      <c r="L39" s="42" t="n"/>
+    </row>
+    <row r="40" ht="18" customHeight="1" s="32">
+      <c r="B40" s="1" t="n"/>
+      <c r="C40" s="38" t="n"/>
+      <c r="D40" s="39" t="n"/>
+      <c r="E40" s="39" t="n"/>
+      <c r="F40" s="39" t="n"/>
+      <c r="G40" s="40" t="n"/>
+      <c r="H40" s="68" t="n"/>
+      <c r="I40" s="22" t="n"/>
+      <c r="J40" s="23" t="n"/>
+      <c r="K40" s="41" t="n"/>
+      <c r="L40" s="42" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1" s="32">
+      <c r="B41" s="1" t="n"/>
+      <c r="C41" s="38" t="n"/>
+      <c r="D41" s="39" t="n"/>
+      <c r="E41" s="39" t="n"/>
+      <c r="F41" s="39" t="n"/>
+      <c r="G41" s="40" t="n"/>
+      <c r="H41" s="68" t="n"/>
+      <c r="I41" s="22" t="n"/>
+      <c r="J41" s="23" t="n"/>
+      <c r="K41" s="41" t="n"/>
+      <c r="L41" s="42" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1" s="32">
+      <c r="B42" s="1" t="n"/>
+      <c r="C42" s="38" t="n"/>
+      <c r="D42" s="39" t="n"/>
+      <c r="E42" s="39" t="n"/>
+      <c r="F42" s="39" t="n"/>
+      <c r="G42" s="40" t="n"/>
+      <c r="H42" s="68" t="n"/>
+      <c r="I42" s="22" t="n"/>
+      <c r="J42" s="23" t="n"/>
+      <c r="K42" s="41" t="n"/>
+      <c r="L42" s="42" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1" s="32">
+      <c r="B43" s="1" t="n"/>
+      <c r="C43" s="38" t="n"/>
+      <c r="D43" s="39" t="n"/>
+      <c r="E43" s="39" t="n"/>
+      <c r="F43" s="39" t="n"/>
+      <c r="G43" s="40" t="n"/>
+      <c r="H43" s="68" t="n"/>
+      <c r="I43" s="27" t="n"/>
+      <c r="J43" s="26" t="n"/>
+      <c r="K43" s="41" t="n"/>
+      <c r="L43" s="42" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1" s="32">
+      <c r="B44" s="1" t="n"/>
+      <c r="C44" s="38" t="n"/>
+      <c r="D44" s="39" t="n"/>
+      <c r="E44" s="39" t="n"/>
+      <c r="F44" s="39" t="n"/>
+      <c r="G44" s="40" t="n"/>
+      <c r="H44" s="68" t="n"/>
+      <c r="I44" s="22" t="n"/>
+      <c r="J44" s="23" t="n"/>
+      <c r="K44" s="41" t="n"/>
+      <c r="L44" s="42" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1" s="32">
+      <c r="B45" s="1" t="n"/>
+      <c r="C45" s="38" t="n"/>
+      <c r="D45" s="39" t="n"/>
+      <c r="E45" s="39" t="n"/>
+      <c r="F45" s="39" t="n"/>
+      <c r="G45" s="40" t="n"/>
+      <c r="H45" s="68" t="n"/>
+      <c r="I45" s="22" t="n"/>
+      <c r="J45" s="23" t="n"/>
+      <c r="K45" s="41" t="n"/>
+      <c r="L45" s="42" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1" s="32">
+      <c r="B46" s="1" t="n"/>
+      <c r="C46" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合  計  </t>
+        </is>
+      </c>
+      <c r="D46" s="47" t="n"/>
+      <c r="E46" s="47" t="n"/>
+      <c r="F46" s="47" t="n"/>
+      <c r="G46" s="47" t="n"/>
+      <c r="H46" s="47" t="n"/>
+      <c r="I46" s="47" t="n"/>
+      <c r="J46" s="48" t="n"/>
+      <c r="K46" s="45">
+        <f>SUM(K5:L45)</f>
+        <v/>
+      </c>
+      <c r="L46" s="30" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="88">
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C46:J46"/>
+    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="F1:I2"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="K41:L41"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="K45:L45"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="K36:L36"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="K4:L4"/>
+  </mergeCells>
+  <pageMargins left="0.7868055555555555" right="0.5902777777777778" top="0.9840277777777777" bottom="0.9840277777777777" header="0.5111111111111111" footer="0.5111111111111111"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="90"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:L46"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.2"/>
+  <cols>
+    <col width="13" customWidth="1" style="32" min="1" max="1"/>
+    <col width="0.88671875" customWidth="1" style="32" min="2" max="2"/>
+    <col width="11.109375" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
+    <col width="6.5546875" customWidth="1" style="32" min="4" max="4"/>
+    <col width="18.77734375" customWidth="1" style="32" min="5" max="5"/>
+    <col width="8.44140625" bestFit="1" customWidth="1" style="32" min="6" max="6"/>
+    <col width="8.77734375" customWidth="1" style="32" min="7" max="7"/>
+    <col width="6.21875" customWidth="1" style="32" min="8" max="8"/>
+    <col width="5.6640625" customWidth="1" style="32" min="9" max="9"/>
+    <col width="11.77734375" customWidth="1" style="32" min="10" max="10"/>
+    <col width="8.6640625" customWidth="1" style="32" min="11" max="12"/>
+    <col width="0.88671875" customWidth="1" style="32" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" customHeight="1" s="32">
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>NO.　{{No}}</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="49" t="inlineStr">
+        <is>
+          <t>内訳明細</t>
+        </is>
+      </c>
+      <c r="J1" s="61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P.　　　7 </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1" s="32">
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1" s="32">
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="n"/>
+      <c r="I3" s="1" t="n"/>
+      <c r="J3" s="1" t="n"/>
+      <c r="K3" s="1" t="n"/>
+      <c r="L3" s="1" t="n"/>
+    </row>
+    <row r="4" ht="18" customHeight="1" s="32">
+      <c r="B4" s="1" t="n"/>
+      <c r="C4" s="46" t="inlineStr">
+        <is>
+          <t>品　　　名</t>
+        </is>
+      </c>
+      <c r="D4" s="47" t="n"/>
+      <c r="E4" s="47" t="n"/>
+      <c r="F4" s="47" t="n"/>
+      <c r="G4" s="48" t="n"/>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>数　量</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>単位</t>
+        </is>
+      </c>
+      <c r="J4" s="12" t="inlineStr">
+        <is>
+          <t>単　価</t>
+        </is>
+      </c>
+      <c r="K4" s="29" t="inlineStr">
+        <is>
+          <t>金　　額</t>
+        </is>
+      </c>
+      <c r="L4" s="30" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1" s="32">
+      <c r="B5" s="1" t="n"/>
+      <c r="C5" s="38" t="n"/>
+      <c r="D5" s="39" t="n"/>
+      <c r="E5" s="39" t="n"/>
+      <c r="F5" s="39" t="n"/>
+      <c r="G5" s="40" t="n"/>
+      <c r="H5" s="68" t="n"/>
+      <c r="I5" s="22" t="n"/>
+      <c r="J5" s="23" t="n"/>
+      <c r="K5" s="41" t="n"/>
+      <c r="L5" s="42" t="n"/>
+    </row>
+    <row r="6" ht="18" customHeight="1" s="32">
+      <c r="B6" s="1" t="n"/>
+      <c r="C6" s="38" t="n"/>
+      <c r="D6" s="39" t="n"/>
+      <c r="E6" s="39" t="n"/>
+      <c r="F6" s="39" t="n"/>
+      <c r="G6" s="40" t="n"/>
+      <c r="H6" s="68" t="n"/>
+      <c r="I6" s="22" t="n"/>
+      <c r="J6" s="23" t="n"/>
+      <c r="K6" s="41" t="n"/>
+      <c r="L6" s="42" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1" s="32">
+      <c r="B7" s="1" t="n"/>
+      <c r="C7" s="38" t="n"/>
+      <c r="D7" s="39" t="n"/>
+      <c r="E7" s="39" t="n"/>
+      <c r="F7" s="39" t="n"/>
+      <c r="G7" s="40" t="n"/>
+      <c r="H7" s="68" t="n"/>
+      <c r="I7" s="22" t="n"/>
+      <c r="J7" s="23" t="n"/>
+      <c r="K7" s="41" t="n"/>
+      <c r="L7" s="42" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1" s="32">
+      <c r="B8" s="1" t="n"/>
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="39" t="n"/>
+      <c r="E8" s="39" t="n"/>
+      <c r="F8" s="39" t="n"/>
+      <c r="G8" s="40" t="n"/>
+      <c r="H8" s="68" t="n"/>
+      <c r="I8" s="22" t="n"/>
+      <c r="J8" s="23" t="n"/>
+      <c r="K8" s="41" t="n"/>
+      <c r="L8" s="42" t="n"/>
+    </row>
+    <row r="9" ht="18" customHeight="1" s="32">
+      <c r="B9" s="1" t="n"/>
+      <c r="C9" s="38" t="n"/>
+      <c r="D9" s="39" t="n"/>
+      <c r="E9" s="39" t="n"/>
+      <c r="F9" s="39" t="n"/>
+      <c r="G9" s="40" t="n"/>
+      <c r="H9" s="68" t="n"/>
+      <c r="I9" s="22" t="n"/>
+      <c r="J9" s="23" t="n"/>
+      <c r="K9" s="41" t="n"/>
+      <c r="L9" s="42" t="n"/>
+    </row>
+    <row r="10" ht="18" customHeight="1" s="32">
+      <c r="B10" s="1" t="n"/>
+      <c r="C10" s="38" t="n"/>
+      <c r="D10" s="39" t="n"/>
+      <c r="E10" s="39" t="n"/>
+      <c r="F10" s="39" t="n"/>
+      <c r="G10" s="40" t="n"/>
+      <c r="H10" s="68" t="n"/>
+      <c r="I10" s="22" t="n"/>
+      <c r="J10" s="23" t="n"/>
+      <c r="K10" s="41" t="n"/>
+      <c r="L10" s="42" t="n"/>
+    </row>
+    <row r="11" ht="18" customHeight="1" s="32">
+      <c r="B11" s="1" t="n"/>
+      <c r="C11" s="38" t="n"/>
+      <c r="D11" s="39" t="n"/>
+      <c r="E11" s="39" t="n"/>
+      <c r="F11" s="39" t="n"/>
+      <c r="G11" s="40" t="n"/>
+      <c r="H11" s="68" t="n"/>
+      <c r="I11" s="22" t="n"/>
+      <c r="J11" s="23" t="n"/>
+      <c r="K11" s="41" t="n"/>
+      <c r="L11" s="42" t="n"/>
+    </row>
+    <row r="12" ht="18" customHeight="1" s="32">
+      <c r="B12" s="1" t="n"/>
+      <c r="C12" s="38" t="n"/>
+      <c r="D12" s="39" t="n"/>
+      <c r="E12" s="39" t="n"/>
+      <c r="F12" s="39" t="n"/>
+      <c r="G12" s="40" t="n"/>
+      <c r="H12" s="68" t="n"/>
+      <c r="I12" s="22" t="n"/>
+      <c r="J12" s="23" t="n"/>
+      <c r="K12" s="41" t="n"/>
+      <c r="L12" s="42" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1" s="32">
+      <c r="B13" s="1" t="n"/>
+      <c r="C13" s="38" t="n"/>
+      <c r="D13" s="39" t="n"/>
+      <c r="E13" s="39" t="n"/>
+      <c r="F13" s="39" t="n"/>
+      <c r="G13" s="40" t="n"/>
+      <c r="H13" s="68" t="n"/>
+      <c r="I13" s="22" t="n"/>
+      <c r="J13" s="23" t="n"/>
+      <c r="K13" s="41" t="n"/>
+      <c r="L13" s="42" t="n"/>
+    </row>
+    <row r="14" ht="18" customHeight="1" s="32">
+      <c r="B14" s="1" t="n"/>
+      <c r="C14" s="38" t="n"/>
+      <c r="D14" s="39" t="n"/>
+      <c r="E14" s="39" t="n"/>
+      <c r="F14" s="39" t="n"/>
+      <c r="G14" s="40" t="n"/>
+      <c r="H14" s="68" t="n"/>
+      <c r="I14" s="22" t="n"/>
+      <c r="J14" s="23" t="n"/>
+      <c r="K14" s="41" t="n"/>
+      <c r="L14" s="42" t="n"/>
+    </row>
+    <row r="15" ht="18" customHeight="1" s="32">
+      <c r="B15" s="1" t="n"/>
+      <c r="C15" s="38" t="n"/>
+      <c r="D15" s="39" t="n"/>
+      <c r="E15" s="39" t="n"/>
+      <c r="F15" s="39" t="n"/>
+      <c r="G15" s="40" t="n"/>
+      <c r="H15" s="68" t="n"/>
+      <c r="I15" s="22" t="n"/>
+      <c r="J15" s="23" t="n"/>
+      <c r="K15" s="41" t="n"/>
+      <c r="L15" s="42" t="n"/>
+    </row>
+    <row r="16" ht="18" customHeight="1" s="32">
+      <c r="B16" s="1" t="n"/>
+      <c r="C16" s="38" t="n"/>
+      <c r="D16" s="39" t="n"/>
+      <c r="E16" s="39" t="n"/>
+      <c r="F16" s="39" t="n"/>
+      <c r="G16" s="40" t="n"/>
+      <c r="H16" s="68" t="n"/>
+      <c r="I16" s="22" t="n"/>
+      <c r="J16" s="23" t="n"/>
+      <c r="K16" s="41" t="n"/>
+      <c r="L16" s="42" t="n"/>
+    </row>
+    <row r="17" ht="18" customHeight="1" s="32">
+      <c r="B17" s="1" t="n"/>
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="39" t="n"/>
+      <c r="E17" s="39" t="n"/>
+      <c r="F17" s="39" t="n"/>
+      <c r="G17" s="40" t="n"/>
+      <c r="H17" s="68" t="n"/>
+      <c r="I17" s="22" t="n"/>
+      <c r="J17" s="23" t="n"/>
+      <c r="K17" s="41" t="n"/>
+      <c r="L17" s="42" t="n"/>
+    </row>
+    <row r="18" ht="18" customHeight="1" s="32">
+      <c r="B18" s="1" t="n"/>
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="39" t="n"/>
+      <c r="E18" s="39" t="n"/>
+      <c r="F18" s="39" t="n"/>
+      <c r="G18" s="40" t="n"/>
+      <c r="H18" s="68" t="n"/>
+      <c r="I18" s="22" t="n"/>
+      <c r="J18" s="23" t="n"/>
+      <c r="K18" s="41" t="n"/>
+      <c r="L18" s="42" t="n"/>
+    </row>
+    <row r="19" ht="18" customHeight="1" s="32">
+      <c r="B19" s="1" t="n"/>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="39" t="n"/>
+      <c r="E19" s="39" t="n"/>
+      <c r="F19" s="39" t="n"/>
+      <c r="G19" s="40" t="n"/>
+      <c r="H19" s="68" t="n"/>
+      <c r="I19" s="22" t="n"/>
+      <c r="J19" s="23" t="n"/>
+      <c r="K19" s="41" t="n"/>
+      <c r="L19" s="42" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1" s="32">
+      <c r="B20" s="1" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="39" t="n"/>
+      <c r="E20" s="39" t="n"/>
+      <c r="F20" s="39" t="n"/>
+      <c r="G20" s="40" t="n"/>
+      <c r="H20" s="68" t="n"/>
+      <c r="I20" s="22" t="n"/>
+      <c r="J20" s="23" t="n"/>
+      <c r="K20" s="41" t="n"/>
+      <c r="L20" s="42" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1" s="32">
+      <c r="B21" s="1" t="n"/>
+      <c r="C21" s="38" t="n"/>
+      <c r="D21" s="39" t="n"/>
+      <c r="E21" s="39" t="n"/>
+      <c r="F21" s="39" t="n"/>
+      <c r="G21" s="40" t="n"/>
+      <c r="H21" s="68" t="n"/>
+      <c r="I21" s="22" t="n"/>
+      <c r="J21" s="23" t="n"/>
+      <c r="K21" s="41" t="n"/>
+      <c r="L21" s="42" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1" s="32">
+      <c r="B22" s="1" t="n"/>
+      <c r="C22" s="38" t="n"/>
+      <c r="D22" s="39" t="n"/>
+      <c r="E22" s="39" t="n"/>
+      <c r="F22" s="39" t="n"/>
+      <c r="G22" s="40" t="n"/>
+      <c r="H22" s="68" t="n"/>
+      <c r="I22" s="22" t="n"/>
+      <c r="J22" s="23" t="n"/>
+      <c r="K22" s="41" t="n"/>
+      <c r="L22" s="42" t="n"/>
+    </row>
+    <row r="23" ht="18" customHeight="1" s="32">
+      <c r="B23" s="1" t="n"/>
+      <c r="C23" s="38" t="n"/>
+      <c r="D23" s="39" t="n"/>
+      <c r="E23" s="39" t="n"/>
+      <c r="F23" s="39" t="n"/>
+      <c r="G23" s="40" t="n"/>
+      <c r="H23" s="68" t="n"/>
+      <c r="I23" s="22" t="n"/>
+      <c r="J23" s="23" t="n"/>
+      <c r="K23" s="41" t="n"/>
+      <c r="L23" s="42" t="n"/>
+    </row>
+    <row r="24" ht="18" customHeight="1" s="32">
+      <c r="B24" s="1" t="n"/>
+      <c r="C24" s="38" t="n"/>
+      <c r="D24" s="39" t="n"/>
+      <c r="E24" s="39" t="n"/>
+      <c r="F24" s="39" t="n"/>
+      <c r="G24" s="40" t="n"/>
+      <c r="H24" s="68" t="n"/>
+      <c r="I24" s="22" t="n"/>
+      <c r="J24" s="23" t="n"/>
+      <c r="K24" s="41" t="n"/>
+      <c r="L24" s="42" t="n"/>
+    </row>
+    <row r="25" ht="18" customHeight="1" s="32">
+      <c r="B25" s="1" t="n"/>
+      <c r="C25" s="38" t="n"/>
+      <c r="D25" s="39" t="n"/>
+      <c r="E25" s="39" t="n"/>
+      <c r="F25" s="39" t="n"/>
+      <c r="G25" s="40" t="n"/>
+      <c r="H25" s="68" t="n"/>
+      <c r="I25" s="22" t="n"/>
+      <c r="J25" s="23" t="n"/>
+      <c r="K25" s="41" t="n"/>
+      <c r="L25" s="42" t="n"/>
+    </row>
+    <row r="26" ht="18" customHeight="1" s="32">
+      <c r="B26" s="1" t="n"/>
+      <c r="C26" s="38" t="n"/>
+      <c r="D26" s="39" t="n"/>
+      <c r="E26" s="39" t="n"/>
+      <c r="F26" s="39" t="n"/>
+      <c r="G26" s="40" t="n"/>
+      <c r="H26" s="68" t="n"/>
+      <c r="I26" s="22" t="n"/>
+      <c r="J26" s="23" t="n"/>
+      <c r="K26" s="41" t="n"/>
+      <c r="L26" s="42" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1" s="32">
+      <c r="B27" s="1" t="n"/>
+      <c r="C27" s="38" t="n"/>
+      <c r="D27" s="39" t="n"/>
+      <c r="E27" s="39" t="n"/>
+      <c r="F27" s="39" t="n"/>
+      <c r="G27" s="40" t="n"/>
+      <c r="H27" s="68" t="n"/>
+      <c r="I27" s="22" t="n"/>
+      <c r="J27" s="23" t="n"/>
+      <c r="K27" s="41" t="n"/>
+      <c r="L27" s="42" t="n"/>
+    </row>
+    <row r="28" ht="18" customHeight="1" s="32">
+      <c r="B28" s="1" t="n"/>
+      <c r="C28" s="38" t="n"/>
+      <c r="D28" s="39" t="n"/>
+      <c r="E28" s="39" t="n"/>
+      <c r="F28" s="39" t="n"/>
+      <c r="G28" s="40" t="n"/>
+      <c r="H28" s="68" t="n"/>
+      <c r="I28" s="22" t="n"/>
+      <c r="J28" s="23" t="n"/>
+      <c r="K28" s="41" t="n"/>
+      <c r="L28" s="42" t="n"/>
+    </row>
+    <row r="29" ht="18" customHeight="1" s="32">
+      <c r="B29" s="1" t="n"/>
+      <c r="C29" s="67" t="n"/>
+      <c r="D29" s="39" t="n"/>
+      <c r="E29" s="39" t="n"/>
+      <c r="F29" s="39" t="n"/>
+      <c r="G29" s="40" t="n"/>
+      <c r="H29" s="68" t="n"/>
+      <c r="I29" s="22" t="n"/>
+      <c r="J29" s="23" t="n"/>
+      <c r="K29" s="41" t="n"/>
+      <c r="L29" s="42" t="n"/>
+    </row>
+    <row r="30" ht="18" customHeight="1" s="32">
+      <c r="B30" s="1" t="n"/>
+      <c r="C30" s="67" t="n"/>
+      <c r="D30" s="39" t="n"/>
+      <c r="E30" s="39" t="n"/>
+      <c r="F30" s="39" t="n"/>
+      <c r="G30" s="40" t="n"/>
+      <c r="H30" s="68" t="n"/>
+      <c r="I30" s="22" t="n"/>
+      <c r="J30" s="23" t="n"/>
+      <c r="K30" s="41" t="n"/>
+      <c r="L30" s="42" t="n"/>
+    </row>
+    <row r="31" ht="18" customHeight="1" s="32">
+      <c r="B31" s="1" t="n"/>
+      <c r="C31" s="67" t="n"/>
+      <c r="D31" s="39" t="n"/>
+      <c r="E31" s="39" t="n"/>
+      <c r="F31" s="39" t="n"/>
+      <c r="G31" s="40" t="n"/>
+      <c r="H31" s="68" t="n"/>
+      <c r="I31" s="22" t="n"/>
+      <c r="J31" s="23" t="n"/>
+      <c r="K31" s="41" t="n"/>
+      <c r="L31" s="42" t="n"/>
+    </row>
+    <row r="32" ht="18" customHeight="1" s="32">
+      <c r="B32" s="1" t="n"/>
+      <c r="C32" s="67" t="n"/>
+      <c r="D32" s="39" t="n"/>
+      <c r="E32" s="39" t="n"/>
+      <c r="F32" s="39" t="n"/>
+      <c r="G32" s="40" t="n"/>
+      <c r="H32" s="68" t="n"/>
+      <c r="I32" s="22" t="n"/>
+      <c r="J32" s="23" t="n"/>
+      <c r="K32" s="41" t="n"/>
+      <c r="L32" s="42" t="n"/>
+    </row>
+    <row r="33" ht="18" customHeight="1" s="32">
+      <c r="B33" s="1" t="n"/>
+      <c r="C33" s="67" t="n"/>
+      <c r="D33" s="39" t="n"/>
+      <c r="E33" s="39" t="n"/>
+      <c r="F33" s="39" t="n"/>
+      <c r="G33" s="40" t="n"/>
+      <c r="H33" s="68" t="n"/>
+      <c r="I33" s="22" t="n"/>
+      <c r="J33" s="23" t="n"/>
+      <c r="K33" s="41" t="n"/>
+      <c r="L33" s="42" t="n"/>
+    </row>
+    <row r="34" ht="18" customHeight="1" s="32">
+      <c r="B34" s="1" t="n"/>
+      <c r="C34" s="67" t="n"/>
+      <c r="D34" s="39" t="n"/>
+      <c r="E34" s="39" t="n"/>
+      <c r="F34" s="39" t="n"/>
+      <c r="G34" s="40" t="n"/>
+      <c r="H34" s="68" t="n"/>
+      <c r="I34" s="22" t="n"/>
+      <c r="J34" s="23" t="n"/>
+      <c r="K34" s="41" t="n"/>
+      <c r="L34" s="42" t="n"/>
+    </row>
+    <row r="35" ht="18" customHeight="1" s="32">
+      <c r="B35" s="1" t="n"/>
+      <c r="C35" s="38" t="n"/>
+      <c r="D35" s="39" t="n"/>
+      <c r="E35" s="39" t="n"/>
+      <c r="F35" s="39" t="n"/>
+      <c r="G35" s="40" t="n"/>
+      <c r="H35" s="68" t="n"/>
+      <c r="I35" s="22" t="n"/>
+      <c r="J35" s="23" t="n"/>
+      <c r="K35" s="41" t="n"/>
+      <c r="L35" s="42" t="n"/>
+    </row>
+    <row r="36" ht="18" customHeight="1" s="32">
+      <c r="B36" s="1" t="n"/>
+      <c r="C36" s="38" t="n"/>
+      <c r="D36" s="39" t="n"/>
+      <c r="E36" s="39" t="n"/>
+      <c r="F36" s="39" t="n"/>
+      <c r="G36" s="40" t="n"/>
+      <c r="H36" s="68" t="n"/>
+      <c r="I36" s="22" t="n"/>
+      <c r="J36" s="23" t="n"/>
+      <c r="K36" s="41" t="n"/>
+      <c r="L36" s="42" t="n"/>
+    </row>
+    <row r="37" ht="18" customHeight="1" s="32">
+      <c r="B37" s="1" t="n"/>
+      <c r="C37" s="38" t="n"/>
+      <c r="D37" s="39" t="n"/>
+      <c r="E37" s="39" t="n"/>
+      <c r="F37" s="39" t="n"/>
+      <c r="G37" s="40" t="n"/>
+      <c r="H37" s="68" t="n"/>
+      <c r="I37" s="22" t="n"/>
+      <c r="J37" s="23" t="n"/>
+      <c r="K37" s="41" t="n"/>
+      <c r="L37" s="42" t="n"/>
+    </row>
+    <row r="38" ht="18" customHeight="1" s="32">
+      <c r="B38" s="1" t="n"/>
+      <c r="C38" s="38" t="n"/>
+      <c r="D38" s="39" t="n"/>
+      <c r="E38" s="39" t="n"/>
+      <c r="F38" s="39" t="n"/>
+      <c r="G38" s="40" t="n"/>
+      <c r="H38" s="68" t="n"/>
+      <c r="I38" s="22" t="n"/>
+      <c r="J38" s="23" t="n"/>
+      <c r="K38" s="41" t="n"/>
+      <c r="L38" s="42" t="n"/>
+    </row>
+    <row r="39" ht="18" customHeight="1" s="32">
+      <c r="B39" s="1" t="n"/>
+      <c r="C39" s="38" t="n"/>
+      <c r="D39" s="39" t="n"/>
+      <c r="E39" s="39" t="n"/>
+      <c r="F39" s="39" t="n"/>
+      <c r="G39" s="40" t="n"/>
+      <c r="H39" s="68" t="n"/>
+      <c r="I39" s="22" t="n"/>
+      <c r="J39" s="23" t="n"/>
+      <c r="K39" s="41" t="n"/>
+      <c r="L39" s="42" t="n"/>
+    </row>
+    <row r="40" ht="18" customHeight="1" s="32">
+      <c r="B40" s="1" t="n"/>
+      <c r="C40" s="38" t="n"/>
+      <c r="D40" s="39" t="n"/>
+      <c r="E40" s="39" t="n"/>
+      <c r="F40" s="39" t="n"/>
+      <c r="G40" s="40" t="n"/>
+      <c r="H40" s="68" t="n"/>
+      <c r="I40" s="22" t="n"/>
+      <c r="J40" s="23" t="n"/>
+      <c r="K40" s="41" t="n"/>
+      <c r="L40" s="42" t="n"/>
+    </row>
+    <row r="41" ht="18" customHeight="1" s="32">
+      <c r="B41" s="1" t="n"/>
+      <c r="C41" s="38" t="n"/>
+      <c r="D41" s="39" t="n"/>
+      <c r="E41" s="39" t="n"/>
+      <c r="F41" s="39" t="n"/>
+      <c r="G41" s="40" t="n"/>
+      <c r="H41" s="68" t="n"/>
+      <c r="I41" s="22" t="n"/>
+      <c r="J41" s="23" t="n"/>
+      <c r="K41" s="41" t="n"/>
+      <c r="L41" s="42" t="n"/>
+    </row>
+    <row r="42" ht="18" customHeight="1" s="32">
+      <c r="B42" s="1" t="n"/>
+      <c r="C42" s="38" t="n"/>
+      <c r="D42" s="39" t="n"/>
+      <c r="E42" s="39" t="n"/>
+      <c r="F42" s="39" t="n"/>
+      <c r="G42" s="40" t="n"/>
+      <c r="H42" s="68" t="n"/>
+      <c r="I42" s="22" t="n"/>
+      <c r="J42" s="23" t="n"/>
+      <c r="K42" s="41" t="n"/>
+      <c r="L42" s="42" t="n"/>
+    </row>
+    <row r="43" ht="18" customHeight="1" s="32">
+      <c r="B43" s="1" t="n"/>
+      <c r="C43" s="38" t="n"/>
+      <c r="D43" s="39" t="n"/>
+      <c r="E43" s="39" t="n"/>
+      <c r="F43" s="39" t="n"/>
+      <c r="G43" s="40" t="n"/>
+      <c r="H43" s="68" t="n"/>
+      <c r="I43" s="27" t="n"/>
+      <c r="J43" s="26" t="n"/>
+      <c r="K43" s="41" t="n"/>
+      <c r="L43" s="42" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1" s="32">
+      <c r="B44" s="1" t="n"/>
+      <c r="C44" s="38" t="n"/>
+      <c r="D44" s="39" t="n"/>
+      <c r="E44" s="39" t="n"/>
+      <c r="F44" s="39" t="n"/>
+      <c r="G44" s="40" t="n"/>
+      <c r="H44" s="68" t="n"/>
+      <c r="I44" s="22" t="n"/>
+      <c r="J44" s="23" t="n"/>
+      <c r="K44" s="41" t="n"/>
+      <c r="L44" s="42" t="n"/>
+    </row>
+    <row r="45" ht="18" customHeight="1" s="32">
+      <c r="B45" s="1" t="n"/>
+      <c r="C45" s="38" t="n"/>
+      <c r="D45" s="39" t="n"/>
+      <c r="E45" s="39" t="n"/>
+      <c r="F45" s="39" t="n"/>
+      <c r="G45" s="40" t="n"/>
+      <c r="H45" s="68" t="n"/>
+      <c r="I45" s="22" t="n"/>
+      <c r="J45" s="23" t="n"/>
+      <c r="K45" s="41" t="n"/>
+      <c r="L45" s="42" t="n"/>
+    </row>
+    <row r="46" ht="18" customHeight="1" s="32">
+      <c r="B46" s="1" t="n"/>
+      <c r="C46" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">合  計  </t>
+        </is>
+      </c>
+      <c r="D46" s="47" t="n"/>
+      <c r="E46" s="47" t="n"/>
+      <c r="F46" s="47" t="n"/>
+      <c r="G46" s="47" t="n"/>
+      <c r="H46" s="47" t="n"/>
+      <c r="I46" s="47" t="n"/>
+      <c r="J46" s="48" t="n"/>
+      <c r="K46" s="45">
+        <f>SUM(K5:L45)</f>
+        <v/>
+      </c>
+      <c r="L46" s="30" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="88">
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="C45:G45"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C29:G29"/>
+    <mergeCell ref="C44:G44"/>
+    <mergeCell ref="C31:G31"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C46:J46"/>
+    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="F1:I2"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="K41:L41"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="K45:L45"/>
+    <mergeCell ref="C26:G26"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="C28:G28"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="K36:L36"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="C43:G43"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="C27:G27"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="K4:L4"/>
+  </mergeCells>
+  <pageMargins left="0.7868055555555555" right="0.5902777777777778" top="0.9840277777777777" bottom="0.9840277777777777" header="0.5111111111111111" footer="0.5111111111111111"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="90"/>
+</worksheet>
 </file>
--- a/template_estimate.xlsx
+++ b/template_estimate.xlsx
@@ -2580,7 +2580,8 @@
       <formula1>品名</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7868055555555555" right="0.5902777777777778" top="0.9840277777777777" bottom="0.9840277777777777" header="0.5111111111111111" footer="0.5111111111111111"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.6889763779527559" right="0.6889763779527559" top="0.9840277777777777" bottom="0.9840277777777777" header="0.5111111111111111" footer="0.5111111111111111"/>
   <pageSetup orientation="portrait" paperSize="9" scale="90"/>
 </worksheet>
 </file>
@@ -3327,7 +3328,8 @@
     <mergeCell ref="C19:G19"/>
     <mergeCell ref="K4:L4"/>
   </mergeCells>
-  <pageMargins left="0.7868055555555555" right="0.5902777777777778" top="0.9840277777777777" bottom="0.9840277777777777" header="0.5111111111111111" footer="0.5111111111111111"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.6889763779527559" right="0.6889763779527559" top="0.9840277777777777" bottom="0.9840277777777777" header="0.5111111111111111" footer="0.5111111111111111"/>
   <pageSetup orientation="portrait" paperSize="9" scale="90"/>
 </worksheet>
 </file>
@@ -4074,7 +4076,8 @@
     <mergeCell ref="C19:G19"/>
     <mergeCell ref="K4:L4"/>
   </mergeCells>
-  <pageMargins left="0.7868055555555555" right="0.5902777777777778" top="0.9840277777777777" bottom="0.9840277777777777" header="0.5111111111111111" footer="0.5111111111111111"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.6889763779527559" right="0.6889763779527559" top="0.9840277777777777" bottom="0.9840277777777777" header="0.5111111111111111" footer="0.5111111111111111"/>
   <pageSetup orientation="portrait" paperSize="9" scale="90"/>
 </worksheet>
 </file>
@@ -4821,7 +4824,8 @@
     <mergeCell ref="C19:G19"/>
     <mergeCell ref="K4:L4"/>
   </mergeCells>
-  <pageMargins left="0.7868055555555555" right="0.5902777777777778" top="0.9840277777777777" bottom="0.9840277777777777" header="0.5111111111111111" footer="0.5111111111111111"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.6889763779527559" right="0.6889763779527559" top="0.9840277777777777" bottom="0.9840277777777777" header="0.5111111111111111" footer="0.5111111111111111"/>
   <pageSetup orientation="portrait" paperSize="9" scale="90"/>
 </worksheet>
 </file>
@@ -5568,7 +5572,8 @@
     <mergeCell ref="C19:G19"/>
     <mergeCell ref="K4:L4"/>
   </mergeCells>
-  <pageMargins left="0.7868055555555555" right="0.5902777777777778" top="0.9840277777777777" bottom="0.9840277777777777" header="0.5111111111111111" footer="0.5111111111111111"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.6889763779527559" right="0.6889763779527559" top="0.9840277777777777" bottom="0.9840277777777777" header="0.5111111111111111" footer="0.5111111111111111"/>
   <pageSetup orientation="portrait" paperSize="9" scale="90"/>
 </worksheet>
 </file>
@@ -6315,7 +6320,8 @@
     <mergeCell ref="C19:G19"/>
     <mergeCell ref="K4:L4"/>
   </mergeCells>
-  <pageMargins left="0.7868055555555555" right="0.5902777777777778" top="0.9840277777777777" bottom="0.9840277777777777" header="0.5111111111111111" footer="0.5111111111111111"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.6889763779527559" right="0.6889763779527559" top="0.9840277777777777" bottom="0.9840277777777777" header="0.5111111111111111" footer="0.5111111111111111"/>
   <pageSetup orientation="portrait" paperSize="9" scale="90"/>
 </worksheet>
 </file>
--- a/template_estimate.xlsx
+++ b/template_estimate.xlsx
@@ -1822,8 +1822,9 @@
       <formula1>単位</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.7868055555555555" right="0.5902777777777778" top="0.9840277777777777" bottom="0.9840277777777777" header="0.5111111111111111" footer="0.5111111111111111"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="90"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="96"/>
 </worksheet>
 </file>
 
@@ -2581,8 +2582,8 @@
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.6889763779527559" right="0.6889763779527559" top="0.9840277777777777" bottom="0.9840277777777777" header="0.5111111111111111" footer="0.5111111111111111"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="90"/>
+  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="96"/>
 </worksheet>
 </file>
 
@@ -3329,8 +3330,8 @@
     <mergeCell ref="K4:L4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.6889763779527559" right="0.6889763779527559" top="0.9840277777777777" bottom="0.9840277777777777" header="0.5111111111111111" footer="0.5111111111111111"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="90"/>
+  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="96"/>
 </worksheet>
 </file>
 
@@ -4077,8 +4078,8 @@
     <mergeCell ref="K4:L4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.6889763779527559" right="0.6889763779527559" top="0.9840277777777777" bottom="0.9840277777777777" header="0.5111111111111111" footer="0.5111111111111111"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="90"/>
+  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="96"/>
 </worksheet>
 </file>
 
@@ -4825,8 +4826,8 @@
     <mergeCell ref="K4:L4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.6889763779527559" right="0.6889763779527559" top="0.9840277777777777" bottom="0.9840277777777777" header="0.5111111111111111" footer="0.5111111111111111"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="90"/>
+  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="96"/>
 </worksheet>
 </file>
 
@@ -5573,8 +5574,8 @@
     <mergeCell ref="K4:L4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.6889763779527559" right="0.6889763779527559" top="0.9840277777777777" bottom="0.9840277777777777" header="0.5111111111111111" footer="0.5111111111111111"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="90"/>
+  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="96"/>
 </worksheet>
 </file>
 
@@ -6321,7 +6322,7 @@
     <mergeCell ref="K4:L4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.6889763779527559" right="0.6889763779527559" top="0.9840277777777777" bottom="0.9840277777777777" header="0.5111111111111111" footer="0.5111111111111111"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="90"/>
+  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="96"/>
 </worksheet>
 </file>
--- a/template_estimate.xlsx
+++ b/template_estimate.xlsx
@@ -1019,7 +1019,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.2"/>
@@ -1038,7 +1038,7 @@
     <col width="0.88671875" customWidth="1" style="32" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="32">
+    <row r="1" ht="21" customHeight="1" s="32">
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="2" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
       <c r="K12" s="52" t="n"/>
       <c r="L12" s="52" t="n"/>
     </row>
-    <row r="13" ht="18" customHeight="1" s="32">
+    <row r="13" ht="30" customHeight="1" s="32">
       <c r="B13" s="1" t="n"/>
       <c r="C13" s="10" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="L16" s="30" t="n"/>
     </row>
-    <row r="17" ht="18" customHeight="1" s="32">
+    <row r="17" ht="19" customHeight="1" s="32">
       <c r="B17" s="1" t="n"/>
       <c r="C17" s="38" t="n"/>
       <c r="D17" s="39" t="n"/>
@@ -1323,7 +1323,7 @@
       <c r="K17" s="41" t="n"/>
       <c r="L17" s="42" t="n"/>
     </row>
-    <row r="18" ht="18" customHeight="1" s="32">
+    <row r="18" ht="19" customHeight="1" s="32">
       <c r="B18" s="1" t="n"/>
       <c r="C18" s="38" t="n"/>
       <c r="D18" s="39" t="n"/>
@@ -1336,7 +1336,7 @@
       <c r="K18" s="41" t="n"/>
       <c r="L18" s="42" t="n"/>
     </row>
-    <row r="19" ht="18" customHeight="1" s="32">
+    <row r="19" ht="19" customHeight="1" s="32">
       <c r="B19" s="1" t="n"/>
       <c r="C19" s="38" t="n"/>
       <c r="D19" s="39" t="n"/>
@@ -1349,7 +1349,7 @@
       <c r="K19" s="41" t="n"/>
       <c r="L19" s="42" t="n"/>
     </row>
-    <row r="20" ht="18" customHeight="1" s="32">
+    <row r="20" ht="19" customHeight="1" s="32">
       <c r="B20" s="1" t="n"/>
       <c r="C20" s="38" t="n"/>
       <c r="D20" s="39" t="n"/>
@@ -1362,7 +1362,7 @@
       <c r="K20" s="41" t="n"/>
       <c r="L20" s="42" t="n"/>
     </row>
-    <row r="21" ht="18" customHeight="1" s="32">
+    <row r="21" ht="19" customHeight="1" s="32">
       <c r="B21" s="1" t="n"/>
       <c r="C21" s="38" t="n"/>
       <c r="D21" s="39" t="n"/>
@@ -1375,7 +1375,7 @@
       <c r="K21" s="41" t="n"/>
       <c r="L21" s="42" t="n"/>
     </row>
-    <row r="22" ht="18" customHeight="1" s="32">
+    <row r="22" ht="19" customHeight="1" s="32">
       <c r="B22" s="1" t="n"/>
       <c r="C22" s="38" t="n"/>
       <c r="D22" s="39" t="n"/>
@@ -1388,7 +1388,7 @@
       <c r="K22" s="41" t="n"/>
       <c r="L22" s="42" t="n"/>
     </row>
-    <row r="23" ht="18" customHeight="1" s="32">
+    <row r="23" ht="19" customHeight="1" s="32">
       <c r="B23" s="1" t="n"/>
       <c r="C23" s="38" t="n"/>
       <c r="D23" s="39" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="K23" s="41" t="n"/>
       <c r="L23" s="42" t="n"/>
     </row>
-    <row r="24" ht="18" customHeight="1" s="32">
+    <row r="24" ht="19" customHeight="1" s="32">
       <c r="B24" s="1" t="n"/>
       <c r="C24" s="38" t="n"/>
       <c r="D24" s="39" t="n"/>
@@ -1414,7 +1414,7 @@
       <c r="K24" s="41" t="n"/>
       <c r="L24" s="42" t="n"/>
     </row>
-    <row r="25" ht="18" customHeight="1" s="32">
+    <row r="25" ht="19" customHeight="1" s="32">
       <c r="B25" s="1" t="n"/>
       <c r="C25" s="38" t="n"/>
       <c r="D25" s="39" t="n"/>
@@ -1427,7 +1427,7 @@
       <c r="K25" s="41" t="n"/>
       <c r="L25" s="42" t="n"/>
     </row>
-    <row r="26" ht="18" customHeight="1" s="32">
+    <row r="26" ht="19" customHeight="1" s="32">
       <c r="B26" s="1" t="n"/>
       <c r="C26" s="38" t="n"/>
       <c r="D26" s="39" t="n"/>
@@ -1440,7 +1440,7 @@
       <c r="K26" s="41" t="n"/>
       <c r="L26" s="42" t="n"/>
     </row>
-    <row r="27" ht="18" customHeight="1" s="32">
+    <row r="27" ht="19" customHeight="1" s="32">
       <c r="B27" s="1" t="n"/>
       <c r="C27" s="38" t="n"/>
       <c r="D27" s="39" t="n"/>
@@ -1453,7 +1453,7 @@
       <c r="K27" s="41" t="n"/>
       <c r="L27" s="42" t="n"/>
     </row>
-    <row r="28" ht="18" customHeight="1" s="32">
+    <row r="28" ht="19" customHeight="1" s="32">
       <c r="B28" s="1" t="n"/>
       <c r="C28" s="38" t="n"/>
       <c r="D28" s="39" t="n"/>
@@ -1466,7 +1466,7 @@
       <c r="K28" s="41" t="n"/>
       <c r="L28" s="42" t="n"/>
     </row>
-    <row r="29" ht="18" customHeight="1" s="32">
+    <row r="29" ht="19" customHeight="1" s="32">
       <c r="B29" s="1" t="n"/>
       <c r="C29" s="67" t="n"/>
       <c r="D29" s="39" t="n"/>
@@ -1479,7 +1479,7 @@
       <c r="K29" s="41" t="n"/>
       <c r="L29" s="42" t="n"/>
     </row>
-    <row r="30" ht="18" customHeight="1" s="32">
+    <row r="30" ht="19" customHeight="1" s="32">
       <c r="B30" s="1" t="n"/>
       <c r="C30" s="67" t="n"/>
       <c r="D30" s="39" t="n"/>
@@ -1492,7 +1492,7 @@
       <c r="K30" s="41" t="n"/>
       <c r="L30" s="42" t="n"/>
     </row>
-    <row r="31" ht="18" customHeight="1" s="32">
+    <row r="31" ht="19" customHeight="1" s="32">
       <c r="B31" s="1" t="n"/>
       <c r="C31" s="67" t="n"/>
       <c r="D31" s="39" t="n"/>
@@ -1505,7 +1505,7 @@
       <c r="K31" s="41" t="n"/>
       <c r="L31" s="42" t="n"/>
     </row>
-    <row r="32" ht="18" customHeight="1" s="32">
+    <row r="32" ht="19" customHeight="1" s="32">
       <c r="B32" s="1" t="n"/>
       <c r="C32" s="67" t="n"/>
       <c r="D32" s="39" t="n"/>
@@ -1518,7 +1518,7 @@
       <c r="K32" s="41" t="n"/>
       <c r="L32" s="42" t="n"/>
     </row>
-    <row r="33" ht="18" customHeight="1" s="32">
+    <row r="33" ht="19" customHeight="1" s="32">
       <c r="B33" s="1" t="n"/>
       <c r="C33" s="67" t="n"/>
       <c r="D33" s="39" t="n"/>
@@ -1531,7 +1531,7 @@
       <c r="K33" s="41" t="n"/>
       <c r="L33" s="42" t="n"/>
     </row>
-    <row r="34" ht="18" customHeight="1" s="32">
+    <row r="34" ht="19" customHeight="1" s="32">
       <c r="B34" s="1" t="n"/>
       <c r="C34" s="67" t="n"/>
       <c r="D34" s="39" t="n"/>
@@ -1544,7 +1544,7 @@
       <c r="K34" s="41" t="n"/>
       <c r="L34" s="42" t="n"/>
     </row>
-    <row r="35" ht="18" customHeight="1" s="32">
+    <row r="35" ht="19" customHeight="1" s="32">
       <c r="B35" s="1" t="n"/>
       <c r="C35" s="38" t="n"/>
       <c r="D35" s="39" t="n"/>
@@ -1557,7 +1557,7 @@
       <c r="K35" s="41" t="n"/>
       <c r="L35" s="42" t="n"/>
     </row>
-    <row r="36" ht="18" customHeight="1" s="32">
+    <row r="36" ht="19" customHeight="1" s="32">
       <c r="B36" s="1" t="n"/>
       <c r="C36" s="38" t="n"/>
       <c r="D36" s="39" t="n"/>
@@ -1570,7 +1570,7 @@
       <c r="K36" s="41" t="n"/>
       <c r="L36" s="42" t="n"/>
     </row>
-    <row r="37" ht="18" customHeight="1" s="32">
+    <row r="37" ht="19" customHeight="1" s="32">
       <c r="B37" s="1" t="n"/>
       <c r="C37" s="38" t="n"/>
       <c r="D37" s="39" t="n"/>
@@ -1583,7 +1583,7 @@
       <c r="K37" s="41" t="n"/>
       <c r="L37" s="42" t="n"/>
     </row>
-    <row r="38" ht="18" customHeight="1" s="32">
+    <row r="38" ht="19" customHeight="1" s="32">
       <c r="B38" s="1" t="n"/>
       <c r="C38" s="38" t="n"/>
       <c r="D38" s="39" t="n"/>
@@ -1596,7 +1596,7 @@
       <c r="K38" s="41" t="n"/>
       <c r="L38" s="42" t="n"/>
     </row>
-    <row r="39" ht="18" customHeight="1" s="32">
+    <row r="39" ht="19" customHeight="1" s="32">
       <c r="B39" s="1" t="n"/>
       <c r="C39" s="38" t="n"/>
       <c r="D39" s="39" t="n"/>
@@ -1609,7 +1609,7 @@
       <c r="K39" s="41" t="n"/>
       <c r="L39" s="42" t="n"/>
     </row>
-    <row r="40" ht="18" customHeight="1" s="32">
+    <row r="40" ht="19" customHeight="1" s="32">
       <c r="B40" s="1" t="n"/>
       <c r="C40" s="38" t="n"/>
       <c r="D40" s="39" t="n"/>
@@ -1622,7 +1622,7 @@
       <c r="K40" s="41" t="n"/>
       <c r="L40" s="42" t="n"/>
     </row>
-    <row r="41" ht="18" customHeight="1" s="32">
+    <row r="41" ht="19" customHeight="1" s="32">
       <c r="B41" s="1" t="n"/>
       <c r="C41" s="38" t="n"/>
       <c r="D41" s="39" t="n"/>
@@ -1635,7 +1635,7 @@
       <c r="K41" s="41" t="n"/>
       <c r="L41" s="42" t="n"/>
     </row>
-    <row r="42" ht="18" customHeight="1" s="32">
+    <row r="42" ht="19" customHeight="1" s="32">
       <c r="B42" s="1" t="n"/>
       <c r="C42" s="38" t="n"/>
       <c r="D42" s="39" t="n"/>
@@ -1648,7 +1648,7 @@
       <c r="K42" s="41" t="n"/>
       <c r="L42" s="42" t="n"/>
     </row>
-    <row r="43" ht="18" customHeight="1" s="32">
+    <row r="43" ht="19" customHeight="1" s="32">
       <c r="B43" s="1" t="n"/>
       <c r="C43" s="38" t="n"/>
       <c r="D43" s="39" t="n"/>
@@ -1661,7 +1661,7 @@
       <c r="K43" s="41" t="n"/>
       <c r="L43" s="42" t="n"/>
     </row>
-    <row r="44" ht="18" customHeight="1" s="32">
+    <row r="44" ht="19" customHeight="1" s="32">
       <c r="B44" s="1" t="n"/>
       <c r="C44" s="38" t="n"/>
       <c r="D44" s="39" t="n"/>
@@ -1674,7 +1674,7 @@
       <c r="K44" s="41" t="n"/>
       <c r="L44" s="42" t="n"/>
     </row>
-    <row r="45" ht="18" customHeight="1" s="32">
+    <row r="45" ht="19" customHeight="1" s="32">
       <c r="B45" s="1" t="n"/>
       <c r="C45" s="38" t="n"/>
       <c r="D45" s="39" t="n"/>
@@ -1687,7 +1687,7 @@
       <c r="K45" s="41" t="n"/>
       <c r="L45" s="42" t="n"/>
     </row>
-    <row r="46" ht="18" customHeight="1" s="32">
+    <row r="46" ht="19" customHeight="1" s="32">
       <c r="B46" s="1" t="n"/>
       <c r="C46" s="38" t="n"/>
       <c r="D46" s="39" t="n"/>
@@ -1823,8 +1823,8 @@
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="96"/>
+  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.4724409448818898" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1832,7 +1832,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.2"/>
@@ -1851,7 +1851,7 @@
     <col width="0.88671875" customWidth="1" style="32" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="32">
+    <row r="1" ht="21" customHeight="1" s="32">
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="2" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="L4" s="30" t="n"/>
     </row>
-    <row r="5" ht="18" customHeight="1" s="32">
+    <row r="5" ht="19" customHeight="1" s="32">
       <c r="B5" s="1" t="n"/>
       <c r="C5" s="38" t="n"/>
       <c r="D5" s="39" t="n"/>
@@ -1939,7 +1939,7 @@
       <c r="K5" s="41" t="n"/>
       <c r="L5" s="42" t="n"/>
     </row>
-    <row r="6" ht="18" customHeight="1" s="32">
+    <row r="6" ht="19" customHeight="1" s="32">
       <c r="B6" s="1" t="n"/>
       <c r="C6" s="38" t="n"/>
       <c r="D6" s="39" t="n"/>
@@ -1952,7 +1952,7 @@
       <c r="K6" s="41" t="n"/>
       <c r="L6" s="42" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1" s="32">
+    <row r="7" ht="19" customHeight="1" s="32">
       <c r="B7" s="1" t="n"/>
       <c r="C7" s="38" t="n"/>
       <c r="D7" s="39" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="K7" s="41" t="n"/>
       <c r="L7" s="42" t="n"/>
     </row>
-    <row r="8" ht="18" customHeight="1" s="32">
+    <row r="8" ht="19" customHeight="1" s="32">
       <c r="B8" s="1" t="n"/>
       <c r="C8" s="38" t="n"/>
       <c r="D8" s="39" t="n"/>
@@ -1978,7 +1978,7 @@
       <c r="K8" s="41" t="n"/>
       <c r="L8" s="42" t="n"/>
     </row>
-    <row r="9" ht="18" customHeight="1" s="32">
+    <row r="9" ht="19" customHeight="1" s="32">
       <c r="B9" s="1" t="n"/>
       <c r="C9" s="38" t="n"/>
       <c r="D9" s="39" t="n"/>
@@ -1991,7 +1991,7 @@
       <c r="K9" s="41" t="n"/>
       <c r="L9" s="42" t="n"/>
     </row>
-    <row r="10" ht="18" customHeight="1" s="32">
+    <row r="10" ht="19" customHeight="1" s="32">
       <c r="B10" s="1" t="n"/>
       <c r="C10" s="38" t="n"/>
       <c r="D10" s="39" t="n"/>
@@ -2004,7 +2004,7 @@
       <c r="K10" s="41" t="n"/>
       <c r="L10" s="42" t="n"/>
     </row>
-    <row r="11" ht="18" customHeight="1" s="32">
+    <row r="11" ht="19" customHeight="1" s="32">
       <c r="B11" s="1" t="n"/>
       <c r="C11" s="38" t="n"/>
       <c r="D11" s="39" t="n"/>
@@ -2017,7 +2017,7 @@
       <c r="K11" s="41" t="n"/>
       <c r="L11" s="42" t="n"/>
     </row>
-    <row r="12" ht="18" customHeight="1" s="32">
+    <row r="12" ht="19" customHeight="1" s="32">
       <c r="B12" s="1" t="n"/>
       <c r="C12" s="38" t="n"/>
       <c r="D12" s="39" t="n"/>
@@ -2030,7 +2030,7 @@
       <c r="K12" s="41" t="n"/>
       <c r="L12" s="42" t="n"/>
     </row>
-    <row r="13" ht="18" customHeight="1" s="32">
+    <row r="13" ht="19" customHeight="1" s="32">
       <c r="B13" s="1" t="n"/>
       <c r="C13" s="38" t="n"/>
       <c r="D13" s="39" t="n"/>
@@ -2043,7 +2043,7 @@
       <c r="K13" s="41" t="n"/>
       <c r="L13" s="42" t="n"/>
     </row>
-    <row r="14" ht="18" customHeight="1" s="32">
+    <row r="14" ht="19" customHeight="1" s="32">
       <c r="B14" s="1" t="n"/>
       <c r="C14" s="38" t="n"/>
       <c r="D14" s="39" t="n"/>
@@ -2056,7 +2056,7 @@
       <c r="K14" s="41" t="n"/>
       <c r="L14" s="42" t="n"/>
     </row>
-    <row r="15" ht="18" customHeight="1" s="32">
+    <row r="15" ht="19" customHeight="1" s="32">
       <c r="B15" s="1" t="n"/>
       <c r="C15" s="38" t="n"/>
       <c r="D15" s="39" t="n"/>
@@ -2069,7 +2069,7 @@
       <c r="K15" s="41" t="n"/>
       <c r="L15" s="42" t="n"/>
     </row>
-    <row r="16" ht="18" customHeight="1" s="32">
+    <row r="16" ht="19" customHeight="1" s="32">
       <c r="B16" s="1" t="n"/>
       <c r="C16" s="38" t="n"/>
       <c r="D16" s="39" t="n"/>
@@ -2082,7 +2082,7 @@
       <c r="K16" s="41" t="n"/>
       <c r="L16" s="42" t="n"/>
     </row>
-    <row r="17" ht="18" customHeight="1" s="32">
+    <row r="17" ht="19" customHeight="1" s="32">
       <c r="B17" s="1" t="n"/>
       <c r="C17" s="38" t="n"/>
       <c r="D17" s="39" t="n"/>
@@ -2095,7 +2095,7 @@
       <c r="K17" s="41" t="n"/>
       <c r="L17" s="42" t="n"/>
     </row>
-    <row r="18" ht="18" customHeight="1" s="32">
+    <row r="18" ht="19" customHeight="1" s="32">
       <c r="B18" s="1" t="n"/>
       <c r="C18" s="38" t="n"/>
       <c r="D18" s="39" t="n"/>
@@ -2108,7 +2108,7 @@
       <c r="K18" s="41" t="n"/>
       <c r="L18" s="42" t="n"/>
     </row>
-    <row r="19" ht="18" customHeight="1" s="32">
+    <row r="19" ht="19" customHeight="1" s="32">
       <c r="B19" s="1" t="n"/>
       <c r="C19" s="38" t="n"/>
       <c r="D19" s="39" t="n"/>
@@ -2121,7 +2121,7 @@
       <c r="K19" s="41" t="n"/>
       <c r="L19" s="42" t="n"/>
     </row>
-    <row r="20" ht="18" customHeight="1" s="32">
+    <row r="20" ht="19" customHeight="1" s="32">
       <c r="B20" s="1" t="n"/>
       <c r="C20" s="38" t="n"/>
       <c r="D20" s="39" t="n"/>
@@ -2134,7 +2134,7 @@
       <c r="K20" s="41" t="n"/>
       <c r="L20" s="42" t="n"/>
     </row>
-    <row r="21" ht="18" customHeight="1" s="32">
+    <row r="21" ht="19" customHeight="1" s="32">
       <c r="B21" s="1" t="n"/>
       <c r="C21" s="38" t="n"/>
       <c r="D21" s="39" t="n"/>
@@ -2147,7 +2147,7 @@
       <c r="K21" s="41" t="n"/>
       <c r="L21" s="42" t="n"/>
     </row>
-    <row r="22" ht="18" customHeight="1" s="32">
+    <row r="22" ht="19" customHeight="1" s="32">
       <c r="B22" s="1" t="n"/>
       <c r="C22" s="38" t="n"/>
       <c r="D22" s="39" t="n"/>
@@ -2160,7 +2160,7 @@
       <c r="K22" s="41" t="n"/>
       <c r="L22" s="42" t="n"/>
     </row>
-    <row r="23" ht="18" customHeight="1" s="32">
+    <row r="23" ht="19" customHeight="1" s="32">
       <c r="B23" s="1" t="n"/>
       <c r="C23" s="38" t="n"/>
       <c r="D23" s="39" t="n"/>
@@ -2173,7 +2173,7 @@
       <c r="K23" s="41" t="n"/>
       <c r="L23" s="42" t="n"/>
     </row>
-    <row r="24" ht="18" customHeight="1" s="32">
+    <row r="24" ht="19" customHeight="1" s="32">
       <c r="B24" s="1" t="n"/>
       <c r="C24" s="38" t="n"/>
       <c r="D24" s="39" t="n"/>
@@ -2186,7 +2186,7 @@
       <c r="K24" s="41" t="n"/>
       <c r="L24" s="42" t="n"/>
     </row>
-    <row r="25" ht="18" customHeight="1" s="32">
+    <row r="25" ht="19" customHeight="1" s="32">
       <c r="B25" s="1" t="n"/>
       <c r="C25" s="38" t="n"/>
       <c r="D25" s="39" t="n"/>
@@ -2199,7 +2199,7 @@
       <c r="K25" s="41" t="n"/>
       <c r="L25" s="42" t="n"/>
     </row>
-    <row r="26" ht="18" customHeight="1" s="32">
+    <row r="26" ht="19" customHeight="1" s="32">
       <c r="B26" s="1" t="n"/>
       <c r="C26" s="38" t="n"/>
       <c r="D26" s="39" t="n"/>
@@ -2212,7 +2212,7 @@
       <c r="K26" s="41" t="n"/>
       <c r="L26" s="42" t="n"/>
     </row>
-    <row r="27" ht="18" customHeight="1" s="32">
+    <row r="27" ht="19" customHeight="1" s="32">
       <c r="B27" s="1" t="n"/>
       <c r="C27" s="38" t="n"/>
       <c r="D27" s="39" t="n"/>
@@ -2225,7 +2225,7 @@
       <c r="K27" s="41" t="n"/>
       <c r="L27" s="42" t="n"/>
     </row>
-    <row r="28" ht="18" customHeight="1" s="32">
+    <row r="28" ht="19" customHeight="1" s="32">
       <c r="B28" s="1" t="n"/>
       <c r="C28" s="38" t="n"/>
       <c r="D28" s="39" t="n"/>
@@ -2238,7 +2238,7 @@
       <c r="K28" s="41" t="n"/>
       <c r="L28" s="42" t="n"/>
     </row>
-    <row r="29" ht="18" customHeight="1" s="32">
+    <row r="29" ht="19" customHeight="1" s="32">
       <c r="B29" s="1" t="n"/>
       <c r="C29" s="67" t="n"/>
       <c r="D29" s="39" t="n"/>
@@ -2251,7 +2251,7 @@
       <c r="K29" s="41" t="n"/>
       <c r="L29" s="42" t="n"/>
     </row>
-    <row r="30" ht="18" customHeight="1" s="32">
+    <row r="30" ht="19" customHeight="1" s="32">
       <c r="B30" s="1" t="n"/>
       <c r="C30" s="67" t="n"/>
       <c r="D30" s="39" t="n"/>
@@ -2264,7 +2264,7 @@
       <c r="K30" s="41" t="n"/>
       <c r="L30" s="42" t="n"/>
     </row>
-    <row r="31" ht="18" customHeight="1" s="32">
+    <row r="31" ht="19" customHeight="1" s="32">
       <c r="B31" s="1" t="n"/>
       <c r="C31" s="67" t="n"/>
       <c r="D31" s="39" t="n"/>
@@ -2277,7 +2277,7 @@
       <c r="K31" s="41" t="n"/>
       <c r="L31" s="42" t="n"/>
     </row>
-    <row r="32" ht="18" customHeight="1" s="32">
+    <row r="32" ht="19" customHeight="1" s="32">
       <c r="B32" s="1" t="n"/>
       <c r="C32" s="67" t="n"/>
       <c r="D32" s="39" t="n"/>
@@ -2290,7 +2290,7 @@
       <c r="K32" s="41" t="n"/>
       <c r="L32" s="42" t="n"/>
     </row>
-    <row r="33" ht="18" customHeight="1" s="32">
+    <row r="33" ht="19" customHeight="1" s="32">
       <c r="B33" s="1" t="n"/>
       <c r="C33" s="67" t="n"/>
       <c r="D33" s="39" t="n"/>
@@ -2303,7 +2303,7 @@
       <c r="K33" s="41" t="n"/>
       <c r="L33" s="42" t="n"/>
     </row>
-    <row r="34" ht="18" customHeight="1" s="32">
+    <row r="34" ht="19" customHeight="1" s="32">
       <c r="B34" s="1" t="n"/>
       <c r="C34" s="67" t="n"/>
       <c r="D34" s="39" t="n"/>
@@ -2316,7 +2316,7 @@
       <c r="K34" s="41" t="n"/>
       <c r="L34" s="42" t="n"/>
     </row>
-    <row r="35" ht="18" customHeight="1" s="32">
+    <row r="35" ht="19" customHeight="1" s="32">
       <c r="B35" s="1" t="n"/>
       <c r="C35" s="38" t="n"/>
       <c r="D35" s="39" t="n"/>
@@ -2329,7 +2329,7 @@
       <c r="K35" s="41" t="n"/>
       <c r="L35" s="42" t="n"/>
     </row>
-    <row r="36" ht="18" customHeight="1" s="32">
+    <row r="36" ht="19" customHeight="1" s="32">
       <c r="B36" s="1" t="n"/>
       <c r="C36" s="38" t="n"/>
       <c r="D36" s="39" t="n"/>
@@ -2342,7 +2342,7 @@
       <c r="K36" s="41" t="n"/>
       <c r="L36" s="42" t="n"/>
     </row>
-    <row r="37" ht="18" customHeight="1" s="32">
+    <row r="37" ht="19" customHeight="1" s="32">
       <c r="B37" s="1" t="n"/>
       <c r="C37" s="38" t="n"/>
       <c r="D37" s="39" t="n"/>
@@ -2355,7 +2355,7 @@
       <c r="K37" s="41" t="n"/>
       <c r="L37" s="42" t="n"/>
     </row>
-    <row r="38" ht="18" customHeight="1" s="32">
+    <row r="38" ht="19" customHeight="1" s="32">
       <c r="B38" s="1" t="n"/>
       <c r="C38" s="38" t="n"/>
       <c r="D38" s="39" t="n"/>
@@ -2368,7 +2368,7 @@
       <c r="K38" s="41" t="n"/>
       <c r="L38" s="42" t="n"/>
     </row>
-    <row r="39" ht="18" customHeight="1" s="32">
+    <row r="39" ht="19" customHeight="1" s="32">
       <c r="B39" s="1" t="n"/>
       <c r="C39" s="38" t="n"/>
       <c r="D39" s="39" t="n"/>
@@ -2381,7 +2381,7 @@
       <c r="K39" s="41" t="n"/>
       <c r="L39" s="42" t="n"/>
     </row>
-    <row r="40" ht="18" customHeight="1" s="32">
+    <row r="40" ht="19" customHeight="1" s="32">
       <c r="B40" s="1" t="n"/>
       <c r="C40" s="38" t="n"/>
       <c r="D40" s="39" t="n"/>
@@ -2394,7 +2394,7 @@
       <c r="K40" s="41" t="n"/>
       <c r="L40" s="42" t="n"/>
     </row>
-    <row r="41" ht="18" customHeight="1" s="32">
+    <row r="41" ht="19" customHeight="1" s="32">
       <c r="B41" s="1" t="n"/>
       <c r="C41" s="38" t="n"/>
       <c r="D41" s="39" t="n"/>
@@ -2407,7 +2407,7 @@
       <c r="K41" s="41" t="n"/>
       <c r="L41" s="42" t="n"/>
     </row>
-    <row r="42" ht="18" customHeight="1" s="32">
+    <row r="42" ht="19" customHeight="1" s="32">
       <c r="B42" s="1" t="n"/>
       <c r="C42" s="38" t="n"/>
       <c r="D42" s="39" t="n"/>
@@ -2420,7 +2420,7 @@
       <c r="K42" s="41" t="n"/>
       <c r="L42" s="42" t="n"/>
     </row>
-    <row r="43" ht="18" customHeight="1" s="32">
+    <row r="43" ht="19" customHeight="1" s="32">
       <c r="B43" s="1" t="n"/>
       <c r="C43" s="38" t="n"/>
       <c r="D43" s="39" t="n"/>
@@ -2433,7 +2433,7 @@
       <c r="K43" s="41" t="n"/>
       <c r="L43" s="42" t="n"/>
     </row>
-    <row r="44" ht="18" customHeight="1" s="32">
+    <row r="44" ht="19" customHeight="1" s="32">
       <c r="B44" s="1" t="n"/>
       <c r="C44" s="38" t="n"/>
       <c r="D44" s="39" t="n"/>
@@ -2446,7 +2446,7 @@
       <c r="K44" s="41" t="n"/>
       <c r="L44" s="42" t="n"/>
     </row>
-    <row r="45" ht="18" customHeight="1" s="32">
+    <row r="45" ht="19" customHeight="1" s="32">
       <c r="B45" s="1" t="n"/>
       <c r="C45" s="38" t="n"/>
       <c r="D45" s="39" t="n"/>
@@ -2582,8 +2582,8 @@
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="96"/>
+  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.4724409448818898" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -2591,7 +2591,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.2"/>
@@ -2610,7 +2610,7 @@
     <col width="0.88671875" customWidth="1" style="32" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="32">
+    <row r="1" ht="21" customHeight="1" s="32">
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="2" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="L4" s="30" t="n"/>
     </row>
-    <row r="5" ht="18" customHeight="1" s="32">
+    <row r="5" ht="19" customHeight="1" s="32">
       <c r="B5" s="1" t="n"/>
       <c r="C5" s="38" t="n"/>
       <c r="D5" s="39" t="n"/>
@@ -2698,7 +2698,7 @@
       <c r="K5" s="41" t="n"/>
       <c r="L5" s="42" t="n"/>
     </row>
-    <row r="6" ht="18" customHeight="1" s="32">
+    <row r="6" ht="19" customHeight="1" s="32">
       <c r="B6" s="1" t="n"/>
       <c r="C6" s="38" t="n"/>
       <c r="D6" s="39" t="n"/>
@@ -2711,7 +2711,7 @@
       <c r="K6" s="41" t="n"/>
       <c r="L6" s="42" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1" s="32">
+    <row r="7" ht="19" customHeight="1" s="32">
       <c r="B7" s="1" t="n"/>
       <c r="C7" s="38" t="n"/>
       <c r="D7" s="39" t="n"/>
@@ -2724,7 +2724,7 @@
       <c r="K7" s="41" t="n"/>
       <c r="L7" s="42" t="n"/>
     </row>
-    <row r="8" ht="18" customHeight="1" s="32">
+    <row r="8" ht="19" customHeight="1" s="32">
       <c r="B8" s="1" t="n"/>
       <c r="C8" s="38" t="n"/>
       <c r="D8" s="39" t="n"/>
@@ -2737,7 +2737,7 @@
       <c r="K8" s="41" t="n"/>
       <c r="L8" s="42" t="n"/>
     </row>
-    <row r="9" ht="18" customHeight="1" s="32">
+    <row r="9" ht="19" customHeight="1" s="32">
       <c r="B9" s="1" t="n"/>
       <c r="C9" s="38" t="n"/>
       <c r="D9" s="39" t="n"/>
@@ -2750,7 +2750,7 @@
       <c r="K9" s="41" t="n"/>
       <c r="L9" s="42" t="n"/>
     </row>
-    <row r="10" ht="18" customHeight="1" s="32">
+    <row r="10" ht="19" customHeight="1" s="32">
       <c r="B10" s="1" t="n"/>
       <c r="C10" s="38" t="n"/>
       <c r="D10" s="39" t="n"/>
@@ -2763,7 +2763,7 @@
       <c r="K10" s="41" t="n"/>
       <c r="L10" s="42" t="n"/>
     </row>
-    <row r="11" ht="18" customHeight="1" s="32">
+    <row r="11" ht="19" customHeight="1" s="32">
       <c r="B11" s="1" t="n"/>
       <c r="C11" s="38" t="n"/>
       <c r="D11" s="39" t="n"/>
@@ -2776,7 +2776,7 @@
       <c r="K11" s="41" t="n"/>
       <c r="L11" s="42" t="n"/>
     </row>
-    <row r="12" ht="18" customHeight="1" s="32">
+    <row r="12" ht="19" customHeight="1" s="32">
       <c r="B12" s="1" t="n"/>
       <c r="C12" s="38" t="n"/>
       <c r="D12" s="39" t="n"/>
@@ -2789,7 +2789,7 @@
       <c r="K12" s="41" t="n"/>
       <c r="L12" s="42" t="n"/>
     </row>
-    <row r="13" ht="18" customHeight="1" s="32">
+    <row r="13" ht="19" customHeight="1" s="32">
       <c r="B13" s="1" t="n"/>
       <c r="C13" s="38" t="n"/>
       <c r="D13" s="39" t="n"/>
@@ -2802,7 +2802,7 @@
       <c r="K13" s="41" t="n"/>
       <c r="L13" s="42" t="n"/>
     </row>
-    <row r="14" ht="18" customHeight="1" s="32">
+    <row r="14" ht="19" customHeight="1" s="32">
       <c r="B14" s="1" t="n"/>
       <c r="C14" s="38" t="n"/>
       <c r="D14" s="39" t="n"/>
@@ -2815,7 +2815,7 @@
       <c r="K14" s="41" t="n"/>
       <c r="L14" s="42" t="n"/>
     </row>
-    <row r="15" ht="18" customHeight="1" s="32">
+    <row r="15" ht="19" customHeight="1" s="32">
       <c r="B15" s="1" t="n"/>
       <c r="C15" s="38" t="n"/>
       <c r="D15" s="39" t="n"/>
@@ -2828,7 +2828,7 @@
       <c r="K15" s="41" t="n"/>
       <c r="L15" s="42" t="n"/>
     </row>
-    <row r="16" ht="18" customHeight="1" s="32">
+    <row r="16" ht="19" customHeight="1" s="32">
       <c r="B16" s="1" t="n"/>
       <c r="C16" s="38" t="n"/>
       <c r="D16" s="39" t="n"/>
@@ -2841,7 +2841,7 @@
       <c r="K16" s="41" t="n"/>
       <c r="L16" s="42" t="n"/>
     </row>
-    <row r="17" ht="18" customHeight="1" s="32">
+    <row r="17" ht="19" customHeight="1" s="32">
       <c r="B17" s="1" t="n"/>
       <c r="C17" s="38" t="n"/>
       <c r="D17" s="39" t="n"/>
@@ -2854,7 +2854,7 @@
       <c r="K17" s="41" t="n"/>
       <c r="L17" s="42" t="n"/>
     </row>
-    <row r="18" ht="18" customHeight="1" s="32">
+    <row r="18" ht="19" customHeight="1" s="32">
       <c r="B18" s="1" t="n"/>
       <c r="C18" s="38" t="n"/>
       <c r="D18" s="39" t="n"/>
@@ -2867,7 +2867,7 @@
       <c r="K18" s="41" t="n"/>
       <c r="L18" s="42" t="n"/>
     </row>
-    <row r="19" ht="18" customHeight="1" s="32">
+    <row r="19" ht="19" customHeight="1" s="32">
       <c r="B19" s="1" t="n"/>
       <c r="C19" s="38" t="n"/>
       <c r="D19" s="39" t="n"/>
@@ -2880,7 +2880,7 @@
       <c r="K19" s="41" t="n"/>
       <c r="L19" s="42" t="n"/>
     </row>
-    <row r="20" ht="18" customHeight="1" s="32">
+    <row r="20" ht="19" customHeight="1" s="32">
       <c r="B20" s="1" t="n"/>
       <c r="C20" s="38" t="n"/>
       <c r="D20" s="39" t="n"/>
@@ -2893,7 +2893,7 @@
       <c r="K20" s="41" t="n"/>
       <c r="L20" s="42" t="n"/>
     </row>
-    <row r="21" ht="18" customHeight="1" s="32">
+    <row r="21" ht="19" customHeight="1" s="32">
       <c r="B21" s="1" t="n"/>
       <c r="C21" s="38" t="n"/>
       <c r="D21" s="39" t="n"/>
@@ -2906,7 +2906,7 @@
       <c r="K21" s="41" t="n"/>
       <c r="L21" s="42" t="n"/>
     </row>
-    <row r="22" ht="18" customHeight="1" s="32">
+    <row r="22" ht="19" customHeight="1" s="32">
       <c r="B22" s="1" t="n"/>
       <c r="C22" s="38" t="n"/>
       <c r="D22" s="39" t="n"/>
@@ -2919,7 +2919,7 @@
       <c r="K22" s="41" t="n"/>
       <c r="L22" s="42" t="n"/>
     </row>
-    <row r="23" ht="18" customHeight="1" s="32">
+    <row r="23" ht="19" customHeight="1" s="32">
       <c r="B23" s="1" t="n"/>
       <c r="C23" s="38" t="n"/>
       <c r="D23" s="39" t="n"/>
@@ -2932,7 +2932,7 @@
       <c r="K23" s="41" t="n"/>
       <c r="L23" s="42" t="n"/>
     </row>
-    <row r="24" ht="18" customHeight="1" s="32">
+    <row r="24" ht="19" customHeight="1" s="32">
       <c r="B24" s="1" t="n"/>
       <c r="C24" s="38" t="n"/>
       <c r="D24" s="39" t="n"/>
@@ -2945,7 +2945,7 @@
       <c r="K24" s="41" t="n"/>
       <c r="L24" s="42" t="n"/>
     </row>
-    <row r="25" ht="18" customHeight="1" s="32">
+    <row r="25" ht="19" customHeight="1" s="32">
       <c r="B25" s="1" t="n"/>
       <c r="C25" s="38" t="n"/>
       <c r="D25" s="39" t="n"/>
@@ -2958,7 +2958,7 @@
       <c r="K25" s="41" t="n"/>
       <c r="L25" s="42" t="n"/>
     </row>
-    <row r="26" ht="18" customHeight="1" s="32">
+    <row r="26" ht="19" customHeight="1" s="32">
       <c r="B26" s="1" t="n"/>
       <c r="C26" s="38" t="n"/>
       <c r="D26" s="39" t="n"/>
@@ -2971,7 +2971,7 @@
       <c r="K26" s="41" t="n"/>
       <c r="L26" s="42" t="n"/>
     </row>
-    <row r="27" ht="18" customHeight="1" s="32">
+    <row r="27" ht="19" customHeight="1" s="32">
       <c r="B27" s="1" t="n"/>
       <c r="C27" s="38" t="n"/>
       <c r="D27" s="39" t="n"/>
@@ -2984,7 +2984,7 @@
       <c r="K27" s="41" t="n"/>
       <c r="L27" s="42" t="n"/>
     </row>
-    <row r="28" ht="18" customHeight="1" s="32">
+    <row r="28" ht="19" customHeight="1" s="32">
       <c r="B28" s="1" t="n"/>
       <c r="C28" s="38" t="n"/>
       <c r="D28" s="39" t="n"/>
@@ -2997,7 +2997,7 @@
       <c r="K28" s="41" t="n"/>
       <c r="L28" s="42" t="n"/>
     </row>
-    <row r="29" ht="18" customHeight="1" s="32">
+    <row r="29" ht="19" customHeight="1" s="32">
       <c r="B29" s="1" t="n"/>
       <c r="C29" s="67" t="n"/>
       <c r="D29" s="39" t="n"/>
@@ -3010,7 +3010,7 @@
       <c r="K29" s="41" t="n"/>
       <c r="L29" s="42" t="n"/>
     </row>
-    <row r="30" ht="18" customHeight="1" s="32">
+    <row r="30" ht="19" customHeight="1" s="32">
       <c r="B30" s="1" t="n"/>
       <c r="C30" s="67" t="n"/>
       <c r="D30" s="39" t="n"/>
@@ -3023,7 +3023,7 @@
       <c r="K30" s="41" t="n"/>
       <c r="L30" s="42" t="n"/>
     </row>
-    <row r="31" ht="18" customHeight="1" s="32">
+    <row r="31" ht="19" customHeight="1" s="32">
       <c r="B31" s="1" t="n"/>
       <c r="C31" s="67" t="n"/>
       <c r="D31" s="39" t="n"/>
@@ -3036,7 +3036,7 @@
       <c r="K31" s="41" t="n"/>
       <c r="L31" s="42" t="n"/>
     </row>
-    <row r="32" ht="18" customHeight="1" s="32">
+    <row r="32" ht="19" customHeight="1" s="32">
       <c r="B32" s="1" t="n"/>
       <c r="C32" s="67" t="n"/>
       <c r="D32" s="39" t="n"/>
@@ -3049,7 +3049,7 @@
       <c r="K32" s="41" t="n"/>
       <c r="L32" s="42" t="n"/>
     </row>
-    <row r="33" ht="18" customHeight="1" s="32">
+    <row r="33" ht="19" customHeight="1" s="32">
       <c r="B33" s="1" t="n"/>
       <c r="C33" s="67" t="n"/>
       <c r="D33" s="39" t="n"/>
@@ -3062,7 +3062,7 @@
       <c r="K33" s="41" t="n"/>
       <c r="L33" s="42" t="n"/>
     </row>
-    <row r="34" ht="18" customHeight="1" s="32">
+    <row r="34" ht="19" customHeight="1" s="32">
       <c r="B34" s="1" t="n"/>
       <c r="C34" s="67" t="n"/>
       <c r="D34" s="39" t="n"/>
@@ -3075,7 +3075,7 @@
       <c r="K34" s="41" t="n"/>
       <c r="L34" s="42" t="n"/>
     </row>
-    <row r="35" ht="18" customHeight="1" s="32">
+    <row r="35" ht="19" customHeight="1" s="32">
       <c r="B35" s="1" t="n"/>
       <c r="C35" s="38" t="n"/>
       <c r="D35" s="39" t="n"/>
@@ -3088,7 +3088,7 @@
       <c r="K35" s="41" t="n"/>
       <c r="L35" s="42" t="n"/>
     </row>
-    <row r="36" ht="18" customHeight="1" s="32">
+    <row r="36" ht="19" customHeight="1" s="32">
       <c r="B36" s="1" t="n"/>
       <c r="C36" s="38" t="n"/>
       <c r="D36" s="39" t="n"/>
@@ -3101,7 +3101,7 @@
       <c r="K36" s="41" t="n"/>
       <c r="L36" s="42" t="n"/>
     </row>
-    <row r="37" ht="18" customHeight="1" s="32">
+    <row r="37" ht="19" customHeight="1" s="32">
       <c r="B37" s="1" t="n"/>
       <c r="C37" s="38" t="n"/>
       <c r="D37" s="39" t="n"/>
@@ -3114,7 +3114,7 @@
       <c r="K37" s="41" t="n"/>
       <c r="L37" s="42" t="n"/>
     </row>
-    <row r="38" ht="18" customHeight="1" s="32">
+    <row r="38" ht="19" customHeight="1" s="32">
       <c r="B38" s="1" t="n"/>
       <c r="C38" s="38" t="n"/>
       <c r="D38" s="39" t="n"/>
@@ -3127,7 +3127,7 @@
       <c r="K38" s="41" t="n"/>
       <c r="L38" s="42" t="n"/>
     </row>
-    <row r="39" ht="18" customHeight="1" s="32">
+    <row r="39" ht="19" customHeight="1" s="32">
       <c r="B39" s="1" t="n"/>
       <c r="C39" s="38" t="n"/>
       <c r="D39" s="39" t="n"/>
@@ -3140,7 +3140,7 @@
       <c r="K39" s="41" t="n"/>
       <c r="L39" s="42" t="n"/>
     </row>
-    <row r="40" ht="18" customHeight="1" s="32">
+    <row r="40" ht="19" customHeight="1" s="32">
       <c r="B40" s="1" t="n"/>
       <c r="C40" s="38" t="n"/>
       <c r="D40" s="39" t="n"/>
@@ -3153,7 +3153,7 @@
       <c r="K40" s="41" t="n"/>
       <c r="L40" s="42" t="n"/>
     </row>
-    <row r="41" ht="18" customHeight="1" s="32">
+    <row r="41" ht="19" customHeight="1" s="32">
       <c r="B41" s="1" t="n"/>
       <c r="C41" s="38" t="n"/>
       <c r="D41" s="39" t="n"/>
@@ -3166,7 +3166,7 @@
       <c r="K41" s="41" t="n"/>
       <c r="L41" s="42" t="n"/>
     </row>
-    <row r="42" ht="18" customHeight="1" s="32">
+    <row r="42" ht="19" customHeight="1" s="32">
       <c r="B42" s="1" t="n"/>
       <c r="C42" s="38" t="n"/>
       <c r="D42" s="39" t="n"/>
@@ -3179,7 +3179,7 @@
       <c r="K42" s="41" t="n"/>
       <c r="L42" s="42" t="n"/>
     </row>
-    <row r="43" ht="18" customHeight="1" s="32">
+    <row r="43" ht="19" customHeight="1" s="32">
       <c r="B43" s="1" t="n"/>
       <c r="C43" s="38" t="n"/>
       <c r="D43" s="39" t="n"/>
@@ -3192,7 +3192,7 @@
       <c r="K43" s="41" t="n"/>
       <c r="L43" s="42" t="n"/>
     </row>
-    <row r="44" ht="18" customHeight="1" s="32">
+    <row r="44" ht="19" customHeight="1" s="32">
       <c r="B44" s="1" t="n"/>
       <c r="C44" s="38" t="n"/>
       <c r="D44" s="39" t="n"/>
@@ -3205,7 +3205,7 @@
       <c r="K44" s="41" t="n"/>
       <c r="L44" s="42" t="n"/>
     </row>
-    <row r="45" ht="18" customHeight="1" s="32">
+    <row r="45" ht="19" customHeight="1" s="32">
       <c r="B45" s="1" t="n"/>
       <c r="C45" s="38" t="n"/>
       <c r="D45" s="39" t="n"/>
@@ -3330,8 +3330,8 @@
     <mergeCell ref="K4:L4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="96"/>
+  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.4724409448818898" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -3339,7 +3339,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.2"/>
@@ -3358,7 +3358,7 @@
     <col width="0.88671875" customWidth="1" style="32" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="32">
+    <row r="1" ht="21" customHeight="1" s="32">
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="2" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
       </c>
       <c r="L4" s="30" t="n"/>
     </row>
-    <row r="5" ht="18" customHeight="1" s="32">
+    <row r="5" ht="19" customHeight="1" s="32">
       <c r="B5" s="1" t="n"/>
       <c r="C5" s="38" t="n"/>
       <c r="D5" s="39" t="n"/>
@@ -3446,7 +3446,7 @@
       <c r="K5" s="41" t="n"/>
       <c r="L5" s="42" t="n"/>
     </row>
-    <row r="6" ht="18" customHeight="1" s="32">
+    <row r="6" ht="19" customHeight="1" s="32">
       <c r="B6" s="1" t="n"/>
       <c r="C6" s="38" t="n"/>
       <c r="D6" s="39" t="n"/>
@@ -3459,7 +3459,7 @@
       <c r="K6" s="41" t="n"/>
       <c r="L6" s="42" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1" s="32">
+    <row r="7" ht="19" customHeight="1" s="32">
       <c r="B7" s="1" t="n"/>
       <c r="C7" s="38" t="n"/>
       <c r="D7" s="39" t="n"/>
@@ -3472,7 +3472,7 @@
       <c r="K7" s="41" t="n"/>
       <c r="L7" s="42" t="n"/>
     </row>
-    <row r="8" ht="18" customHeight="1" s="32">
+    <row r="8" ht="19" customHeight="1" s="32">
       <c r="B8" s="1" t="n"/>
       <c r="C8" s="38" t="n"/>
       <c r="D8" s="39" t="n"/>
@@ -3485,7 +3485,7 @@
       <c r="K8" s="41" t="n"/>
       <c r="L8" s="42" t="n"/>
     </row>
-    <row r="9" ht="18" customHeight="1" s="32">
+    <row r="9" ht="19" customHeight="1" s="32">
       <c r="B9" s="1" t="n"/>
       <c r="C9" s="38" t="n"/>
       <c r="D9" s="39" t="n"/>
@@ -3498,7 +3498,7 @@
       <c r="K9" s="41" t="n"/>
       <c r="L9" s="42" t="n"/>
     </row>
-    <row r="10" ht="18" customHeight="1" s="32">
+    <row r="10" ht="19" customHeight="1" s="32">
       <c r="B10" s="1" t="n"/>
       <c r="C10" s="38" t="n"/>
       <c r="D10" s="39" t="n"/>
@@ -3511,7 +3511,7 @@
       <c r="K10" s="41" t="n"/>
       <c r="L10" s="42" t="n"/>
     </row>
-    <row r="11" ht="18" customHeight="1" s="32">
+    <row r="11" ht="19" customHeight="1" s="32">
       <c r="B11" s="1" t="n"/>
       <c r="C11" s="38" t="n"/>
       <c r="D11" s="39" t="n"/>
@@ -3524,7 +3524,7 @@
       <c r="K11" s="41" t="n"/>
       <c r="L11" s="42" t="n"/>
     </row>
-    <row r="12" ht="18" customHeight="1" s="32">
+    <row r="12" ht="19" customHeight="1" s="32">
       <c r="B12" s="1" t="n"/>
       <c r="C12" s="38" t="n"/>
       <c r="D12" s="39" t="n"/>
@@ -3537,7 +3537,7 @@
       <c r="K12" s="41" t="n"/>
       <c r="L12" s="42" t="n"/>
     </row>
-    <row r="13" ht="18" customHeight="1" s="32">
+    <row r="13" ht="19" customHeight="1" s="32">
       <c r="B13" s="1" t="n"/>
       <c r="C13" s="38" t="n"/>
       <c r="D13" s="39" t="n"/>
@@ -3550,7 +3550,7 @@
       <c r="K13" s="41" t="n"/>
       <c r="L13" s="42" t="n"/>
     </row>
-    <row r="14" ht="18" customHeight="1" s="32">
+    <row r="14" ht="19" customHeight="1" s="32">
       <c r="B14" s="1" t="n"/>
       <c r="C14" s="38" t="n"/>
       <c r="D14" s="39" t="n"/>
@@ -3563,7 +3563,7 @@
       <c r="K14" s="41" t="n"/>
       <c r="L14" s="42" t="n"/>
     </row>
-    <row r="15" ht="18" customHeight="1" s="32">
+    <row r="15" ht="19" customHeight="1" s="32">
       <c r="B15" s="1" t="n"/>
       <c r="C15" s="38" t="n"/>
       <c r="D15" s="39" t="n"/>
@@ -3576,7 +3576,7 @@
       <c r="K15" s="41" t="n"/>
       <c r="L15" s="42" t="n"/>
     </row>
-    <row r="16" ht="18" customHeight="1" s="32">
+    <row r="16" ht="19" customHeight="1" s="32">
       <c r="B16" s="1" t="n"/>
       <c r="C16" s="38" t="n"/>
       <c r="D16" s="39" t="n"/>
@@ -3589,7 +3589,7 @@
       <c r="K16" s="41" t="n"/>
       <c r="L16" s="42" t="n"/>
     </row>
-    <row r="17" ht="18" customHeight="1" s="32">
+    <row r="17" ht="19" customHeight="1" s="32">
       <c r="B17" s="1" t="n"/>
       <c r="C17" s="38" t="n"/>
       <c r="D17" s="39" t="n"/>
@@ -3602,7 +3602,7 @@
       <c r="K17" s="41" t="n"/>
       <c r="L17" s="42" t="n"/>
     </row>
-    <row r="18" ht="18" customHeight="1" s="32">
+    <row r="18" ht="19" customHeight="1" s="32">
       <c r="B18" s="1" t="n"/>
       <c r="C18" s="38" t="n"/>
       <c r="D18" s="39" t="n"/>
@@ -3615,7 +3615,7 @@
       <c r="K18" s="41" t="n"/>
       <c r="L18" s="42" t="n"/>
     </row>
-    <row r="19" ht="18" customHeight="1" s="32">
+    <row r="19" ht="19" customHeight="1" s="32">
       <c r="B19" s="1" t="n"/>
       <c r="C19" s="38" t="n"/>
       <c r="D19" s="39" t="n"/>
@@ -3628,7 +3628,7 @@
       <c r="K19" s="41" t="n"/>
       <c r="L19" s="42" t="n"/>
     </row>
-    <row r="20" ht="18" customHeight="1" s="32">
+    <row r="20" ht="19" customHeight="1" s="32">
       <c r="B20" s="1" t="n"/>
       <c r="C20" s="38" t="n"/>
       <c r="D20" s="39" t="n"/>
@@ -3641,7 +3641,7 @@
       <c r="K20" s="41" t="n"/>
       <c r="L20" s="42" t="n"/>
     </row>
-    <row r="21" ht="18" customHeight="1" s="32">
+    <row r="21" ht="19" customHeight="1" s="32">
       <c r="B21" s="1" t="n"/>
       <c r="C21" s="38" t="n"/>
       <c r="D21" s="39" t="n"/>
@@ -3654,7 +3654,7 @@
       <c r="K21" s="41" t="n"/>
       <c r="L21" s="42" t="n"/>
     </row>
-    <row r="22" ht="18" customHeight="1" s="32">
+    <row r="22" ht="19" customHeight="1" s="32">
       <c r="B22" s="1" t="n"/>
       <c r="C22" s="38" t="n"/>
       <c r="D22" s="39" t="n"/>
@@ -3667,7 +3667,7 @@
       <c r="K22" s="41" t="n"/>
       <c r="L22" s="42" t="n"/>
     </row>
-    <row r="23" ht="18" customHeight="1" s="32">
+    <row r="23" ht="19" customHeight="1" s="32">
       <c r="B23" s="1" t="n"/>
       <c r="C23" s="38" t="n"/>
       <c r="D23" s="39" t="n"/>
@@ -3680,7 +3680,7 @@
       <c r="K23" s="41" t="n"/>
       <c r="L23" s="42" t="n"/>
     </row>
-    <row r="24" ht="18" customHeight="1" s="32">
+    <row r="24" ht="19" customHeight="1" s="32">
       <c r="B24" s="1" t="n"/>
       <c r="C24" s="38" t="n"/>
       <c r="D24" s="39" t="n"/>
@@ -3693,7 +3693,7 @@
       <c r="K24" s="41" t="n"/>
       <c r="L24" s="42" t="n"/>
     </row>
-    <row r="25" ht="18" customHeight="1" s="32">
+    <row r="25" ht="19" customHeight="1" s="32">
       <c r="B25" s="1" t="n"/>
       <c r="C25" s="38" t="n"/>
       <c r="D25" s="39" t="n"/>
@@ -3706,7 +3706,7 @@
       <c r="K25" s="41" t="n"/>
       <c r="L25" s="42" t="n"/>
     </row>
-    <row r="26" ht="18" customHeight="1" s="32">
+    <row r="26" ht="19" customHeight="1" s="32">
       <c r="B26" s="1" t="n"/>
       <c r="C26" s="38" t="n"/>
       <c r="D26" s="39" t="n"/>
@@ -3719,7 +3719,7 @@
       <c r="K26" s="41" t="n"/>
       <c r="L26" s="42" t="n"/>
     </row>
-    <row r="27" ht="18" customHeight="1" s="32">
+    <row r="27" ht="19" customHeight="1" s="32">
       <c r="B27" s="1" t="n"/>
       <c r="C27" s="38" t="n"/>
       <c r="D27" s="39" t="n"/>
@@ -3732,7 +3732,7 @@
       <c r="K27" s="41" t="n"/>
       <c r="L27" s="42" t="n"/>
     </row>
-    <row r="28" ht="18" customHeight="1" s="32">
+    <row r="28" ht="19" customHeight="1" s="32">
       <c r="B28" s="1" t="n"/>
       <c r="C28" s="38" t="n"/>
       <c r="D28" s="39" t="n"/>
@@ -3745,7 +3745,7 @@
       <c r="K28" s="41" t="n"/>
       <c r="L28" s="42" t="n"/>
     </row>
-    <row r="29" ht="18" customHeight="1" s="32">
+    <row r="29" ht="19" customHeight="1" s="32">
       <c r="B29" s="1" t="n"/>
       <c r="C29" s="67" t="n"/>
       <c r="D29" s="39" t="n"/>
@@ -3758,7 +3758,7 @@
       <c r="K29" s="41" t="n"/>
       <c r="L29" s="42" t="n"/>
     </row>
-    <row r="30" ht="18" customHeight="1" s="32">
+    <row r="30" ht="19" customHeight="1" s="32">
       <c r="B30" s="1" t="n"/>
       <c r="C30" s="67" t="n"/>
       <c r="D30" s="39" t="n"/>
@@ -3771,7 +3771,7 @@
       <c r="K30" s="41" t="n"/>
       <c r="L30" s="42" t="n"/>
     </row>
-    <row r="31" ht="18" customHeight="1" s="32">
+    <row r="31" ht="19" customHeight="1" s="32">
       <c r="B31" s="1" t="n"/>
       <c r="C31" s="67" t="n"/>
       <c r="D31" s="39" t="n"/>
@@ -3784,7 +3784,7 @@
       <c r="K31" s="41" t="n"/>
       <c r="L31" s="42" t="n"/>
     </row>
-    <row r="32" ht="18" customHeight="1" s="32">
+    <row r="32" ht="19" customHeight="1" s="32">
       <c r="B32" s="1" t="n"/>
       <c r="C32" s="67" t="n"/>
       <c r="D32" s="39" t="n"/>
@@ -3797,7 +3797,7 @@
       <c r="K32" s="41" t="n"/>
       <c r="L32" s="42" t="n"/>
     </row>
-    <row r="33" ht="18" customHeight="1" s="32">
+    <row r="33" ht="19" customHeight="1" s="32">
       <c r="B33" s="1" t="n"/>
       <c r="C33" s="67" t="n"/>
       <c r="D33" s="39" t="n"/>
@@ -3810,7 +3810,7 @@
       <c r="K33" s="41" t="n"/>
       <c r="L33" s="42" t="n"/>
     </row>
-    <row r="34" ht="18" customHeight="1" s="32">
+    <row r="34" ht="19" customHeight="1" s="32">
       <c r="B34" s="1" t="n"/>
       <c r="C34" s="67" t="n"/>
       <c r="D34" s="39" t="n"/>
@@ -3823,7 +3823,7 @@
       <c r="K34" s="41" t="n"/>
       <c r="L34" s="42" t="n"/>
     </row>
-    <row r="35" ht="18" customHeight="1" s="32">
+    <row r="35" ht="19" customHeight="1" s="32">
       <c r="B35" s="1" t="n"/>
       <c r="C35" s="38" t="n"/>
       <c r="D35" s="39" t="n"/>
@@ -3836,7 +3836,7 @@
       <c r="K35" s="41" t="n"/>
       <c r="L35" s="42" t="n"/>
     </row>
-    <row r="36" ht="18" customHeight="1" s="32">
+    <row r="36" ht="19" customHeight="1" s="32">
       <c r="B36" s="1" t="n"/>
       <c r="C36" s="38" t="n"/>
       <c r="D36" s="39" t="n"/>
@@ -3849,7 +3849,7 @@
       <c r="K36" s="41" t="n"/>
       <c r="L36" s="42" t="n"/>
     </row>
-    <row r="37" ht="18" customHeight="1" s="32">
+    <row r="37" ht="19" customHeight="1" s="32">
       <c r="B37" s="1" t="n"/>
       <c r="C37" s="38" t="n"/>
       <c r="D37" s="39" t="n"/>
@@ -3862,7 +3862,7 @@
       <c r="K37" s="41" t="n"/>
       <c r="L37" s="42" t="n"/>
     </row>
-    <row r="38" ht="18" customHeight="1" s="32">
+    <row r="38" ht="19" customHeight="1" s="32">
       <c r="B38" s="1" t="n"/>
       <c r="C38" s="38" t="n"/>
       <c r="D38" s="39" t="n"/>
@@ -3875,7 +3875,7 @@
       <c r="K38" s="41" t="n"/>
       <c r="L38" s="42" t="n"/>
     </row>
-    <row r="39" ht="18" customHeight="1" s="32">
+    <row r="39" ht="19" customHeight="1" s="32">
       <c r="B39" s="1" t="n"/>
       <c r="C39" s="38" t="n"/>
       <c r="D39" s="39" t="n"/>
@@ -3888,7 +3888,7 @@
       <c r="K39" s="41" t="n"/>
       <c r="L39" s="42" t="n"/>
     </row>
-    <row r="40" ht="18" customHeight="1" s="32">
+    <row r="40" ht="19" customHeight="1" s="32">
       <c r="B40" s="1" t="n"/>
       <c r="C40" s="38" t="n"/>
       <c r="D40" s="39" t="n"/>
@@ -3901,7 +3901,7 @@
       <c r="K40" s="41" t="n"/>
       <c r="L40" s="42" t="n"/>
     </row>
-    <row r="41" ht="18" customHeight="1" s="32">
+    <row r="41" ht="19" customHeight="1" s="32">
       <c r="B41" s="1" t="n"/>
       <c r="C41" s="38" t="n"/>
       <c r="D41" s="39" t="n"/>
@@ -3914,7 +3914,7 @@
       <c r="K41" s="41" t="n"/>
       <c r="L41" s="42" t="n"/>
     </row>
-    <row r="42" ht="18" customHeight="1" s="32">
+    <row r="42" ht="19" customHeight="1" s="32">
       <c r="B42" s="1" t="n"/>
       <c r="C42" s="38" t="n"/>
       <c r="D42" s="39" t="n"/>
@@ -3927,7 +3927,7 @@
       <c r="K42" s="41" t="n"/>
       <c r="L42" s="42" t="n"/>
     </row>
-    <row r="43" ht="18" customHeight="1" s="32">
+    <row r="43" ht="19" customHeight="1" s="32">
       <c r="B43" s="1" t="n"/>
       <c r="C43" s="38" t="n"/>
       <c r="D43" s="39" t="n"/>
@@ -3940,7 +3940,7 @@
       <c r="K43" s="41" t="n"/>
       <c r="L43" s="42" t="n"/>
     </row>
-    <row r="44" ht="18" customHeight="1" s="32">
+    <row r="44" ht="19" customHeight="1" s="32">
       <c r="B44" s="1" t="n"/>
       <c r="C44" s="38" t="n"/>
       <c r="D44" s="39" t="n"/>
@@ -3953,7 +3953,7 @@
       <c r="K44" s="41" t="n"/>
       <c r="L44" s="42" t="n"/>
     </row>
-    <row r="45" ht="18" customHeight="1" s="32">
+    <row r="45" ht="19" customHeight="1" s="32">
       <c r="B45" s="1" t="n"/>
       <c r="C45" s="38" t="n"/>
       <c r="D45" s="39" t="n"/>
@@ -4078,8 +4078,8 @@
     <mergeCell ref="K4:L4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="96"/>
+  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.4724409448818898" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -4087,7 +4087,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.2"/>
@@ -4106,7 +4106,7 @@
     <col width="0.88671875" customWidth="1" style="32" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="32">
+    <row r="1" ht="21" customHeight="1" s="32">
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="2" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="L4" s="30" t="n"/>
     </row>
-    <row r="5" ht="18" customHeight="1" s="32">
+    <row r="5" ht="19" customHeight="1" s="32">
       <c r="B5" s="1" t="n"/>
       <c r="C5" s="38" t="n"/>
       <c r="D5" s="39" t="n"/>
@@ -4194,7 +4194,7 @@
       <c r="K5" s="41" t="n"/>
       <c r="L5" s="42" t="n"/>
     </row>
-    <row r="6" ht="18" customHeight="1" s="32">
+    <row r="6" ht="19" customHeight="1" s="32">
       <c r="B6" s="1" t="n"/>
       <c r="C6" s="38" t="n"/>
       <c r="D6" s="39" t="n"/>
@@ -4207,7 +4207,7 @@
       <c r="K6" s="41" t="n"/>
       <c r="L6" s="42" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1" s="32">
+    <row r="7" ht="19" customHeight="1" s="32">
       <c r="B7" s="1" t="n"/>
       <c r="C7" s="38" t="n"/>
       <c r="D7" s="39" t="n"/>
@@ -4220,7 +4220,7 @@
       <c r="K7" s="41" t="n"/>
       <c r="L7" s="42" t="n"/>
     </row>
-    <row r="8" ht="18" customHeight="1" s="32">
+    <row r="8" ht="19" customHeight="1" s="32">
       <c r="B8" s="1" t="n"/>
       <c r="C8" s="38" t="n"/>
       <c r="D8" s="39" t="n"/>
@@ -4233,7 +4233,7 @@
       <c r="K8" s="41" t="n"/>
       <c r="L8" s="42" t="n"/>
     </row>
-    <row r="9" ht="18" customHeight="1" s="32">
+    <row r="9" ht="19" customHeight="1" s="32">
       <c r="B9" s="1" t="n"/>
       <c r="C9" s="38" t="n"/>
       <c r="D9" s="39" t="n"/>
@@ -4246,7 +4246,7 @@
       <c r="K9" s="41" t="n"/>
       <c r="L9" s="42" t="n"/>
     </row>
-    <row r="10" ht="18" customHeight="1" s="32">
+    <row r="10" ht="19" customHeight="1" s="32">
       <c r="B10" s="1" t="n"/>
       <c r="C10" s="38" t="n"/>
       <c r="D10" s="39" t="n"/>
@@ -4259,7 +4259,7 @@
       <c r="K10" s="41" t="n"/>
       <c r="L10" s="42" t="n"/>
     </row>
-    <row r="11" ht="18" customHeight="1" s="32">
+    <row r="11" ht="19" customHeight="1" s="32">
       <c r="B11" s="1" t="n"/>
       <c r="C11" s="38" t="n"/>
       <c r="D11" s="39" t="n"/>
@@ -4272,7 +4272,7 @@
       <c r="K11" s="41" t="n"/>
       <c r="L11" s="42" t="n"/>
     </row>
-    <row r="12" ht="18" customHeight="1" s="32">
+    <row r="12" ht="19" customHeight="1" s="32">
       <c r="B12" s="1" t="n"/>
       <c r="C12" s="38" t="n"/>
       <c r="D12" s="39" t="n"/>
@@ -4285,7 +4285,7 @@
       <c r="K12" s="41" t="n"/>
       <c r="L12" s="42" t="n"/>
     </row>
-    <row r="13" ht="18" customHeight="1" s="32">
+    <row r="13" ht="19" customHeight="1" s="32">
       <c r="B13" s="1" t="n"/>
       <c r="C13" s="38" t="n"/>
       <c r="D13" s="39" t="n"/>
@@ -4298,7 +4298,7 @@
       <c r="K13" s="41" t="n"/>
       <c r="L13" s="42" t="n"/>
     </row>
-    <row r="14" ht="18" customHeight="1" s="32">
+    <row r="14" ht="19" customHeight="1" s="32">
       <c r="B14" s="1" t="n"/>
       <c r="C14" s="38" t="n"/>
       <c r="D14" s="39" t="n"/>
@@ -4311,7 +4311,7 @@
       <c r="K14" s="41" t="n"/>
       <c r="L14" s="42" t="n"/>
     </row>
-    <row r="15" ht="18" customHeight="1" s="32">
+    <row r="15" ht="19" customHeight="1" s="32">
       <c r="B15" s="1" t="n"/>
       <c r="C15" s="38" t="n"/>
       <c r="D15" s="39" t="n"/>
@@ -4324,7 +4324,7 @@
       <c r="K15" s="41" t="n"/>
       <c r="L15" s="42" t="n"/>
     </row>
-    <row r="16" ht="18" customHeight="1" s="32">
+    <row r="16" ht="19" customHeight="1" s="32">
       <c r="B16" s="1" t="n"/>
       <c r="C16" s="38" t="n"/>
       <c r="D16" s="39" t="n"/>
@@ -4337,7 +4337,7 @@
       <c r="K16" s="41" t="n"/>
       <c r="L16" s="42" t="n"/>
     </row>
-    <row r="17" ht="18" customHeight="1" s="32">
+    <row r="17" ht="19" customHeight="1" s="32">
       <c r="B17" s="1" t="n"/>
       <c r="C17" s="38" t="n"/>
       <c r="D17" s="39" t="n"/>
@@ -4350,7 +4350,7 @@
       <c r="K17" s="41" t="n"/>
       <c r="L17" s="42" t="n"/>
     </row>
-    <row r="18" ht="18" customHeight="1" s="32">
+    <row r="18" ht="19" customHeight="1" s="32">
       <c r="B18" s="1" t="n"/>
       <c r="C18" s="38" t="n"/>
       <c r="D18" s="39" t="n"/>
@@ -4363,7 +4363,7 @@
       <c r="K18" s="41" t="n"/>
       <c r="L18" s="42" t="n"/>
     </row>
-    <row r="19" ht="18" customHeight="1" s="32">
+    <row r="19" ht="19" customHeight="1" s="32">
       <c r="B19" s="1" t="n"/>
       <c r="C19" s="38" t="n"/>
       <c r="D19" s="39" t="n"/>
@@ -4376,7 +4376,7 @@
       <c r="K19" s="41" t="n"/>
       <c r="L19" s="42" t="n"/>
     </row>
-    <row r="20" ht="18" customHeight="1" s="32">
+    <row r="20" ht="19" customHeight="1" s="32">
       <c r="B20" s="1" t="n"/>
       <c r="C20" s="38" t="n"/>
       <c r="D20" s="39" t="n"/>
@@ -4389,7 +4389,7 @@
       <c r="K20" s="41" t="n"/>
       <c r="L20" s="42" t="n"/>
     </row>
-    <row r="21" ht="18" customHeight="1" s="32">
+    <row r="21" ht="19" customHeight="1" s="32">
       <c r="B21" s="1" t="n"/>
       <c r="C21" s="38" t="n"/>
       <c r="D21" s="39" t="n"/>
@@ -4402,7 +4402,7 @@
       <c r="K21" s="41" t="n"/>
       <c r="L21" s="42" t="n"/>
     </row>
-    <row r="22" ht="18" customHeight="1" s="32">
+    <row r="22" ht="19" customHeight="1" s="32">
       <c r="B22" s="1" t="n"/>
       <c r="C22" s="38" t="n"/>
       <c r="D22" s="39" t="n"/>
@@ -4415,7 +4415,7 @@
       <c r="K22" s="41" t="n"/>
       <c r="L22" s="42" t="n"/>
     </row>
-    <row r="23" ht="18" customHeight="1" s="32">
+    <row r="23" ht="19" customHeight="1" s="32">
       <c r="B23" s="1" t="n"/>
       <c r="C23" s="38" t="n"/>
       <c r="D23" s="39" t="n"/>
@@ -4428,7 +4428,7 @@
       <c r="K23" s="41" t="n"/>
       <c r="L23" s="42" t="n"/>
     </row>
-    <row r="24" ht="18" customHeight="1" s="32">
+    <row r="24" ht="19" customHeight="1" s="32">
       <c r="B24" s="1" t="n"/>
       <c r="C24" s="38" t="n"/>
       <c r="D24" s="39" t="n"/>
@@ -4441,7 +4441,7 @@
       <c r="K24" s="41" t="n"/>
       <c r="L24" s="42" t="n"/>
     </row>
-    <row r="25" ht="18" customHeight="1" s="32">
+    <row r="25" ht="19" customHeight="1" s="32">
       <c r="B25" s="1" t="n"/>
       <c r="C25" s="38" t="n"/>
       <c r="D25" s="39" t="n"/>
@@ -4454,7 +4454,7 @@
       <c r="K25" s="41" t="n"/>
       <c r="L25" s="42" t="n"/>
     </row>
-    <row r="26" ht="18" customHeight="1" s="32">
+    <row r="26" ht="19" customHeight="1" s="32">
       <c r="B26" s="1" t="n"/>
       <c r="C26" s="38" t="n"/>
       <c r="D26" s="39" t="n"/>
@@ -4467,7 +4467,7 @@
       <c r="K26" s="41" t="n"/>
       <c r="L26" s="42" t="n"/>
     </row>
-    <row r="27" ht="18" customHeight="1" s="32">
+    <row r="27" ht="19" customHeight="1" s="32">
       <c r="B27" s="1" t="n"/>
       <c r="C27" s="38" t="n"/>
       <c r="D27" s="39" t="n"/>
@@ -4480,7 +4480,7 @@
       <c r="K27" s="41" t="n"/>
       <c r="L27" s="42" t="n"/>
     </row>
-    <row r="28" ht="18" customHeight="1" s="32">
+    <row r="28" ht="19" customHeight="1" s="32">
       <c r="B28" s="1" t="n"/>
       <c r="C28" s="38" t="n"/>
       <c r="D28" s="39" t="n"/>
@@ -4493,7 +4493,7 @@
       <c r="K28" s="41" t="n"/>
       <c r="L28" s="42" t="n"/>
     </row>
-    <row r="29" ht="18" customHeight="1" s="32">
+    <row r="29" ht="19" customHeight="1" s="32">
       <c r="B29" s="1" t="n"/>
       <c r="C29" s="67" t="n"/>
       <c r="D29" s="39" t="n"/>
@@ -4506,7 +4506,7 @@
       <c r="K29" s="41" t="n"/>
       <c r="L29" s="42" t="n"/>
     </row>
-    <row r="30" ht="18" customHeight="1" s="32">
+    <row r="30" ht="19" customHeight="1" s="32">
       <c r="B30" s="1" t="n"/>
       <c r="C30" s="67" t="n"/>
       <c r="D30" s="39" t="n"/>
@@ -4519,7 +4519,7 @@
       <c r="K30" s="41" t="n"/>
       <c r="L30" s="42" t="n"/>
     </row>
-    <row r="31" ht="18" customHeight="1" s="32">
+    <row r="31" ht="19" customHeight="1" s="32">
       <c r="B31" s="1" t="n"/>
       <c r="C31" s="67" t="n"/>
       <c r="D31" s="39" t="n"/>
@@ -4532,7 +4532,7 @@
       <c r="K31" s="41" t="n"/>
       <c r="L31" s="42" t="n"/>
     </row>
-    <row r="32" ht="18" customHeight="1" s="32">
+    <row r="32" ht="19" customHeight="1" s="32">
       <c r="B32" s="1" t="n"/>
       <c r="C32" s="67" t="n"/>
       <c r="D32" s="39" t="n"/>
@@ -4545,7 +4545,7 @@
       <c r="K32" s="41" t="n"/>
       <c r="L32" s="42" t="n"/>
     </row>
-    <row r="33" ht="18" customHeight="1" s="32">
+    <row r="33" ht="19" customHeight="1" s="32">
       <c r="B33" s="1" t="n"/>
       <c r="C33" s="67" t="n"/>
       <c r="D33" s="39" t="n"/>
@@ -4558,7 +4558,7 @@
       <c r="K33" s="41" t="n"/>
       <c r="L33" s="42" t="n"/>
     </row>
-    <row r="34" ht="18" customHeight="1" s="32">
+    <row r="34" ht="19" customHeight="1" s="32">
       <c r="B34" s="1" t="n"/>
       <c r="C34" s="67" t="n"/>
       <c r="D34" s="39" t="n"/>
@@ -4571,7 +4571,7 @@
       <c r="K34" s="41" t="n"/>
       <c r="L34" s="42" t="n"/>
     </row>
-    <row r="35" ht="18" customHeight="1" s="32">
+    <row r="35" ht="19" customHeight="1" s="32">
       <c r="B35" s="1" t="n"/>
       <c r="C35" s="38" t="n"/>
       <c r="D35" s="39" t="n"/>
@@ -4584,7 +4584,7 @@
       <c r="K35" s="41" t="n"/>
       <c r="L35" s="42" t="n"/>
     </row>
-    <row r="36" ht="18" customHeight="1" s="32">
+    <row r="36" ht="19" customHeight="1" s="32">
       <c r="B36" s="1" t="n"/>
       <c r="C36" s="38" t="n"/>
       <c r="D36" s="39" t="n"/>
@@ -4597,7 +4597,7 @@
       <c r="K36" s="41" t="n"/>
       <c r="L36" s="42" t="n"/>
     </row>
-    <row r="37" ht="18" customHeight="1" s="32">
+    <row r="37" ht="19" customHeight="1" s="32">
       <c r="B37" s="1" t="n"/>
       <c r="C37" s="38" t="n"/>
       <c r="D37" s="39" t="n"/>
@@ -4610,7 +4610,7 @@
       <c r="K37" s="41" t="n"/>
       <c r="L37" s="42" t="n"/>
     </row>
-    <row r="38" ht="18" customHeight="1" s="32">
+    <row r="38" ht="19" customHeight="1" s="32">
       <c r="B38" s="1" t="n"/>
       <c r="C38" s="38" t="n"/>
       <c r="D38" s="39" t="n"/>
@@ -4623,7 +4623,7 @@
       <c r="K38" s="41" t="n"/>
       <c r="L38" s="42" t="n"/>
     </row>
-    <row r="39" ht="18" customHeight="1" s="32">
+    <row r="39" ht="19" customHeight="1" s="32">
       <c r="B39" s="1" t="n"/>
       <c r="C39" s="38" t="n"/>
       <c r="D39" s="39" t="n"/>
@@ -4636,7 +4636,7 @@
       <c r="K39" s="41" t="n"/>
       <c r="L39" s="42" t="n"/>
     </row>
-    <row r="40" ht="18" customHeight="1" s="32">
+    <row r="40" ht="19" customHeight="1" s="32">
       <c r="B40" s="1" t="n"/>
       <c r="C40" s="38" t="n"/>
       <c r="D40" s="39" t="n"/>
@@ -4649,7 +4649,7 @@
       <c r="K40" s="41" t="n"/>
       <c r="L40" s="42" t="n"/>
     </row>
-    <row r="41" ht="18" customHeight="1" s="32">
+    <row r="41" ht="19" customHeight="1" s="32">
       <c r="B41" s="1" t="n"/>
       <c r="C41" s="38" t="n"/>
       <c r="D41" s="39" t="n"/>
@@ -4662,7 +4662,7 @@
       <c r="K41" s="41" t="n"/>
       <c r="L41" s="42" t="n"/>
     </row>
-    <row r="42" ht="18" customHeight="1" s="32">
+    <row r="42" ht="19" customHeight="1" s="32">
       <c r="B42" s="1" t="n"/>
       <c r="C42" s="38" t="n"/>
       <c r="D42" s="39" t="n"/>
@@ -4675,7 +4675,7 @@
       <c r="K42" s="41" t="n"/>
       <c r="L42" s="42" t="n"/>
     </row>
-    <row r="43" ht="18" customHeight="1" s="32">
+    <row r="43" ht="19" customHeight="1" s="32">
       <c r="B43" s="1" t="n"/>
       <c r="C43" s="38" t="n"/>
       <c r="D43" s="39" t="n"/>
@@ -4688,7 +4688,7 @@
       <c r="K43" s="41" t="n"/>
       <c r="L43" s="42" t="n"/>
     </row>
-    <row r="44" ht="18" customHeight="1" s="32">
+    <row r="44" ht="19" customHeight="1" s="32">
       <c r="B44" s="1" t="n"/>
       <c r="C44" s="38" t="n"/>
       <c r="D44" s="39" t="n"/>
@@ -4701,7 +4701,7 @@
       <c r="K44" s="41" t="n"/>
       <c r="L44" s="42" t="n"/>
     </row>
-    <row r="45" ht="18" customHeight="1" s="32">
+    <row r="45" ht="19" customHeight="1" s="32">
       <c r="B45" s="1" t="n"/>
       <c r="C45" s="38" t="n"/>
       <c r="D45" s="39" t="n"/>
@@ -4826,8 +4826,8 @@
     <mergeCell ref="K4:L4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="96"/>
+  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.4724409448818898" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -4835,7 +4835,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.2"/>
@@ -4854,7 +4854,7 @@
     <col width="0.88671875" customWidth="1" style="32" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="32">
+    <row r="1" ht="21" customHeight="1" s="32">
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="2" t="inlineStr">
         <is>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="L4" s="30" t="n"/>
     </row>
-    <row r="5" ht="18" customHeight="1" s="32">
+    <row r="5" ht="19" customHeight="1" s="32">
       <c r="B5" s="1" t="n"/>
       <c r="C5" s="38" t="n"/>
       <c r="D5" s="39" t="n"/>
@@ -4942,7 +4942,7 @@
       <c r="K5" s="41" t="n"/>
       <c r="L5" s="42" t="n"/>
     </row>
-    <row r="6" ht="18" customHeight="1" s="32">
+    <row r="6" ht="19" customHeight="1" s="32">
       <c r="B6" s="1" t="n"/>
       <c r="C6" s="38" t="n"/>
       <c r="D6" s="39" t="n"/>
@@ -4955,7 +4955,7 @@
       <c r="K6" s="41" t="n"/>
       <c r="L6" s="42" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1" s="32">
+    <row r="7" ht="19" customHeight="1" s="32">
       <c r="B7" s="1" t="n"/>
       <c r="C7" s="38" t="n"/>
       <c r="D7" s="39" t="n"/>
@@ -4968,7 +4968,7 @@
       <c r="K7" s="41" t="n"/>
       <c r="L7" s="42" t="n"/>
     </row>
-    <row r="8" ht="18" customHeight="1" s="32">
+    <row r="8" ht="19" customHeight="1" s="32">
       <c r="B8" s="1" t="n"/>
       <c r="C8" s="38" t="n"/>
       <c r="D8" s="39" t="n"/>
@@ -4981,7 +4981,7 @@
       <c r="K8" s="41" t="n"/>
       <c r="L8" s="42" t="n"/>
     </row>
-    <row r="9" ht="18" customHeight="1" s="32">
+    <row r="9" ht="19" customHeight="1" s="32">
       <c r="B9" s="1" t="n"/>
       <c r="C9" s="38" t="n"/>
       <c r="D9" s="39" t="n"/>
@@ -4994,7 +4994,7 @@
       <c r="K9" s="41" t="n"/>
       <c r="L9" s="42" t="n"/>
     </row>
-    <row r="10" ht="18" customHeight="1" s="32">
+    <row r="10" ht="19" customHeight="1" s="32">
       <c r="B10" s="1" t="n"/>
       <c r="C10" s="38" t="n"/>
       <c r="D10" s="39" t="n"/>
@@ -5007,7 +5007,7 @@
       <c r="K10" s="41" t="n"/>
       <c r="L10" s="42" t="n"/>
     </row>
-    <row r="11" ht="18" customHeight="1" s="32">
+    <row r="11" ht="19" customHeight="1" s="32">
       <c r="B11" s="1" t="n"/>
       <c r="C11" s="38" t="n"/>
       <c r="D11" s="39" t="n"/>
@@ -5020,7 +5020,7 @@
       <c r="K11" s="41" t="n"/>
       <c r="L11" s="42" t="n"/>
     </row>
-    <row r="12" ht="18" customHeight="1" s="32">
+    <row r="12" ht="19" customHeight="1" s="32">
       <c r="B12" s="1" t="n"/>
       <c r="C12" s="38" t="n"/>
       <c r="D12" s="39" t="n"/>
@@ -5033,7 +5033,7 @@
       <c r="K12" s="41" t="n"/>
       <c r="L12" s="42" t="n"/>
     </row>
-    <row r="13" ht="18" customHeight="1" s="32">
+    <row r="13" ht="19" customHeight="1" s="32">
       <c r="B13" s="1" t="n"/>
       <c r="C13" s="38" t="n"/>
       <c r="D13" s="39" t="n"/>
@@ -5046,7 +5046,7 @@
       <c r="K13" s="41" t="n"/>
       <c r="L13" s="42" t="n"/>
     </row>
-    <row r="14" ht="18" customHeight="1" s="32">
+    <row r="14" ht="19" customHeight="1" s="32">
       <c r="B14" s="1" t="n"/>
       <c r="C14" s="38" t="n"/>
       <c r="D14" s="39" t="n"/>
@@ -5059,7 +5059,7 @@
       <c r="K14" s="41" t="n"/>
       <c r="L14" s="42" t="n"/>
     </row>
-    <row r="15" ht="18" customHeight="1" s="32">
+    <row r="15" ht="19" customHeight="1" s="32">
       <c r="B15" s="1" t="n"/>
       <c r="C15" s="38" t="n"/>
       <c r="D15" s="39" t="n"/>
@@ -5072,7 +5072,7 @@
       <c r="K15" s="41" t="n"/>
       <c r="L15" s="42" t="n"/>
     </row>
-    <row r="16" ht="18" customHeight="1" s="32">
+    <row r="16" ht="19" customHeight="1" s="32">
       <c r="B16" s="1" t="n"/>
       <c r="C16" s="38" t="n"/>
       <c r="D16" s="39" t="n"/>
@@ -5085,7 +5085,7 @@
       <c r="K16" s="41" t="n"/>
       <c r="L16" s="42" t="n"/>
     </row>
-    <row r="17" ht="18" customHeight="1" s="32">
+    <row r="17" ht="19" customHeight="1" s="32">
       <c r="B17" s="1" t="n"/>
       <c r="C17" s="38" t="n"/>
       <c r="D17" s="39" t="n"/>
@@ -5098,7 +5098,7 @@
       <c r="K17" s="41" t="n"/>
       <c r="L17" s="42" t="n"/>
     </row>
-    <row r="18" ht="18" customHeight="1" s="32">
+    <row r="18" ht="19" customHeight="1" s="32">
       <c r="B18" s="1" t="n"/>
       <c r="C18" s="38" t="n"/>
       <c r="D18" s="39" t="n"/>
@@ -5111,7 +5111,7 @@
       <c r="K18" s="41" t="n"/>
       <c r="L18" s="42" t="n"/>
     </row>
-    <row r="19" ht="18" customHeight="1" s="32">
+    <row r="19" ht="19" customHeight="1" s="32">
       <c r="B19" s="1" t="n"/>
       <c r="C19" s="38" t="n"/>
       <c r="D19" s="39" t="n"/>
@@ -5124,7 +5124,7 @@
       <c r="K19" s="41" t="n"/>
       <c r="L19" s="42" t="n"/>
     </row>
-    <row r="20" ht="18" customHeight="1" s="32">
+    <row r="20" ht="19" customHeight="1" s="32">
       <c r="B20" s="1" t="n"/>
       <c r="C20" s="38" t="n"/>
       <c r="D20" s="39" t="n"/>
@@ -5137,7 +5137,7 @@
       <c r="K20" s="41" t="n"/>
       <c r="L20" s="42" t="n"/>
     </row>
-    <row r="21" ht="18" customHeight="1" s="32">
+    <row r="21" ht="19" customHeight="1" s="32">
       <c r="B21" s="1" t="n"/>
       <c r="C21" s="38" t="n"/>
       <c r="D21" s="39" t="n"/>
@@ -5150,7 +5150,7 @@
       <c r="K21" s="41" t="n"/>
       <c r="L21" s="42" t="n"/>
     </row>
-    <row r="22" ht="18" customHeight="1" s="32">
+    <row r="22" ht="19" customHeight="1" s="32">
       <c r="B22" s="1" t="n"/>
       <c r="C22" s="38" t="n"/>
       <c r="D22" s="39" t="n"/>
@@ -5163,7 +5163,7 @@
       <c r="K22" s="41" t="n"/>
       <c r="L22" s="42" t="n"/>
     </row>
-    <row r="23" ht="18" customHeight="1" s="32">
+    <row r="23" ht="19" customHeight="1" s="32">
       <c r="B23" s="1" t="n"/>
       <c r="C23" s="38" t="n"/>
       <c r="D23" s="39" t="n"/>
@@ -5176,7 +5176,7 @@
       <c r="K23" s="41" t="n"/>
       <c r="L23" s="42" t="n"/>
     </row>
-    <row r="24" ht="18" customHeight="1" s="32">
+    <row r="24" ht="19" customHeight="1" s="32">
       <c r="B24" s="1" t="n"/>
       <c r="C24" s="38" t="n"/>
       <c r="D24" s="39" t="n"/>
@@ -5189,7 +5189,7 @@
       <c r="K24" s="41" t="n"/>
       <c r="L24" s="42" t="n"/>
     </row>
-    <row r="25" ht="18" customHeight="1" s="32">
+    <row r="25" ht="19" customHeight="1" s="32">
       <c r="B25" s="1" t="n"/>
       <c r="C25" s="38" t="n"/>
       <c r="D25" s="39" t="n"/>
@@ -5202,7 +5202,7 @@
       <c r="K25" s="41" t="n"/>
       <c r="L25" s="42" t="n"/>
     </row>
-    <row r="26" ht="18" customHeight="1" s="32">
+    <row r="26" ht="19" customHeight="1" s="32">
       <c r="B26" s="1" t="n"/>
       <c r="C26" s="38" t="n"/>
       <c r="D26" s="39" t="n"/>
@@ -5215,7 +5215,7 @@
       <c r="K26" s="41" t="n"/>
       <c r="L26" s="42" t="n"/>
     </row>
-    <row r="27" ht="18" customHeight="1" s="32">
+    <row r="27" ht="19" customHeight="1" s="32">
       <c r="B27" s="1" t="n"/>
       <c r="C27" s="38" t="n"/>
       <c r="D27" s="39" t="n"/>
@@ -5228,7 +5228,7 @@
       <c r="K27" s="41" t="n"/>
       <c r="L27" s="42" t="n"/>
     </row>
-    <row r="28" ht="18" customHeight="1" s="32">
+    <row r="28" ht="19" customHeight="1" s="32">
       <c r="B28" s="1" t="n"/>
       <c r="C28" s="38" t="n"/>
       <c r="D28" s="39" t="n"/>
@@ -5241,7 +5241,7 @@
       <c r="K28" s="41" t="n"/>
       <c r="L28" s="42" t="n"/>
     </row>
-    <row r="29" ht="18" customHeight="1" s="32">
+    <row r="29" ht="19" customHeight="1" s="32">
       <c r="B29" s="1" t="n"/>
       <c r="C29" s="67" t="n"/>
       <c r="D29" s="39" t="n"/>
@@ -5254,7 +5254,7 @@
       <c r="K29" s="41" t="n"/>
       <c r="L29" s="42" t="n"/>
     </row>
-    <row r="30" ht="18" customHeight="1" s="32">
+    <row r="30" ht="19" customHeight="1" s="32">
       <c r="B30" s="1" t="n"/>
       <c r="C30" s="67" t="n"/>
       <c r="D30" s="39" t="n"/>
@@ -5267,7 +5267,7 @@
       <c r="K30" s="41" t="n"/>
       <c r="L30" s="42" t="n"/>
     </row>
-    <row r="31" ht="18" customHeight="1" s="32">
+    <row r="31" ht="19" customHeight="1" s="32">
       <c r="B31" s="1" t="n"/>
       <c r="C31" s="67" t="n"/>
       <c r="D31" s="39" t="n"/>
@@ -5280,7 +5280,7 @@
       <c r="K31" s="41" t="n"/>
       <c r="L31" s="42" t="n"/>
     </row>
-    <row r="32" ht="18" customHeight="1" s="32">
+    <row r="32" ht="19" customHeight="1" s="32">
       <c r="B32" s="1" t="n"/>
       <c r="C32" s="67" t="n"/>
       <c r="D32" s="39" t="n"/>
@@ -5293,7 +5293,7 @@
       <c r="K32" s="41" t="n"/>
       <c r="L32" s="42" t="n"/>
     </row>
-    <row r="33" ht="18" customHeight="1" s="32">
+    <row r="33" ht="19" customHeight="1" s="32">
       <c r="B33" s="1" t="n"/>
       <c r="C33" s="67" t="n"/>
       <c r="D33" s="39" t="n"/>
@@ -5306,7 +5306,7 @@
       <c r="K33" s="41" t="n"/>
       <c r="L33" s="42" t="n"/>
     </row>
-    <row r="34" ht="18" customHeight="1" s="32">
+    <row r="34" ht="19" customHeight="1" s="32">
       <c r="B34" s="1" t="n"/>
       <c r="C34" s="67" t="n"/>
       <c r="D34" s="39" t="n"/>
@@ -5319,7 +5319,7 @@
       <c r="K34" s="41" t="n"/>
       <c r="L34" s="42" t="n"/>
     </row>
-    <row r="35" ht="18" customHeight="1" s="32">
+    <row r="35" ht="19" customHeight="1" s="32">
       <c r="B35" s="1" t="n"/>
       <c r="C35" s="38" t="n"/>
       <c r="D35" s="39" t="n"/>
@@ -5332,7 +5332,7 @@
       <c r="K35" s="41" t="n"/>
       <c r="L35" s="42" t="n"/>
     </row>
-    <row r="36" ht="18" customHeight="1" s="32">
+    <row r="36" ht="19" customHeight="1" s="32">
       <c r="B36" s="1" t="n"/>
       <c r="C36" s="38" t="n"/>
       <c r="D36" s="39" t="n"/>
@@ -5345,7 +5345,7 @@
       <c r="K36" s="41" t="n"/>
       <c r="L36" s="42" t="n"/>
     </row>
-    <row r="37" ht="18" customHeight="1" s="32">
+    <row r="37" ht="19" customHeight="1" s="32">
       <c r="B37" s="1" t="n"/>
       <c r="C37" s="38" t="n"/>
       <c r="D37" s="39" t="n"/>
@@ -5358,7 +5358,7 @@
       <c r="K37" s="41" t="n"/>
       <c r="L37" s="42" t="n"/>
     </row>
-    <row r="38" ht="18" customHeight="1" s="32">
+    <row r="38" ht="19" customHeight="1" s="32">
       <c r="B38" s="1" t="n"/>
       <c r="C38" s="38" t="n"/>
       <c r="D38" s="39" t="n"/>
@@ -5371,7 +5371,7 @@
       <c r="K38" s="41" t="n"/>
       <c r="L38" s="42" t="n"/>
     </row>
-    <row r="39" ht="18" customHeight="1" s="32">
+    <row r="39" ht="19" customHeight="1" s="32">
       <c r="B39" s="1" t="n"/>
       <c r="C39" s="38" t="n"/>
       <c r="D39" s="39" t="n"/>
@@ -5384,7 +5384,7 @@
       <c r="K39" s="41" t="n"/>
       <c r="L39" s="42" t="n"/>
     </row>
-    <row r="40" ht="18" customHeight="1" s="32">
+    <row r="40" ht="19" customHeight="1" s="32">
       <c r="B40" s="1" t="n"/>
       <c r="C40" s="38" t="n"/>
       <c r="D40" s="39" t="n"/>
@@ -5397,7 +5397,7 @@
       <c r="K40" s="41" t="n"/>
       <c r="L40" s="42" t="n"/>
     </row>
-    <row r="41" ht="18" customHeight="1" s="32">
+    <row r="41" ht="19" customHeight="1" s="32">
       <c r="B41" s="1" t="n"/>
       <c r="C41" s="38" t="n"/>
       <c r="D41" s="39" t="n"/>
@@ -5410,7 +5410,7 @@
       <c r="K41" s="41" t="n"/>
       <c r="L41" s="42" t="n"/>
     </row>
-    <row r="42" ht="18" customHeight="1" s="32">
+    <row r="42" ht="19" customHeight="1" s="32">
       <c r="B42" s="1" t="n"/>
       <c r="C42" s="38" t="n"/>
       <c r="D42" s="39" t="n"/>
@@ -5423,7 +5423,7 @@
       <c r="K42" s="41" t="n"/>
       <c r="L42" s="42" t="n"/>
     </row>
-    <row r="43" ht="18" customHeight="1" s="32">
+    <row r="43" ht="19" customHeight="1" s="32">
       <c r="B43" s="1" t="n"/>
       <c r="C43" s="38" t="n"/>
       <c r="D43" s="39" t="n"/>
@@ -5436,7 +5436,7 @@
       <c r="K43" s="41" t="n"/>
       <c r="L43" s="42" t="n"/>
     </row>
-    <row r="44" ht="18" customHeight="1" s="32">
+    <row r="44" ht="19" customHeight="1" s="32">
       <c r="B44" s="1" t="n"/>
       <c r="C44" s="38" t="n"/>
       <c r="D44" s="39" t="n"/>
@@ -5449,7 +5449,7 @@
       <c r="K44" s="41" t="n"/>
       <c r="L44" s="42" t="n"/>
     </row>
-    <row r="45" ht="18" customHeight="1" s="32">
+    <row r="45" ht="19" customHeight="1" s="32">
       <c r="B45" s="1" t="n"/>
       <c r="C45" s="38" t="n"/>
       <c r="D45" s="39" t="n"/>
@@ -5574,8 +5574,8 @@
     <mergeCell ref="K4:L4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="96"/>
+  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.4724409448818898" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -5583,7 +5583,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.2"/>
@@ -5602,7 +5602,7 @@
     <col width="0.88671875" customWidth="1" style="32" min="13" max="13"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="32">
+    <row r="1" ht="21" customHeight="1" s="32">
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="2" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
       </c>
       <c r="L4" s="30" t="n"/>
     </row>
-    <row r="5" ht="18" customHeight="1" s="32">
+    <row r="5" ht="19" customHeight="1" s="32">
       <c r="B5" s="1" t="n"/>
       <c r="C5" s="38" t="n"/>
       <c r="D5" s="39" t="n"/>
@@ -5690,7 +5690,7 @@
       <c r="K5" s="41" t="n"/>
       <c r="L5" s="42" t="n"/>
     </row>
-    <row r="6" ht="18" customHeight="1" s="32">
+    <row r="6" ht="19" customHeight="1" s="32">
       <c r="B6" s="1" t="n"/>
       <c r="C6" s="38" t="n"/>
       <c r="D6" s="39" t="n"/>
@@ -5703,7 +5703,7 @@
       <c r="K6" s="41" t="n"/>
       <c r="L6" s="42" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1" s="32">
+    <row r="7" ht="19" customHeight="1" s="32">
       <c r="B7" s="1" t="n"/>
       <c r="C7" s="38" t="n"/>
       <c r="D7" s="39" t="n"/>
@@ -5716,7 +5716,7 @@
       <c r="K7" s="41" t="n"/>
       <c r="L7" s="42" t="n"/>
     </row>
-    <row r="8" ht="18" customHeight="1" s="32">
+    <row r="8" ht="19" customHeight="1" s="32">
       <c r="B8" s="1" t="n"/>
       <c r="C8" s="38" t="n"/>
       <c r="D8" s="39" t="n"/>
@@ -5729,7 +5729,7 @@
       <c r="K8" s="41" t="n"/>
       <c r="L8" s="42" t="n"/>
     </row>
-    <row r="9" ht="18" customHeight="1" s="32">
+    <row r="9" ht="19" customHeight="1" s="32">
       <c r="B9" s="1" t="n"/>
       <c r="C9" s="38" t="n"/>
       <c r="D9" s="39" t="n"/>
@@ -5742,7 +5742,7 @@
       <c r="K9" s="41" t="n"/>
       <c r="L9" s="42" t="n"/>
     </row>
-    <row r="10" ht="18" customHeight="1" s="32">
+    <row r="10" ht="19" customHeight="1" s="32">
       <c r="B10" s="1" t="n"/>
       <c r="C10" s="38" t="n"/>
       <c r="D10" s="39" t="n"/>
@@ -5755,7 +5755,7 @@
       <c r="K10" s="41" t="n"/>
       <c r="L10" s="42" t="n"/>
     </row>
-    <row r="11" ht="18" customHeight="1" s="32">
+    <row r="11" ht="19" customHeight="1" s="32">
       <c r="B11" s="1" t="n"/>
       <c r="C11" s="38" t="n"/>
       <c r="D11" s="39" t="n"/>
@@ -5768,7 +5768,7 @@
       <c r="K11" s="41" t="n"/>
       <c r="L11" s="42" t="n"/>
     </row>
-    <row r="12" ht="18" customHeight="1" s="32">
+    <row r="12" ht="19" customHeight="1" s="32">
       <c r="B12" s="1" t="n"/>
       <c r="C12" s="38" t="n"/>
       <c r="D12" s="39" t="n"/>
@@ -5781,7 +5781,7 @@
       <c r="K12" s="41" t="n"/>
       <c r="L12" s="42" t="n"/>
     </row>
-    <row r="13" ht="18" customHeight="1" s="32">
+    <row r="13" ht="19" customHeight="1" s="32">
       <c r="B13" s="1" t="n"/>
       <c r="C13" s="38" t="n"/>
       <c r="D13" s="39" t="n"/>
@@ -5794,7 +5794,7 @@
       <c r="K13" s="41" t="n"/>
       <c r="L13" s="42" t="n"/>
     </row>
-    <row r="14" ht="18" customHeight="1" s="32">
+    <row r="14" ht="19" customHeight="1" s="32">
       <c r="B14" s="1" t="n"/>
       <c r="C14" s="38" t="n"/>
       <c r="D14" s="39" t="n"/>
@@ -5807,7 +5807,7 @@
       <c r="K14" s="41" t="n"/>
       <c r="L14" s="42" t="n"/>
     </row>
-    <row r="15" ht="18" customHeight="1" s="32">
+    <row r="15" ht="19" customHeight="1" s="32">
       <c r="B15" s="1" t="n"/>
       <c r="C15" s="38" t="n"/>
       <c r="D15" s="39" t="n"/>
@@ -5820,7 +5820,7 @@
       <c r="K15" s="41" t="n"/>
       <c r="L15" s="42" t="n"/>
     </row>
-    <row r="16" ht="18" customHeight="1" s="32">
+    <row r="16" ht="19" customHeight="1" s="32">
       <c r="B16" s="1" t="n"/>
       <c r="C16" s="38" t="n"/>
       <c r="D16" s="39" t="n"/>
@@ -5833,7 +5833,7 @@
       <c r="K16" s="41" t="n"/>
       <c r="L16" s="42" t="n"/>
     </row>
-    <row r="17" ht="18" customHeight="1" s="32">
+    <row r="17" ht="19" customHeight="1" s="32">
       <c r="B17" s="1" t="n"/>
       <c r="C17" s="38" t="n"/>
       <c r="D17" s="39" t="n"/>
@@ -5846,7 +5846,7 @@
       <c r="K17" s="41" t="n"/>
       <c r="L17" s="42" t="n"/>
     </row>
-    <row r="18" ht="18" customHeight="1" s="32">
+    <row r="18" ht="19" customHeight="1" s="32">
       <c r="B18" s="1" t="n"/>
       <c r="C18" s="38" t="n"/>
       <c r="D18" s="39" t="n"/>
@@ -5859,7 +5859,7 @@
       <c r="K18" s="41" t="n"/>
       <c r="L18" s="42" t="n"/>
     </row>
-    <row r="19" ht="18" customHeight="1" s="32">
+    <row r="19" ht="19" customHeight="1" s="32">
       <c r="B19" s="1" t="n"/>
       <c r="C19" s="38" t="n"/>
       <c r="D19" s="39" t="n"/>
@@ -5872,7 +5872,7 @@
       <c r="K19" s="41" t="n"/>
       <c r="L19" s="42" t="n"/>
     </row>
-    <row r="20" ht="18" customHeight="1" s="32">
+    <row r="20" ht="19" customHeight="1" s="32">
       <c r="B20" s="1" t="n"/>
       <c r="C20" s="38" t="n"/>
       <c r="D20" s="39" t="n"/>
@@ -5885,7 +5885,7 @@
       <c r="K20" s="41" t="n"/>
       <c r="L20" s="42" t="n"/>
     </row>
-    <row r="21" ht="18" customHeight="1" s="32">
+    <row r="21" ht="19" customHeight="1" s="32">
       <c r="B21" s="1" t="n"/>
       <c r="C21" s="38" t="n"/>
       <c r="D21" s="39" t="n"/>
@@ -5898,7 +5898,7 @@
       <c r="K21" s="41" t="n"/>
       <c r="L21" s="42" t="n"/>
     </row>
-    <row r="22" ht="18" customHeight="1" s="32">
+    <row r="22" ht="19" customHeight="1" s="32">
       <c r="B22" s="1" t="n"/>
       <c r="C22" s="38" t="n"/>
       <c r="D22" s="39" t="n"/>
@@ -5911,7 +5911,7 @@
       <c r="K22" s="41" t="n"/>
       <c r="L22" s="42" t="n"/>
     </row>
-    <row r="23" ht="18" customHeight="1" s="32">
+    <row r="23" ht="19" customHeight="1" s="32">
       <c r="B23" s="1" t="n"/>
       <c r="C23" s="38" t="n"/>
       <c r="D23" s="39" t="n"/>
@@ -5924,7 +5924,7 @@
       <c r="K23" s="41" t="n"/>
       <c r="L23" s="42" t="n"/>
     </row>
-    <row r="24" ht="18" customHeight="1" s="32">
+    <row r="24" ht="19" customHeight="1" s="32">
       <c r="B24" s="1" t="n"/>
       <c r="C24" s="38" t="n"/>
       <c r="D24" s="39" t="n"/>
@@ -5937,7 +5937,7 @@
       <c r="K24" s="41" t="n"/>
       <c r="L24" s="42" t="n"/>
     </row>
-    <row r="25" ht="18" customHeight="1" s="32">
+    <row r="25" ht="19" customHeight="1" s="32">
       <c r="B25" s="1" t="n"/>
       <c r="C25" s="38" t="n"/>
       <c r="D25" s="39" t="n"/>
@@ -5950,7 +5950,7 @@
       <c r="K25" s="41" t="n"/>
       <c r="L25" s="42" t="n"/>
     </row>
-    <row r="26" ht="18" customHeight="1" s="32">
+    <row r="26" ht="19" customHeight="1" s="32">
       <c r="B26" s="1" t="n"/>
       <c r="C26" s="38" t="n"/>
       <c r="D26" s="39" t="n"/>
@@ -5963,7 +5963,7 @@
       <c r="K26" s="41" t="n"/>
       <c r="L26" s="42" t="n"/>
     </row>
-    <row r="27" ht="18" customHeight="1" s="32">
+    <row r="27" ht="19" customHeight="1" s="32">
       <c r="B27" s="1" t="n"/>
       <c r="C27" s="38" t="n"/>
       <c r="D27" s="39" t="n"/>
@@ -5976,7 +5976,7 @@
       <c r="K27" s="41" t="n"/>
       <c r="L27" s="42" t="n"/>
     </row>
-    <row r="28" ht="18" customHeight="1" s="32">
+    <row r="28" ht="19" customHeight="1" s="32">
       <c r="B28" s="1" t="n"/>
       <c r="C28" s="38" t="n"/>
       <c r="D28" s="39" t="n"/>
@@ -5989,7 +5989,7 @@
       <c r="K28" s="41" t="n"/>
       <c r="L28" s="42" t="n"/>
     </row>
-    <row r="29" ht="18" customHeight="1" s="32">
+    <row r="29" ht="19" customHeight="1" s="32">
       <c r="B29" s="1" t="n"/>
       <c r="C29" s="67" t="n"/>
       <c r="D29" s="39" t="n"/>
@@ -6002,7 +6002,7 @@
       <c r="K29" s="41" t="n"/>
       <c r="L29" s="42" t="n"/>
     </row>
-    <row r="30" ht="18" customHeight="1" s="32">
+    <row r="30" ht="19" customHeight="1" s="32">
       <c r="B30" s="1" t="n"/>
       <c r="C30" s="67" t="n"/>
       <c r="D30" s="39" t="n"/>
@@ -6015,7 +6015,7 @@
       <c r="K30" s="41" t="n"/>
       <c r="L30" s="42" t="n"/>
     </row>
-    <row r="31" ht="18" customHeight="1" s="32">
+    <row r="31" ht="19" customHeight="1" s="32">
       <c r="B31" s="1" t="n"/>
       <c r="C31" s="67" t="n"/>
       <c r="D31" s="39" t="n"/>
@@ -6028,7 +6028,7 @@
       <c r="K31" s="41" t="n"/>
       <c r="L31" s="42" t="n"/>
     </row>
-    <row r="32" ht="18" customHeight="1" s="32">
+    <row r="32" ht="19" customHeight="1" s="32">
       <c r="B32" s="1" t="n"/>
       <c r="C32" s="67" t="n"/>
       <c r="D32" s="39" t="n"/>
@@ -6041,7 +6041,7 @@
       <c r="K32" s="41" t="n"/>
       <c r="L32" s="42" t="n"/>
     </row>
-    <row r="33" ht="18" customHeight="1" s="32">
+    <row r="33" ht="19" customHeight="1" s="32">
       <c r="B33" s="1" t="n"/>
       <c r="C33" s="67" t="n"/>
       <c r="D33" s="39" t="n"/>
@@ -6054,7 +6054,7 @@
       <c r="K33" s="41" t="n"/>
       <c r="L33" s="42" t="n"/>
     </row>
-    <row r="34" ht="18" customHeight="1" s="32">
+    <row r="34" ht="19" customHeight="1" s="32">
       <c r="B34" s="1" t="n"/>
       <c r="C34" s="67" t="n"/>
       <c r="D34" s="39" t="n"/>
@@ -6067,7 +6067,7 @@
       <c r="K34" s="41" t="n"/>
       <c r="L34" s="42" t="n"/>
     </row>
-    <row r="35" ht="18" customHeight="1" s="32">
+    <row r="35" ht="19" customHeight="1" s="32">
       <c r="B35" s="1" t="n"/>
       <c r="C35" s="38" t="n"/>
       <c r="D35" s="39" t="n"/>
@@ -6080,7 +6080,7 @@
       <c r="K35" s="41" t="n"/>
       <c r="L35" s="42" t="n"/>
     </row>
-    <row r="36" ht="18" customHeight="1" s="32">
+    <row r="36" ht="19" customHeight="1" s="32">
       <c r="B36" s="1" t="n"/>
       <c r="C36" s="38" t="n"/>
       <c r="D36" s="39" t="n"/>
@@ -6093,7 +6093,7 @@
       <c r="K36" s="41" t="n"/>
       <c r="L36" s="42" t="n"/>
     </row>
-    <row r="37" ht="18" customHeight="1" s="32">
+    <row r="37" ht="19" customHeight="1" s="32">
       <c r="B37" s="1" t="n"/>
       <c r="C37" s="38" t="n"/>
       <c r="D37" s="39" t="n"/>
@@ -6106,7 +6106,7 @@
       <c r="K37" s="41" t="n"/>
       <c r="L37" s="42" t="n"/>
     </row>
-    <row r="38" ht="18" customHeight="1" s="32">
+    <row r="38" ht="19" customHeight="1" s="32">
       <c r="B38" s="1" t="n"/>
       <c r="C38" s="38" t="n"/>
       <c r="D38" s="39" t="n"/>
@@ -6119,7 +6119,7 @@
       <c r="K38" s="41" t="n"/>
       <c r="L38" s="42" t="n"/>
     </row>
-    <row r="39" ht="18" customHeight="1" s="32">
+    <row r="39" ht="19" customHeight="1" s="32">
       <c r="B39" s="1" t="n"/>
       <c r="C39" s="38" t="n"/>
       <c r="D39" s="39" t="n"/>
@@ -6132,7 +6132,7 @@
       <c r="K39" s="41" t="n"/>
       <c r="L39" s="42" t="n"/>
     </row>
-    <row r="40" ht="18" customHeight="1" s="32">
+    <row r="40" ht="19" customHeight="1" s="32">
       <c r="B40" s="1" t="n"/>
       <c r="C40" s="38" t="n"/>
       <c r="D40" s="39" t="n"/>
@@ -6145,7 +6145,7 @@
       <c r="K40" s="41" t="n"/>
       <c r="L40" s="42" t="n"/>
     </row>
-    <row r="41" ht="18" customHeight="1" s="32">
+    <row r="41" ht="19" customHeight="1" s="32">
       <c r="B41" s="1" t="n"/>
       <c r="C41" s="38" t="n"/>
       <c r="D41" s="39" t="n"/>
@@ -6158,7 +6158,7 @@
       <c r="K41" s="41" t="n"/>
       <c r="L41" s="42" t="n"/>
     </row>
-    <row r="42" ht="18" customHeight="1" s="32">
+    <row r="42" ht="19" customHeight="1" s="32">
       <c r="B42" s="1" t="n"/>
       <c r="C42" s="38" t="n"/>
       <c r="D42" s="39" t="n"/>
@@ -6171,7 +6171,7 @@
       <c r="K42" s="41" t="n"/>
       <c r="L42" s="42" t="n"/>
     </row>
-    <row r="43" ht="18" customHeight="1" s="32">
+    <row r="43" ht="19" customHeight="1" s="32">
       <c r="B43" s="1" t="n"/>
       <c r="C43" s="38" t="n"/>
       <c r="D43" s="39" t="n"/>
@@ -6184,7 +6184,7 @@
       <c r="K43" s="41" t="n"/>
       <c r="L43" s="42" t="n"/>
     </row>
-    <row r="44" ht="18" customHeight="1" s="32">
+    <row r="44" ht="19" customHeight="1" s="32">
       <c r="B44" s="1" t="n"/>
       <c r="C44" s="38" t="n"/>
       <c r="D44" s="39" t="n"/>
@@ -6197,7 +6197,7 @@
       <c r="K44" s="41" t="n"/>
       <c r="L44" s="42" t="n"/>
     </row>
-    <row r="45" ht="18" customHeight="1" s="32">
+    <row r="45" ht="19" customHeight="1" s="32">
       <c r="B45" s="1" t="n"/>
       <c r="C45" s="38" t="n"/>
       <c r="D45" s="39" t="n"/>
@@ -6322,7 +6322,7 @@
     <mergeCell ref="K4:L4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="96"/>
+  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.4724409448818898" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/template_estimate.xlsx
+++ b/template_estimate.xlsx
@@ -1018,7 +1018,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M47"/>
@@ -1831,7 +1830,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:L46"/>
@@ -2590,7 +2588,6 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:L46"/>
@@ -3338,7 +3335,6 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:L46"/>
@@ -4086,7 +4082,6 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:L46"/>
@@ -4834,7 +4829,6 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:L46"/>
@@ -5582,7 +5576,6 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:L46"/>

--- a/template_estimate.xlsx
+++ b/template_estimate.xlsx
@@ -149,7 +149,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="37">
     <border>
       <left/>
       <right/>
@@ -487,6 +487,53 @@
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border/>
+    <border>
+      <left style="hair"/>
+      <right style="hair"/>
+      <top style="hair"/>
+    </border>
+    <border>
+      <left style="hair"/>
+      <right style="hair"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="hair"/>
+      <right style="hair"/>
+      <top style="hair"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="hair"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair"/>
+      <right style="hair"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="hair"/>
+      <right style="hair"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <bottom/>
+    </border>
+    <border>
+      <right style="hair"/>
     </border>
   </borders>
   <cellStyleXfs count="3">
@@ -500,7 +547,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -681,6 +728,23 @@
     <xf numFmtId="3" fontId="10" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1200,9 +1264,9 @@
       <c r="G11" s="1" t="n"/>
       <c r="H11" s="1" t="n"/>
       <c r="I11" s="1" t="n"/>
-      <c r="J11" s="62" t="n"/>
-      <c r="K11" s="58" t="n"/>
-      <c r="L11" s="51" t="n"/>
+      <c r="J11" s="69" t="n"/>
+      <c r="K11" s="70" t="n"/>
+      <c r="L11" s="71" t="n"/>
     </row>
     <row r="12" ht="16.5" customHeight="1" s="32">
       <c r="B12" s="1" t="n"/>
@@ -1211,9 +1275,9 @@
       <c r="G12" s="1" t="n"/>
       <c r="H12" s="3" t="n"/>
       <c r="I12" s="1" t="n"/>
-      <c r="J12" s="63" t="n"/>
-      <c r="K12" s="52" t="n"/>
-      <c r="L12" s="52" t="n"/>
+      <c r="J12" s="77" t="n"/>
+      <c r="K12" s="72" t="n"/>
+      <c r="L12" s="72" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1" s="32">
       <c r="B13" s="1" t="n"/>
@@ -1230,9 +1294,9 @@
       <c r="E13" s="36" t="n"/>
       <c r="F13" s="36" t="n"/>
       <c r="G13" s="1" t="n"/>
-      <c r="J13" s="63" t="n"/>
-      <c r="K13" s="53" t="n"/>
-      <c r="L13" s="53" t="n"/>
+      <c r="J13" s="77" t="n"/>
+      <c r="K13" s="73" t="n"/>
+      <c r="L13" s="73" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1" s="32">
       <c r="B14" s="1" t="n"/>
@@ -1724,11 +1788,11 @@
     <mergeCell ref="I14:L14"/>
     <mergeCell ref="K24:L24"/>
     <mergeCell ref="K33:L33"/>
+    <mergeCell ref="L12:L13"/>
     <mergeCell ref="C45:G45"/>
     <mergeCell ref="K26:L26"/>
     <mergeCell ref="K35:L35"/>
     <mergeCell ref="C29:G29"/>
-    <mergeCell ref="L11:L13"/>
     <mergeCell ref="C44:G44"/>
     <mergeCell ref="C31:G31"/>
     <mergeCell ref="C40:G40"/>
@@ -1751,13 +1815,13 @@
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="K43:L43"/>
     <mergeCell ref="C46:G46"/>
+    <mergeCell ref="J12:J13"/>
     <mergeCell ref="K27:L27"/>
     <mergeCell ref="I7:L7"/>
     <mergeCell ref="C39:G39"/>
     <mergeCell ref="K17:L17"/>
     <mergeCell ref="C32:G32"/>
     <mergeCell ref="C38:G38"/>
-    <mergeCell ref="J11:J13"/>
     <mergeCell ref="K19:L19"/>
     <mergeCell ref="K16:L16"/>
     <mergeCell ref="K25:L25"/>
@@ -1776,7 +1840,6 @@
     <mergeCell ref="K31:L31"/>
     <mergeCell ref="K46:L46"/>
     <mergeCell ref="K40:L40"/>
-    <mergeCell ref="K11:K13"/>
     <mergeCell ref="K23:L23"/>
     <mergeCell ref="C6:E6"/>
     <mergeCell ref="J1:L1"/>
@@ -1792,6 +1855,7 @@
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="E10:F10"/>
     <mergeCell ref="C47:J47"/>
+    <mergeCell ref="K12:K13"/>
     <mergeCell ref="C41:G41"/>
     <mergeCell ref="K22:L22"/>
     <mergeCell ref="C43:G43"/>

--- a/template_estimate.xlsx
+++ b/template_estimate.xlsx
@@ -149,7 +149,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="37">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -535,6 +535,13 @@
     <border>
       <right style="hair"/>
     </border>
+    <border>
+      <left/>
+      <right style="hair"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
@@ -547,7 +554,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -745,6 +752,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1089,9 +1097,9 @@
   <cols>
     <col width="5.44140625" customWidth="1" style="32" min="1" max="1"/>
     <col width="0.88671875" customWidth="1" style="32" min="2" max="2"/>
-    <col width="11.109375" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
+    <col width="8.710000000000001" bestFit="1" customWidth="1" style="32" min="3" max="3"/>
     <col width="6.5546875" customWidth="1" style="32" min="4" max="4"/>
-    <col width="18.77734375" customWidth="1" style="32" min="5" max="5"/>
+    <col width="21.17671875" customWidth="1" style="32" min="5" max="5"/>
     <col width="7.77734375" customWidth="1" style="32" min="6" max="6"/>
     <col width="8.77734375" customWidth="1" style="32" min="7" max="7"/>
     <col width="6.21875" customWidth="1" style="32" min="8" max="8"/>
@@ -1276,8 +1284,8 @@
       <c r="H12" s="3" t="n"/>
       <c r="I12" s="1" t="n"/>
       <c r="J12" s="77" t="n"/>
-      <c r="K12" s="72" t="n"/>
-      <c r="L12" s="72" t="n"/>
+      <c r="K12" s="75" t="n"/>
+      <c r="L12" s="75" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1" s="32">
       <c r="B13" s="1" t="n"/>
@@ -1294,9 +1302,9 @@
       <c r="E13" s="36" t="n"/>
       <c r="F13" s="36" t="n"/>
       <c r="G13" s="1" t="n"/>
-      <c r="J13" s="77" t="n"/>
-      <c r="K13" s="73" t="n"/>
-      <c r="L13" s="73" t="n"/>
+      <c r="J13" s="78" t="n"/>
+      <c r="K13" s="76" t="n"/>
+      <c r="L13" s="76" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1" s="32">
       <c r="B14" s="1" t="n"/>
@@ -1988,7 +1996,7 @@
       </c>
       <c r="L4" s="30" t="n"/>
     </row>
-    <row r="5" ht="19" customHeight="1" s="32">
+    <row r="5" ht="18.5" customHeight="1" s="32">
       <c r="B5" s="1" t="n"/>
       <c r="C5" s="38" t="n"/>
       <c r="D5" s="39" t="n"/>
@@ -2001,7 +2009,7 @@
       <c r="K5" s="41" t="n"/>
       <c r="L5" s="42" t="n"/>
     </row>
-    <row r="6" ht="19" customHeight="1" s="32">
+    <row r="6" ht="18.5" customHeight="1" s="32">
       <c r="B6" s="1" t="n"/>
       <c r="C6" s="38" t="n"/>
       <c r="D6" s="39" t="n"/>
@@ -2014,7 +2022,7 @@
       <c r="K6" s="41" t="n"/>
       <c r="L6" s="42" t="n"/>
     </row>
-    <row r="7" ht="19" customHeight="1" s="32">
+    <row r="7" ht="18.5" customHeight="1" s="32">
       <c r="B7" s="1" t="n"/>
       <c r="C7" s="38" t="n"/>
       <c r="D7" s="39" t="n"/>
@@ -2027,7 +2035,7 @@
       <c r="K7" s="41" t="n"/>
       <c r="L7" s="42" t="n"/>
     </row>
-    <row r="8" ht="19" customHeight="1" s="32">
+    <row r="8" ht="18.5" customHeight="1" s="32">
       <c r="B8" s="1" t="n"/>
       <c r="C8" s="38" t="n"/>
       <c r="D8" s="39" t="n"/>
@@ -2040,7 +2048,7 @@
       <c r="K8" s="41" t="n"/>
       <c r="L8" s="42" t="n"/>
     </row>
-    <row r="9" ht="19" customHeight="1" s="32">
+    <row r="9" ht="18.5" customHeight="1" s="32">
       <c r="B9" s="1" t="n"/>
       <c r="C9" s="38" t="n"/>
       <c r="D9" s="39" t="n"/>
@@ -2053,7 +2061,7 @@
       <c r="K9" s="41" t="n"/>
       <c r="L9" s="42" t="n"/>
     </row>
-    <row r="10" ht="19" customHeight="1" s="32">
+    <row r="10" ht="18.5" customHeight="1" s="32">
       <c r="B10" s="1" t="n"/>
       <c r="C10" s="38" t="n"/>
       <c r="D10" s="39" t="n"/>
@@ -2066,7 +2074,7 @@
       <c r="K10" s="41" t="n"/>
       <c r="L10" s="42" t="n"/>
     </row>
-    <row r="11" ht="19" customHeight="1" s="32">
+    <row r="11" ht="18.5" customHeight="1" s="32">
       <c r="B11" s="1" t="n"/>
       <c r="C11" s="38" t="n"/>
       <c r="D11" s="39" t="n"/>
@@ -2079,7 +2087,7 @@
       <c r="K11" s="41" t="n"/>
       <c r="L11" s="42" t="n"/>
     </row>
-    <row r="12" ht="19" customHeight="1" s="32">
+    <row r="12" ht="18.5" customHeight="1" s="32">
       <c r="B12" s="1" t="n"/>
       <c r="C12" s="38" t="n"/>
       <c r="D12" s="39" t="n"/>
@@ -2092,7 +2100,7 @@
       <c r="K12" s="41" t="n"/>
       <c r="L12" s="42" t="n"/>
     </row>
-    <row r="13" ht="19" customHeight="1" s="32">
+    <row r="13" ht="18.5" customHeight="1" s="32">
       <c r="B13" s="1" t="n"/>
       <c r="C13" s="38" t="n"/>
       <c r="D13" s="39" t="n"/>
@@ -2105,7 +2113,7 @@
       <c r="K13" s="41" t="n"/>
       <c r="L13" s="42" t="n"/>
     </row>
-    <row r="14" ht="19" customHeight="1" s="32">
+    <row r="14" ht="18.5" customHeight="1" s="32">
       <c r="B14" s="1" t="n"/>
       <c r="C14" s="38" t="n"/>
       <c r="D14" s="39" t="n"/>
@@ -2118,7 +2126,7 @@
       <c r="K14" s="41" t="n"/>
       <c r="L14" s="42" t="n"/>
     </row>
-    <row r="15" ht="19" customHeight="1" s="32">
+    <row r="15" ht="18.5" customHeight="1" s="32">
       <c r="B15" s="1" t="n"/>
       <c r="C15" s="38" t="n"/>
       <c r="D15" s="39" t="n"/>
@@ -2131,7 +2139,7 @@
       <c r="K15" s="41" t="n"/>
       <c r="L15" s="42" t="n"/>
     </row>
-    <row r="16" ht="19" customHeight="1" s="32">
+    <row r="16" ht="18.5" customHeight="1" s="32">
       <c r="B16" s="1" t="n"/>
       <c r="C16" s="38" t="n"/>
       <c r="D16" s="39" t="n"/>
@@ -2144,7 +2152,7 @@
       <c r="K16" s="41" t="n"/>
       <c r="L16" s="42" t="n"/>
     </row>
-    <row r="17" ht="19" customHeight="1" s="32">
+    <row r="17" ht="18.5" customHeight="1" s="32">
       <c r="B17" s="1" t="n"/>
       <c r="C17" s="38" t="n"/>
       <c r="D17" s="39" t="n"/>
@@ -2157,7 +2165,7 @@
       <c r="K17" s="41" t="n"/>
       <c r="L17" s="42" t="n"/>
     </row>
-    <row r="18" ht="19" customHeight="1" s="32">
+    <row r="18" ht="18.5" customHeight="1" s="32">
       <c r="B18" s="1" t="n"/>
       <c r="C18" s="38" t="n"/>
       <c r="D18" s="39" t="n"/>
@@ -2170,7 +2178,7 @@
       <c r="K18" s="41" t="n"/>
       <c r="L18" s="42" t="n"/>
     </row>
-    <row r="19" ht="19" customHeight="1" s="32">
+    <row r="19" ht="18.5" customHeight="1" s="32">
       <c r="B19" s="1" t="n"/>
       <c r="C19" s="38" t="n"/>
       <c r="D19" s="39" t="n"/>
@@ -2183,7 +2191,7 @@
       <c r="K19" s="41" t="n"/>
       <c r="L19" s="42" t="n"/>
     </row>
-    <row r="20" ht="19" customHeight="1" s="32">
+    <row r="20" ht="18.5" customHeight="1" s="32">
       <c r="B20" s="1" t="n"/>
       <c r="C20" s="38" t="n"/>
       <c r="D20" s="39" t="n"/>
@@ -2196,7 +2204,7 @@
       <c r="K20" s="41" t="n"/>
       <c r="L20" s="42" t="n"/>
     </row>
-    <row r="21" ht="19" customHeight="1" s="32">
+    <row r="21" ht="18.5" customHeight="1" s="32">
       <c r="B21" s="1" t="n"/>
       <c r="C21" s="38" t="n"/>
       <c r="D21" s="39" t="n"/>
@@ -2209,7 +2217,7 @@
       <c r="K21" s="41" t="n"/>
       <c r="L21" s="42" t="n"/>
     </row>
-    <row r="22" ht="19" customHeight="1" s="32">
+    <row r="22" ht="18.5" customHeight="1" s="32">
       <c r="B22" s="1" t="n"/>
       <c r="C22" s="38" t="n"/>
       <c r="D22" s="39" t="n"/>
@@ -2222,7 +2230,7 @@
       <c r="K22" s="41" t="n"/>
       <c r="L22" s="42" t="n"/>
     </row>
-    <row r="23" ht="19" customHeight="1" s="32">
+    <row r="23" ht="18.5" customHeight="1" s="32">
       <c r="B23" s="1" t="n"/>
       <c r="C23" s="38" t="n"/>
       <c r="D23" s="39" t="n"/>
@@ -2235,7 +2243,7 @@
       <c r="K23" s="41" t="n"/>
       <c r="L23" s="42" t="n"/>
     </row>
-    <row r="24" ht="19" customHeight="1" s="32">
+    <row r="24" ht="18.5" customHeight="1" s="32">
       <c r="B24" s="1" t="n"/>
       <c r="C24" s="38" t="n"/>
       <c r="D24" s="39" t="n"/>
@@ -2248,7 +2256,7 @@
       <c r="K24" s="41" t="n"/>
       <c r="L24" s="42" t="n"/>
     </row>
-    <row r="25" ht="19" customHeight="1" s="32">
+    <row r="25" ht="18.5" customHeight="1" s="32">
       <c r="B25" s="1" t="n"/>
       <c r="C25" s="38" t="n"/>
       <c r="D25" s="39" t="n"/>
@@ -2261,7 +2269,7 @@
       <c r="K25" s="41" t="n"/>
       <c r="L25" s="42" t="n"/>
     </row>
-    <row r="26" ht="19" customHeight="1" s="32">
+    <row r="26" ht="18.5" customHeight="1" s="32">
       <c r="B26" s="1" t="n"/>
       <c r="C26" s="38" t="n"/>
       <c r="D26" s="39" t="n"/>
@@ -2274,7 +2282,7 @@
       <c r="K26" s="41" t="n"/>
       <c r="L26" s="42" t="n"/>
     </row>
-    <row r="27" ht="19" customHeight="1" s="32">
+    <row r="27" ht="18.5" customHeight="1" s="32">
       <c r="B27" s="1" t="n"/>
       <c r="C27" s="38" t="n"/>
       <c r="D27" s="39" t="n"/>
@@ -2287,7 +2295,7 @@
       <c r="K27" s="41" t="n"/>
       <c r="L27" s="42" t="n"/>
     </row>
-    <row r="28" ht="19" customHeight="1" s="32">
+    <row r="28" ht="18.5" customHeight="1" s="32">
       <c r="B28" s="1" t="n"/>
       <c r="C28" s="38" t="n"/>
       <c r="D28" s="39" t="n"/>
@@ -2300,7 +2308,7 @@
       <c r="K28" s="41" t="n"/>
       <c r="L28" s="42" t="n"/>
     </row>
-    <row r="29" ht="19" customHeight="1" s="32">
+    <row r="29" ht="18.5" customHeight="1" s="32">
       <c r="B29" s="1" t="n"/>
       <c r="C29" s="67" t="n"/>
       <c r="D29" s="39" t="n"/>
@@ -2313,7 +2321,7 @@
       <c r="K29" s="41" t="n"/>
       <c r="L29" s="42" t="n"/>
     </row>
-    <row r="30" ht="19" customHeight="1" s="32">
+    <row r="30" ht="18.5" customHeight="1" s="32">
       <c r="B30" s="1" t="n"/>
       <c r="C30" s="67" t="n"/>
       <c r="D30" s="39" t="n"/>
@@ -2326,7 +2334,7 @@
       <c r="K30" s="41" t="n"/>
       <c r="L30" s="42" t="n"/>
     </row>
-    <row r="31" ht="19" customHeight="1" s="32">
+    <row r="31" ht="18.5" customHeight="1" s="32">
       <c r="B31" s="1" t="n"/>
       <c r="C31" s="67" t="n"/>
       <c r="D31" s="39" t="n"/>
@@ -2339,7 +2347,7 @@
       <c r="K31" s="41" t="n"/>
       <c r="L31" s="42" t="n"/>
     </row>
-    <row r="32" ht="19" customHeight="1" s="32">
+    <row r="32" ht="18.5" customHeight="1" s="32">
       <c r="B32" s="1" t="n"/>
       <c r="C32" s="67" t="n"/>
       <c r="D32" s="39" t="n"/>
@@ -2352,7 +2360,7 @@
       <c r="K32" s="41" t="n"/>
       <c r="L32" s="42" t="n"/>
     </row>
-    <row r="33" ht="19" customHeight="1" s="32">
+    <row r="33" ht="18.5" customHeight="1" s="32">
       <c r="B33" s="1" t="n"/>
       <c r="C33" s="67" t="n"/>
       <c r="D33" s="39" t="n"/>
@@ -2365,7 +2373,7 @@
       <c r="K33" s="41" t="n"/>
       <c r="L33" s="42" t="n"/>
     </row>
-    <row r="34" ht="19" customHeight="1" s="32">
+    <row r="34" ht="18.5" customHeight="1" s="32">
       <c r="B34" s="1" t="n"/>
       <c r="C34" s="67" t="n"/>
       <c r="D34" s="39" t="n"/>
@@ -2378,7 +2386,7 @@
       <c r="K34" s="41" t="n"/>
       <c r="L34" s="42" t="n"/>
     </row>
-    <row r="35" ht="19" customHeight="1" s="32">
+    <row r="35" ht="18.5" customHeight="1" s="32">
       <c r="B35" s="1" t="n"/>
       <c r="C35" s="38" t="n"/>
       <c r="D35" s="39" t="n"/>
@@ -2391,7 +2399,7 @@
       <c r="K35" s="41" t="n"/>
       <c r="L35" s="42" t="n"/>
     </row>
-    <row r="36" ht="19" customHeight="1" s="32">
+    <row r="36" ht="18.5" customHeight="1" s="32">
       <c r="B36" s="1" t="n"/>
       <c r="C36" s="38" t="n"/>
       <c r="D36" s="39" t="n"/>
@@ -2404,7 +2412,7 @@
       <c r="K36" s="41" t="n"/>
       <c r="L36" s="42" t="n"/>
     </row>
-    <row r="37" ht="19" customHeight="1" s="32">
+    <row r="37" ht="18.5" customHeight="1" s="32">
       <c r="B37" s="1" t="n"/>
       <c r="C37" s="38" t="n"/>
       <c r="D37" s="39" t="n"/>
@@ -2417,7 +2425,7 @@
       <c r="K37" s="41" t="n"/>
       <c r="L37" s="42" t="n"/>
     </row>
-    <row r="38" ht="19" customHeight="1" s="32">
+    <row r="38" ht="18.5" customHeight="1" s="32">
       <c r="B38" s="1" t="n"/>
       <c r="C38" s="38" t="n"/>
       <c r="D38" s="39" t="n"/>
@@ -2430,7 +2438,7 @@
       <c r="K38" s="41" t="n"/>
       <c r="L38" s="42" t="n"/>
     </row>
-    <row r="39" ht="19" customHeight="1" s="32">
+    <row r="39" ht="18.5" customHeight="1" s="32">
       <c r="B39" s="1" t="n"/>
       <c r="C39" s="38" t="n"/>
       <c r="D39" s="39" t="n"/>
@@ -2443,7 +2451,7 @@
       <c r="K39" s="41" t="n"/>
       <c r="L39" s="42" t="n"/>
     </row>
-    <row r="40" ht="19" customHeight="1" s="32">
+    <row r="40" ht="18.5" customHeight="1" s="32">
       <c r="B40" s="1" t="n"/>
       <c r="C40" s="38" t="n"/>
       <c r="D40" s="39" t="n"/>
@@ -2456,7 +2464,7 @@
       <c r="K40" s="41" t="n"/>
       <c r="L40" s="42" t="n"/>
     </row>
-    <row r="41" ht="19" customHeight="1" s="32">
+    <row r="41" ht="18.5" customHeight="1" s="32">
       <c r="B41" s="1" t="n"/>
       <c r="C41" s="38" t="n"/>
       <c r="D41" s="39" t="n"/>
@@ -2469,7 +2477,7 @@
       <c r="K41" s="41" t="n"/>
       <c r="L41" s="42" t="n"/>
     </row>
-    <row r="42" ht="19" customHeight="1" s="32">
+    <row r="42" ht="18.5" customHeight="1" s="32">
       <c r="B42" s="1" t="n"/>
       <c r="C42" s="38" t="n"/>
       <c r="D42" s="39" t="n"/>
@@ -2482,7 +2490,7 @@
       <c r="K42" s="41" t="n"/>
       <c r="L42" s="42" t="n"/>
     </row>
-    <row r="43" ht="19" customHeight="1" s="32">
+    <row r="43" ht="18.5" customHeight="1" s="32">
       <c r="B43" s="1" t="n"/>
       <c r="C43" s="38" t="n"/>
       <c r="D43" s="39" t="n"/>
@@ -2495,7 +2503,7 @@
       <c r="K43" s="41" t="n"/>
       <c r="L43" s="42" t="n"/>
     </row>
-    <row r="44" ht="19" customHeight="1" s="32">
+    <row r="44" ht="18.5" customHeight="1" s="32">
       <c r="B44" s="1" t="n"/>
       <c r="C44" s="38" t="n"/>
       <c r="D44" s="39" t="n"/>
@@ -2508,7 +2516,7 @@
       <c r="K44" s="41" t="n"/>
       <c r="L44" s="42" t="n"/>
     </row>
-    <row r="45" ht="19" customHeight="1" s="32">
+    <row r="45" ht="18.5" customHeight="1" s="32">
       <c r="B45" s="1" t="n"/>
       <c r="C45" s="38" t="n"/>
       <c r="D45" s="39" t="n"/>
@@ -2746,7 +2754,7 @@
       </c>
       <c r="L4" s="30" t="n"/>
     </row>
-    <row r="5" ht="19" customHeight="1" s="32">
+    <row r="5" ht="18.5" customHeight="1" s="32">
       <c r="B5" s="1" t="n"/>
       <c r="C5" s="38" t="n"/>
       <c r="D5" s="39" t="n"/>
@@ -2759,7 +2767,7 @@
       <c r="K5" s="41" t="n"/>
       <c r="L5" s="42" t="n"/>
     </row>
-    <row r="6" ht="19" customHeight="1" s="32">
+    <row r="6" ht="18.5" customHeight="1" s="32">
       <c r="B6" s="1" t="n"/>
       <c r="C6" s="38" t="n"/>
       <c r="D6" s="39" t="n"/>
@@ -2772,7 +2780,7 @@
       <c r="K6" s="41" t="n"/>
       <c r="L6" s="42" t="n"/>
     </row>
-    <row r="7" ht="19" customHeight="1" s="32">
+    <row r="7" ht="18.5" customHeight="1" s="32">
       <c r="B7" s="1" t="n"/>
       <c r="C7" s="38" t="n"/>
       <c r="D7" s="39" t="n"/>
@@ -2785,7 +2793,7 @@
       <c r="K7" s="41" t="n"/>
       <c r="L7" s="42" t="n"/>
     </row>
-    <row r="8" ht="19" customHeight="1" s="32">
+    <row r="8" ht="18.5" customHeight="1" s="32">
       <c r="B8" s="1" t="n"/>
       <c r="C8" s="38" t="n"/>
       <c r="D8" s="39" t="n"/>
@@ -2798,7 +2806,7 @@
       <c r="K8" s="41" t="n"/>
       <c r="L8" s="42" t="n"/>
     </row>
-    <row r="9" ht="19" customHeight="1" s="32">
+    <row r="9" ht="18.5" customHeight="1" s="32">
       <c r="B9" s="1" t="n"/>
       <c r="C9" s="38" t="n"/>
       <c r="D9" s="39" t="n"/>
@@ -2811,7 +2819,7 @@
       <c r="K9" s="41" t="n"/>
       <c r="L9" s="42" t="n"/>
     </row>
-    <row r="10" ht="19" customHeight="1" s="32">
+    <row r="10" ht="18.5" customHeight="1" s="32">
       <c r="B10" s="1" t="n"/>
       <c r="C10" s="38" t="n"/>
       <c r="D10" s="39" t="n"/>
@@ -2824,7 +2832,7 @@
       <c r="K10" s="41" t="n"/>
       <c r="L10" s="42" t="n"/>
     </row>
-    <row r="11" ht="19" customHeight="1" s="32">
+    <row r="11" ht="18.5" customHeight="1" s="32">
       <c r="B11" s="1" t="n"/>
       <c r="C11" s="38" t="n"/>
       <c r="D11" s="39" t="n"/>
@@ -2837,7 +2845,7 @@
       <c r="K11" s="41" t="n"/>
       <c r="L11" s="42" t="n"/>
     </row>
-    <row r="12" ht="19" customHeight="1" s="32">
+    <row r="12" ht="18.5" customHeight="1" s="32">
       <c r="B12" s="1" t="n"/>
       <c r="C12" s="38" t="n"/>
       <c r="D12" s="39" t="n"/>
@@ -2850,7 +2858,7 @@
       <c r="K12" s="41" t="n"/>
       <c r="L12" s="42" t="n"/>
     </row>
-    <row r="13" ht="19" customHeight="1" s="32">
+    <row r="13" ht="18.5" customHeight="1" s="32">
       <c r="B13" s="1" t="n"/>
       <c r="C13" s="38" t="n"/>
       <c r="D13" s="39" t="n"/>
@@ -2863,7 +2871,7 @@
       <c r="K13" s="41" t="n"/>
       <c r="L13" s="42" t="n"/>
     </row>
-    <row r="14" ht="19" customHeight="1" s="32">
+    <row r="14" ht="18.5" customHeight="1" s="32">
       <c r="B14" s="1" t="n"/>
       <c r="C14" s="38" t="n"/>
       <c r="D14" s="39" t="n"/>
@@ -2876,7 +2884,7 @@
       <c r="K14" s="41" t="n"/>
       <c r="L14" s="42" t="n"/>
     </row>
-    <row r="15" ht="19" customHeight="1" s="32">
+    <row r="15" ht="18.5" customHeight="1" s="32">
       <c r="B15" s="1" t="n"/>
       <c r="C15" s="38" t="n"/>
       <c r="D15" s="39" t="n"/>
@@ -2889,7 +2897,7 @@
       <c r="K15" s="41" t="n"/>
       <c r="L15" s="42" t="n"/>
     </row>
-    <row r="16" ht="19" customHeight="1" s="32">
+    <row r="16" ht="18.5" customHeight="1" s="32">
       <c r="B16" s="1" t="n"/>
       <c r="C16" s="38" t="n"/>
       <c r="D16" s="39" t="n"/>
@@ -2902,7 +2910,7 @@
       <c r="K16" s="41" t="n"/>
       <c r="L16" s="42" t="n"/>
     </row>
-    <row r="17" ht="19" customHeight="1" s="32">
+    <row r="17" ht="18.5" customHeight="1" s="32">
       <c r="B17" s="1" t="n"/>
       <c r="C17" s="38" t="n"/>
       <c r="D17" s="39" t="n"/>
@@ -2915,7 +2923,7 @@
       <c r="K17" s="41" t="n"/>
       <c r="L17" s="42" t="n"/>
     </row>
-    <row r="18" ht="19" customHeight="1" s="32">
+    <row r="18" ht="18.5" customHeight="1" s="32">
       <c r="B18" s="1" t="n"/>
       <c r="C18" s="38" t="n"/>
       <c r="D18" s="39" t="n"/>
@@ -2928,7 +2936,7 @@
       <c r="K18" s="41" t="n"/>
       <c r="L18" s="42" t="n"/>
     </row>
-    <row r="19" ht="19" customHeight="1" s="32">
+    <row r="19" ht="18.5" customHeight="1" s="32">
       <c r="B19" s="1" t="n"/>
       <c r="C19" s="38" t="n"/>
       <c r="D19" s="39" t="n"/>
@@ -2941,7 +2949,7 @@
       <c r="K19" s="41" t="n"/>
       <c r="L19" s="42" t="n"/>
     </row>
-    <row r="20" ht="19" customHeight="1" s="32">
+    <row r="20" ht="18.5" customHeight="1" s="32">
       <c r="B20" s="1" t="n"/>
       <c r="C20" s="38" t="n"/>
       <c r="D20" s="39" t="n"/>
@@ -2954,7 +2962,7 @@
       <c r="K20" s="41" t="n"/>
       <c r="L20" s="42" t="n"/>
     </row>
-    <row r="21" ht="19" customHeight="1" s="32">
+    <row r="21" ht="18.5" customHeight="1" s="32">
       <c r="B21" s="1" t="n"/>
       <c r="C21" s="38" t="n"/>
       <c r="D21" s="39" t="n"/>
@@ -2967,7 +2975,7 @@
       <c r="K21" s="41" t="n"/>
       <c r="L21" s="42" t="n"/>
     </row>
-    <row r="22" ht="19" customHeight="1" s="32">
+    <row r="22" ht="18.5" customHeight="1" s="32">
       <c r="B22" s="1" t="n"/>
       <c r="C22" s="38" t="n"/>
       <c r="D22" s="39" t="n"/>
@@ -2980,7 +2988,7 @@
       <c r="K22" s="41" t="n"/>
       <c r="L22" s="42" t="n"/>
     </row>
-    <row r="23" ht="19" customHeight="1" s="32">
+    <row r="23" ht="18.5" customHeight="1" s="32">
       <c r="B23" s="1" t="n"/>
       <c r="C23" s="38" t="n"/>
       <c r="D23" s="39" t="n"/>
@@ -2993,7 +3001,7 @@
       <c r="K23" s="41" t="n"/>
       <c r="L23" s="42" t="n"/>
     </row>
-    <row r="24" ht="19" customHeight="1" s="32">
+    <row r="24" ht="18.5" customHeight="1" s="32">
       <c r="B24" s="1" t="n"/>
       <c r="C24" s="38" t="n"/>
       <c r="D24" s="39" t="n"/>
@@ -3006,7 +3014,7 @@
       <c r="K24" s="41" t="n"/>
       <c r="L24" s="42" t="n"/>
     </row>
-    <row r="25" ht="19" customHeight="1" s="32">
+    <row r="25" ht="18.5" customHeight="1" s="32">
       <c r="B25" s="1" t="n"/>
       <c r="C25" s="38" t="n"/>
       <c r="D25" s="39" t="n"/>
@@ -3019,7 +3027,7 @@
       <c r="K25" s="41" t="n"/>
       <c r="L25" s="42" t="n"/>
     </row>
-    <row r="26" ht="19" customHeight="1" s="32">
+    <row r="26" ht="18.5" customHeight="1" s="32">
       <c r="B26" s="1" t="n"/>
       <c r="C26" s="38" t="n"/>
       <c r="D26" s="39" t="n"/>
@@ -3032,7 +3040,7 @@
       <c r="K26" s="41" t="n"/>
       <c r="L26" s="42" t="n"/>
     </row>
-    <row r="27" ht="19" customHeight="1" s="32">
+    <row r="27" ht="18.5" customHeight="1" s="32">
       <c r="B27" s="1" t="n"/>
       <c r="C27" s="38" t="n"/>
       <c r="D27" s="39" t="n"/>
@@ -3045,7 +3053,7 @@
       <c r="K27" s="41" t="n"/>
       <c r="L27" s="42" t="n"/>
     </row>
-    <row r="28" ht="19" customHeight="1" s="32">
+    <row r="28" ht="18.5" customHeight="1" s="32">
       <c r="B28" s="1" t="n"/>
       <c r="C28" s="38" t="n"/>
       <c r="D28" s="39" t="n"/>
@@ -3058,7 +3066,7 @@
       <c r="K28" s="41" t="n"/>
       <c r="L28" s="42" t="n"/>
     </row>
-    <row r="29" ht="19" customHeight="1" s="32">
+    <row r="29" ht="18.5" customHeight="1" s="32">
       <c r="B29" s="1" t="n"/>
       <c r="C29" s="67" t="n"/>
       <c r="D29" s="39" t="n"/>
@@ -3071,7 +3079,7 @@
       <c r="K29" s="41" t="n"/>
       <c r="L29" s="42" t="n"/>
     </row>
-    <row r="30" ht="19" customHeight="1" s="32">
+    <row r="30" ht="18.5" customHeight="1" s="32">
       <c r="B30" s="1" t="n"/>
       <c r="C30" s="67" t="n"/>
       <c r="D30" s="39" t="n"/>
@@ -3084,7 +3092,7 @@
       <c r="K30" s="41" t="n"/>
       <c r="L30" s="42" t="n"/>
     </row>
-    <row r="31" ht="19" customHeight="1" s="32">
+    <row r="31" ht="18.5" customHeight="1" s="32">
       <c r="B31" s="1" t="n"/>
       <c r="C31" s="67" t="n"/>
       <c r="D31" s="39" t="n"/>
@@ -3097,7 +3105,7 @@
       <c r="K31" s="41" t="n"/>
       <c r="L31" s="42" t="n"/>
     </row>
-    <row r="32" ht="19" customHeight="1" s="32">
+    <row r="32" ht="18.5" customHeight="1" s="32">
       <c r="B32" s="1" t="n"/>
       <c r="C32" s="67" t="n"/>
       <c r="D32" s="39" t="n"/>
@@ -3110,7 +3118,7 @@
       <c r="K32" s="41" t="n"/>
       <c r="L32" s="42" t="n"/>
     </row>
-    <row r="33" ht="19" customHeight="1" s="32">
+    <row r="33" ht="18.5" customHeight="1" s="32">
       <c r="B33" s="1" t="n"/>
       <c r="C33" s="67" t="n"/>
       <c r="D33" s="39" t="n"/>
@@ -3123,7 +3131,7 @@
       <c r="K33" s="41" t="n"/>
       <c r="L33" s="42" t="n"/>
     </row>
-    <row r="34" ht="19" customHeight="1" s="32">
+    <row r="34" ht="18.5" customHeight="1" s="32">
       <c r="B34" s="1" t="n"/>
       <c r="C34" s="67" t="n"/>
       <c r="D34" s="39" t="n"/>
@@ -3136,7 +3144,7 @@
       <c r="K34" s="41" t="n"/>
       <c r="L34" s="42" t="n"/>
     </row>
-    <row r="35" ht="19" customHeight="1" s="32">
+    <row r="35" ht="18.5" customHeight="1" s="32">
       <c r="B35" s="1" t="n"/>
       <c r="C35" s="38" t="n"/>
       <c r="D35" s="39" t="n"/>
@@ -3149,7 +3157,7 @@
       <c r="K35" s="41" t="n"/>
       <c r="L35" s="42" t="n"/>
     </row>
-    <row r="36" ht="19" customHeight="1" s="32">
+    <row r="36" ht="18.5" customHeight="1" s="32">
       <c r="B36" s="1" t="n"/>
       <c r="C36" s="38" t="n"/>
       <c r="D36" s="39" t="n"/>
@@ -3162,7 +3170,7 @@
       <c r="K36" s="41" t="n"/>
       <c r="L36" s="42" t="n"/>
     </row>
-    <row r="37" ht="19" customHeight="1" s="32">
+    <row r="37" ht="18.5" customHeight="1" s="32">
       <c r="B37" s="1" t="n"/>
       <c r="C37" s="38" t="n"/>
       <c r="D37" s="39" t="n"/>
@@ -3175,7 +3183,7 @@
       <c r="K37" s="41" t="n"/>
       <c r="L37" s="42" t="n"/>
     </row>
-    <row r="38" ht="19" customHeight="1" s="32">
+    <row r="38" ht="18.5" customHeight="1" s="32">
       <c r="B38" s="1" t="n"/>
       <c r="C38" s="38" t="n"/>
       <c r="D38" s="39" t="n"/>
@@ -3188,7 +3196,7 @@
       <c r="K38" s="41" t="n"/>
       <c r="L38" s="42" t="n"/>
     </row>
-    <row r="39" ht="19" customHeight="1" s="32">
+    <row r="39" ht="18.5" customHeight="1" s="32">
       <c r="B39" s="1" t="n"/>
       <c r="C39" s="38" t="n"/>
       <c r="D39" s="39" t="n"/>
@@ -3201,7 +3209,7 @@
       <c r="K39" s="41" t="n"/>
       <c r="L39" s="42" t="n"/>
     </row>
-    <row r="40" ht="19" customHeight="1" s="32">
+    <row r="40" ht="18.5" customHeight="1" s="32">
       <c r="B40" s="1" t="n"/>
       <c r="C40" s="38" t="n"/>
       <c r="D40" s="39" t="n"/>
@@ -3214,7 +3222,7 @@
       <c r="K40" s="41" t="n"/>
       <c r="L40" s="42" t="n"/>
     </row>
-    <row r="41" ht="19" customHeight="1" s="32">
+    <row r="41" ht="18.5" customHeight="1" s="32">
       <c r="B41" s="1" t="n"/>
       <c r="C41" s="38" t="n"/>
       <c r="D41" s="39" t="n"/>
@@ -3227,7 +3235,7 @@
       <c r="K41" s="41" t="n"/>
       <c r="L41" s="42" t="n"/>
     </row>
-    <row r="42" ht="19" customHeight="1" s="32">
+    <row r="42" ht="18.5" customHeight="1" s="32">
       <c r="B42" s="1" t="n"/>
       <c r="C42" s="38" t="n"/>
       <c r="D42" s="39" t="n"/>
@@ -3240,7 +3248,7 @@
       <c r="K42" s="41" t="n"/>
       <c r="L42" s="42" t="n"/>
     </row>
-    <row r="43" ht="19" customHeight="1" s="32">
+    <row r="43" ht="18.5" customHeight="1" s="32">
       <c r="B43" s="1" t="n"/>
       <c r="C43" s="38" t="n"/>
       <c r="D43" s="39" t="n"/>
@@ -3253,7 +3261,7 @@
       <c r="K43" s="41" t="n"/>
       <c r="L43" s="42" t="n"/>
     </row>
-    <row r="44" ht="19" customHeight="1" s="32">
+    <row r="44" ht="18.5" customHeight="1" s="32">
       <c r="B44" s="1" t="n"/>
       <c r="C44" s="38" t="n"/>
       <c r="D44" s="39" t="n"/>
@@ -3266,7 +3274,7 @@
       <c r="K44" s="41" t="n"/>
       <c r="L44" s="42" t="n"/>
     </row>
-    <row r="45" ht="19" customHeight="1" s="32">
+    <row r="45" ht="18.5" customHeight="1" s="32">
       <c r="B45" s="1" t="n"/>
       <c r="C45" s="38" t="n"/>
       <c r="D45" s="39" t="n"/>
@@ -3493,7 +3501,7 @@
       </c>
       <c r="L4" s="30" t="n"/>
     </row>
-    <row r="5" ht="19" customHeight="1" s="32">
+    <row r="5" ht="18.5" customHeight="1" s="32">
       <c r="B5" s="1" t="n"/>
       <c r="C5" s="38" t="n"/>
       <c r="D5" s="39" t="n"/>
@@ -3506,7 +3514,7 @@
       <c r="K5" s="41" t="n"/>
       <c r="L5" s="42" t="n"/>
     </row>
-    <row r="6" ht="19" customHeight="1" s="32">
+    <row r="6" ht="18.5" customHeight="1" s="32">
       <c r="B6" s="1" t="n"/>
       <c r="C6" s="38" t="n"/>
       <c r="D6" s="39" t="n"/>
@@ -3519,7 +3527,7 @@
       <c r="K6" s="41" t="n"/>
       <c r="L6" s="42" t="n"/>
     </row>
-    <row r="7" ht="19" customHeight="1" s="32">
+    <row r="7" ht="18.5" customHeight="1" s="32">
       <c r="B7" s="1" t="n"/>
       <c r="C7" s="38" t="n"/>
       <c r="D7" s="39" t="n"/>
@@ -3532,7 +3540,7 @@
       <c r="K7" s="41" t="n"/>
       <c r="L7" s="42" t="n"/>
     </row>
-    <row r="8" ht="19" customHeight="1" s="32">
+    <row r="8" ht="18.5" customHeight="1" s="32">
       <c r="B8" s="1" t="n"/>
       <c r="C8" s="38" t="n"/>
       <c r="D8" s="39" t="n"/>
@@ -3545,7 +3553,7 @@
       <c r="K8" s="41" t="n"/>
       <c r="L8" s="42" t="n"/>
     </row>
-    <row r="9" ht="19" customHeight="1" s="32">
+    <row r="9" ht="18.5" customHeight="1" s="32">
       <c r="B9" s="1" t="n"/>
       <c r="C9" s="38" t="n"/>
       <c r="D9" s="39" t="n"/>
@@ -3558,7 +3566,7 @@
       <c r="K9" s="41" t="n"/>
       <c r="L9" s="42" t="n"/>
     </row>
-    <row r="10" ht="19" customHeight="1" s="32">
+    <row r="10" ht="18.5" customHeight="1" s="32">
       <c r="B10" s="1" t="n"/>
       <c r="C10" s="38" t="n"/>
       <c r="D10" s="39" t="n"/>
@@ -3571,7 +3579,7 @@
       <c r="K10" s="41" t="n"/>
       <c r="L10" s="42" t="n"/>
     </row>
-    <row r="11" ht="19" customHeight="1" s="32">
+    <row r="11" ht="18.5" customHeight="1" s="32">
       <c r="B11" s="1" t="n"/>
       <c r="C11" s="38" t="n"/>
       <c r="D11" s="39" t="n"/>
@@ -3584,7 +3592,7 @@
       <c r="K11" s="41" t="n"/>
       <c r="L11" s="42" t="n"/>
     </row>
-    <row r="12" ht="19" customHeight="1" s="32">
+    <row r="12" ht="18.5" customHeight="1" s="32">
       <c r="B12" s="1" t="n"/>
       <c r="C12" s="38" t="n"/>
       <c r="D12" s="39" t="n"/>
@@ -3597,7 +3605,7 @@
       <c r="K12" s="41" t="n"/>
       <c r="L12" s="42" t="n"/>
     </row>
-    <row r="13" ht="19" customHeight="1" s="32">
+    <row r="13" ht="18.5" customHeight="1" s="32">
       <c r="B13" s="1" t="n"/>
       <c r="C13" s="38" t="n"/>
       <c r="D13" s="39" t="n"/>
@@ -3610,7 +3618,7 @@
       <c r="K13" s="41" t="n"/>
       <c r="L13" s="42" t="n"/>
     </row>
-    <row r="14" ht="19" customHeight="1" s="32">
+    <row r="14" ht="18.5" customHeight="1" s="32">
       <c r="B14" s="1" t="n"/>
       <c r="C14" s="38" t="n"/>
       <c r="D14" s="39" t="n"/>
@@ -3623,7 +3631,7 @@
       <c r="K14" s="41" t="n"/>
       <c r="L14" s="42" t="n"/>
     </row>
-    <row r="15" ht="19" customHeight="1" s="32">
+    <row r="15" ht="18.5" customHeight="1" s="32">
       <c r="B15" s="1" t="n"/>
       <c r="C15" s="38" t="n"/>
       <c r="D15" s="39" t="n"/>
@@ -3636,7 +3644,7 @@
       <c r="K15" s="41" t="n"/>
       <c r="L15" s="42" t="n"/>
     </row>
-    <row r="16" ht="19" customHeight="1" s="32">
+    <row r="16" ht="18.5" customHeight="1" s="32">
       <c r="B16" s="1" t="n"/>
       <c r="C16" s="38" t="n"/>
       <c r="D16" s="39" t="n"/>
@@ -3649,7 +3657,7 @@
       <c r="K16" s="41" t="n"/>
       <c r="L16" s="42" t="n"/>
     </row>
-    <row r="17" ht="19" customHeight="1" s="32">
+    <row r="17" ht="18.5" customHeight="1" s="32">
       <c r="B17" s="1" t="n"/>
       <c r="C17" s="38" t="n"/>
       <c r="D17" s="39" t="n"/>
@@ -3662,7 +3670,7 @@
       <c r="K17" s="41" t="n"/>
       <c r="L17" s="42" t="n"/>
     </row>
-    <row r="18" ht="19" customHeight="1" s="32">
+    <row r="18" ht="18.5" customHeight="1" s="32">
       <c r="B18" s="1" t="n"/>
       <c r="C18" s="38" t="n"/>
       <c r="D18" s="39" t="n"/>
@@ -3675,7 +3683,7 @@
       <c r="K18" s="41" t="n"/>
       <c r="L18" s="42" t="n"/>
     </row>
-    <row r="19" ht="19" customHeight="1" s="32">
+    <row r="19" ht="18.5" customHeight="1" s="32">
       <c r="B19" s="1" t="n"/>
       <c r="C19" s="38" t="n"/>
       <c r="D19" s="39" t="n"/>
@@ -3688,7 +3696,7 @@
       <c r="K19" s="41" t="n"/>
       <c r="L19" s="42" t="n"/>
     </row>
-    <row r="20" ht="19" customHeight="1" s="32">
+    <row r="20" ht="18.5" customHeight="1" s="32">
       <c r="B20" s="1" t="n"/>
       <c r="C20" s="38" t="n"/>
       <c r="D20" s="39" t="n"/>
@@ -3701,7 +3709,7 @@
       <c r="K20" s="41" t="n"/>
       <c r="L20" s="42" t="n"/>
     </row>
-    <row r="21" ht="19" customHeight="1" s="32">
+    <row r="21" ht="18.5" customHeight="1" s="32">
       <c r="B21" s="1" t="n"/>
       <c r="C21" s="38" t="n"/>
       <c r="D21" s="39" t="n"/>
@@ -3714,7 +3722,7 @@
       <c r="K21" s="41" t="n"/>
       <c r="L21" s="42" t="n"/>
     </row>
-    <row r="22" ht="19" customHeight="1" s="32">
+    <row r="22" ht="18.5" customHeight="1" s="32">
       <c r="B22" s="1" t="n"/>
       <c r="C22" s="38" t="n"/>
       <c r="D22" s="39" t="n"/>
@@ -3727,7 +3735,7 @@
       <c r="K22" s="41" t="n"/>
       <c r="L22" s="42" t="n"/>
     </row>
-    <row r="23" ht="19" customHeight="1" s="32">
+    <row r="23" ht="18.5" customHeight="1" s="32">
       <c r="B23" s="1" t="n"/>
       <c r="C23" s="38" t="n"/>
       <c r="D23" s="39" t="n"/>
@@ -3740,7 +3748,7 @@
       <c r="K23" s="41" t="n"/>
       <c r="L23" s="42" t="n"/>
     </row>
-    <row r="24" ht="19" customHeight="1" s="32">
+    <row r="24" ht="18.5" customHeight="1" s="32">
       <c r="B24" s="1" t="n"/>
       <c r="C24" s="38" t="n"/>
       <c r="D24" s="39" t="n"/>
@@ -3753,7 +3761,7 @@
       <c r="K24" s="41" t="n"/>
       <c r="L24" s="42" t="n"/>
     </row>
-    <row r="25" ht="19" customHeight="1" s="32">
+    <row r="25" ht="18.5" customHeight="1" s="32">
       <c r="B25" s="1" t="n"/>
       <c r="C25" s="38" t="n"/>
       <c r="D25" s="39" t="n"/>
@@ -3766,7 +3774,7 @@
       <c r="K25" s="41" t="n"/>
       <c r="L25" s="42" t="n"/>
     </row>
-    <row r="26" ht="19" customHeight="1" s="32">
+    <row r="26" ht="18.5" customHeight="1" s="32">
       <c r="B26" s="1" t="n"/>
       <c r="C26" s="38" t="n"/>
       <c r="D26" s="39" t="n"/>
@@ -3779,7 +3787,7 @@
       <c r="K26" s="41" t="n"/>
       <c r="L26" s="42" t="n"/>
     </row>
-    <row r="27" ht="19" customHeight="1" s="32">
+    <row r="27" ht="18.5" customHeight="1" s="32">
       <c r="B27" s="1" t="n"/>
       <c r="C27" s="38" t="n"/>
       <c r="D27" s="39" t="n"/>
@@ -3792,7 +3800,7 @@
       <c r="K27" s="41" t="n"/>
       <c r="L27" s="42" t="n"/>
     </row>
-    <row r="28" ht="19" customHeight="1" s="32">
+    <row r="28" ht="18.5" customHeight="1" s="32">
       <c r="B28" s="1" t="n"/>
       <c r="C28" s="38" t="n"/>
       <c r="D28" s="39" t="n"/>
@@ -3805,7 +3813,7 @@
       <c r="K28" s="41" t="n"/>
       <c r="L28" s="42" t="n"/>
     </row>
-    <row r="29" ht="19" customHeight="1" s="32">
+    <row r="29" ht="18.5" customHeight="1" s="32">
       <c r="B29" s="1" t="n"/>
       <c r="C29" s="67" t="n"/>
       <c r="D29" s="39" t="n"/>
@@ -3818,7 +3826,7 @@
       <c r="K29" s="41" t="n"/>
       <c r="L29" s="42" t="n"/>
     </row>
-    <row r="30" ht="19" customHeight="1" s="32">
+    <row r="30" ht="18.5" customHeight="1" s="32">
       <c r="B30" s="1" t="n"/>
       <c r="C30" s="67" t="n"/>
       <c r="D30" s="39" t="n"/>
@@ -3831,7 +3839,7 @@
       <c r="K30" s="41" t="n"/>
       <c r="L30" s="42" t="n"/>
     </row>
-    <row r="31" ht="19" customHeight="1" s="32">
+    <row r="31" ht="18.5" customHeight="1" s="32">
       <c r="B31" s="1" t="n"/>
       <c r="C31" s="67" t="n"/>
       <c r="D31" s="39" t="n"/>
@@ -3844,7 +3852,7 @@
       <c r="K31" s="41" t="n"/>
       <c r="L31" s="42" t="n"/>
     </row>
-    <row r="32" ht="19" customHeight="1" s="32">
+    <row r="32" ht="18.5" customHeight="1" s="32">
       <c r="B32" s="1" t="n"/>
       <c r="C32" s="67" t="n"/>
       <c r="D32" s="39" t="n"/>
@@ -3857,7 +3865,7 @@
       <c r="K32" s="41" t="n"/>
       <c r="L32" s="42" t="n"/>
     </row>
-    <row r="33" ht="19" customHeight="1" s="32">
+    <row r="33" ht="18.5" customHeight="1" s="32">
       <c r="B33" s="1" t="n"/>
       <c r="C33" s="67" t="n"/>
       <c r="D33" s="39" t="n"/>
@@ -3870,7 +3878,7 @@
       <c r="K33" s="41" t="n"/>
       <c r="L33" s="42" t="n"/>
     </row>
-    <row r="34" ht="19" customHeight="1" s="32">
+    <row r="34" ht="18.5" customHeight="1" s="32">
       <c r="B34" s="1" t="n"/>
       <c r="C34" s="67" t="n"/>
       <c r="D34" s="39" t="n"/>
@@ -3883,7 +3891,7 @@
       <c r="K34" s="41" t="n"/>
       <c r="L34" s="42" t="n"/>
     </row>
-    <row r="35" ht="19" customHeight="1" s="32">
+    <row r="35" ht="18.5" customHeight="1" s="32">
       <c r="B35" s="1" t="n"/>
       <c r="C35" s="38" t="n"/>
       <c r="D35" s="39" t="n"/>
@@ -3896,7 +3904,7 @@
       <c r="K35" s="41" t="n"/>
       <c r="L35" s="42" t="n"/>
     </row>
-    <row r="36" ht="19" customHeight="1" s="32">
+    <row r="36" ht="18.5" customHeight="1" s="32">
       <c r="B36" s="1" t="n"/>
       <c r="C36" s="38" t="n"/>
       <c r="D36" s="39" t="n"/>
@@ -3909,7 +3917,7 @@
       <c r="K36" s="41" t="n"/>
       <c r="L36" s="42" t="n"/>
     </row>
-    <row r="37" ht="19" customHeight="1" s="32">
+    <row r="37" ht="18.5" customHeight="1" s="32">
       <c r="B37" s="1" t="n"/>
       <c r="C37" s="38" t="n"/>
       <c r="D37" s="39" t="n"/>
@@ -3922,7 +3930,7 @@
       <c r="K37" s="41" t="n"/>
       <c r="L37" s="42" t="n"/>
     </row>
-    <row r="38" ht="19" customHeight="1" s="32">
+    <row r="38" ht="18.5" customHeight="1" s="32">
       <c r="B38" s="1" t="n"/>
       <c r="C38" s="38" t="n"/>
       <c r="D38" s="39" t="n"/>
@@ -3935,7 +3943,7 @@
       <c r="K38" s="41" t="n"/>
       <c r="L38" s="42" t="n"/>
     </row>
-    <row r="39" ht="19" customHeight="1" s="32">
+    <row r="39" ht="18.5" customHeight="1" s="32">
       <c r="B39" s="1" t="n"/>
       <c r="C39" s="38" t="n"/>
       <c r="D39" s="39" t="n"/>
@@ -3948,7 +3956,7 @@
       <c r="K39" s="41" t="n"/>
       <c r="L39" s="42" t="n"/>
     </row>
-    <row r="40" ht="19" customHeight="1" s="32">
+    <row r="40" ht="18.5" customHeight="1" s="32">
       <c r="B40" s="1" t="n"/>
       <c r="C40" s="38" t="n"/>
       <c r="D40" s="39" t="n"/>
@@ -3961,7 +3969,7 @@
       <c r="K40" s="41" t="n"/>
       <c r="L40" s="42" t="n"/>
     </row>
-    <row r="41" ht="19" customHeight="1" s="32">
+    <row r="41" ht="18.5" customHeight="1" s="32">
       <c r="B41" s="1" t="n"/>
       <c r="C41" s="38" t="n"/>
       <c r="D41" s="39" t="n"/>
@@ -3974,7 +3982,7 @@
       <c r="K41" s="41" t="n"/>
       <c r="L41" s="42" t="n"/>
     </row>
-    <row r="42" ht="19" customHeight="1" s="32">
+    <row r="42" ht="18.5" customHeight="1" s="32">
       <c r="B42" s="1" t="n"/>
       <c r="C42" s="38" t="n"/>
       <c r="D42" s="39" t="n"/>
@@ -3987,7 +3995,7 @@
       <c r="K42" s="41" t="n"/>
       <c r="L42" s="42" t="n"/>
     </row>
-    <row r="43" ht="19" customHeight="1" s="32">
+    <row r="43" ht="18.5" customHeight="1" s="32">
       <c r="B43" s="1" t="n"/>
       <c r="C43" s="38" t="n"/>
       <c r="D43" s="39" t="n"/>
@@ -4000,7 +4008,7 @@
       <c r="K43" s="41" t="n"/>
       <c r="L43" s="42" t="n"/>
     </row>
-    <row r="44" ht="19" customHeight="1" s="32">
+    <row r="44" ht="18.5" customHeight="1" s="32">
       <c r="B44" s="1" t="n"/>
       <c r="C44" s="38" t="n"/>
       <c r="D44" s="39" t="n"/>
@@ -4013,7 +4021,7 @@
       <c r="K44" s="41" t="n"/>
       <c r="L44" s="42" t="n"/>
     </row>
-    <row r="45" ht="19" customHeight="1" s="32">
+    <row r="45" ht="18.5" customHeight="1" s="32">
       <c r="B45" s="1" t="n"/>
       <c r="C45" s="38" t="n"/>
       <c r="D45" s="39" t="n"/>
@@ -4240,7 +4248,7 @@
       </c>
       <c r="L4" s="30" t="n"/>
     </row>
-    <row r="5" ht="19" customHeight="1" s="32">
+    <row r="5" ht="18.5" customHeight="1" s="32">
       <c r="B5" s="1" t="n"/>
       <c r="C5" s="38" t="n"/>
       <c r="D5" s="39" t="n"/>
@@ -4253,7 +4261,7 @@
       <c r="K5" s="41" t="n"/>
       <c r="L5" s="42" t="n"/>
     </row>
-    <row r="6" ht="19" customHeight="1" s="32">
+    <row r="6" ht="18.5" customHeight="1" s="32">
       <c r="B6" s="1" t="n"/>
       <c r="C6" s="38" t="n"/>
       <c r="D6" s="39" t="n"/>
@@ -4266,7 +4274,7 @@
       <c r="K6" s="41" t="n"/>
       <c r="L6" s="42" t="n"/>
     </row>
-    <row r="7" ht="19" customHeight="1" s="32">
+    <row r="7" ht="18.5" customHeight="1" s="32">
       <c r="B7" s="1" t="n"/>
       <c r="C7" s="38" t="n"/>
       <c r="D7" s="39" t="n"/>
@@ -4279,7 +4287,7 @@
       <c r="K7" s="41" t="n"/>
       <c r="L7" s="42" t="n"/>
     </row>
-    <row r="8" ht="19" customHeight="1" s="32">
+    <row r="8" ht="18.5" customHeight="1" s="32">
       <c r="B8" s="1" t="n"/>
       <c r="C8" s="38" t="n"/>
       <c r="D8" s="39" t="n"/>
@@ -4292,7 +4300,7 @@
       <c r="K8" s="41" t="n"/>
       <c r="L8" s="42" t="n"/>
     </row>
-    <row r="9" ht="19" customHeight="1" s="32">
+    <row r="9" ht="18.5" customHeight="1" s="32">
       <c r="B9" s="1" t="n"/>
       <c r="C9" s="38" t="n"/>
       <c r="D9" s="39" t="n"/>
@@ -4305,7 +4313,7 @@
       <c r="K9" s="41" t="n"/>
       <c r="L9" s="42" t="n"/>
     </row>
-    <row r="10" ht="19" customHeight="1" s="32">
+    <row r="10" ht="18.5" customHeight="1" s="32">
       <c r="B10" s="1" t="n"/>
       <c r="C10" s="38" t="n"/>
       <c r="D10" s="39" t="n"/>
@@ -4318,7 +4326,7 @@
       <c r="K10" s="41" t="n"/>
       <c r="L10" s="42" t="n"/>
     </row>
-    <row r="11" ht="19" customHeight="1" s="32">
+    <row r="11" ht="18.5" customHeight="1" s="32">
       <c r="B11" s="1" t="n"/>
       <c r="C11" s="38" t="n"/>
       <c r="D11" s="39" t="n"/>
@@ -4331,7 +4339,7 @@
       <c r="K11" s="41" t="n"/>
       <c r="L11" s="42" t="n"/>
     </row>
-    <row r="12" ht="19" customHeight="1" s="32">
+    <row r="12" ht="18.5" customHeight="1" s="32">
       <c r="B12" s="1" t="n"/>
       <c r="C12" s="38" t="n"/>
       <c r="D12" s="39" t="n"/>
@@ -4344,7 +4352,7 @@
       <c r="K12" s="41" t="n"/>
       <c r="L12" s="42" t="n"/>
     </row>
-    <row r="13" ht="19" customHeight="1" s="32">
+    <row r="13" ht="18.5" customHeight="1" s="32">
       <c r="B13" s="1" t="n"/>
       <c r="C13" s="38" t="n"/>
       <c r="D13" s="39" t="n"/>
@@ -4357,7 +4365,7 @@
       <c r="K13" s="41" t="n"/>
       <c r="L13" s="42" t="n"/>
     </row>
-    <row r="14" ht="19" customHeight="1" s="32">
+    <row r="14" ht="18.5" customHeight="1" s="32">
       <c r="B14" s="1" t="n"/>
       <c r="C14" s="38" t="n"/>
       <c r="D14" s="39" t="n"/>
@@ -4370,7 +4378,7 @@
       <c r="K14" s="41" t="n"/>
       <c r="L14" s="42" t="n"/>
     </row>
-    <row r="15" ht="19" customHeight="1" s="32">
+    <row r="15" ht="18.5" customHeight="1" s="32">
       <c r="B15" s="1" t="n"/>
       <c r="C15" s="38" t="n"/>
       <c r="D15" s="39" t="n"/>
@@ -4383,7 +4391,7 @@
       <c r="K15" s="41" t="n"/>
       <c r="L15" s="42" t="n"/>
     </row>
-    <row r="16" ht="19" customHeight="1" s="32">
+    <row r="16" ht="18.5" customHeight="1" s="32">
       <c r="B16" s="1" t="n"/>
       <c r="C16" s="38" t="n"/>
       <c r="D16" s="39" t="n"/>
@@ -4396,7 +4404,7 @@
       <c r="K16" s="41" t="n"/>
       <c r="L16" s="42" t="n"/>
     </row>
-    <row r="17" ht="19" customHeight="1" s="32">
+    <row r="17" ht="18.5" customHeight="1" s="32">
       <c r="B17" s="1" t="n"/>
       <c r="C17" s="38" t="n"/>
       <c r="D17" s="39" t="n"/>
@@ -4409,7 +4417,7 @@
       <c r="K17" s="41" t="n"/>
       <c r="L17" s="42" t="n"/>
     </row>
-    <row r="18" ht="19" customHeight="1" s="32">
+    <row r="18" ht="18.5" customHeight="1" s="32">
       <c r="B18" s="1" t="n"/>
       <c r="C18" s="38" t="n"/>
       <c r="D18" s="39" t="n"/>
@@ -4422,7 +4430,7 @@
       <c r="K18" s="41" t="n"/>
       <c r="L18" s="42" t="n"/>
     </row>
-    <row r="19" ht="19" customHeight="1" s="32">
+    <row r="19" ht="18.5" customHeight="1" s="32">
       <c r="B19" s="1" t="n"/>
       <c r="C19" s="38" t="n"/>
       <c r="D19" s="39" t="n"/>
@@ -4435,7 +4443,7 @@
       <c r="K19" s="41" t="n"/>
       <c r="L19" s="42" t="n"/>
     </row>
-    <row r="20" ht="19" customHeight="1" s="32">
+    <row r="20" ht="18.5" customHeight="1" s="32">
       <c r="B20" s="1" t="n"/>
       <c r="C20" s="38" t="n"/>
       <c r="D20" s="39" t="n"/>
@@ -4448,7 +4456,7 @@
       <c r="K20" s="41" t="n"/>
       <c r="L20" s="42" t="n"/>
     </row>
-    <row r="21" ht="19" customHeight="1" s="32">
+    <row r="21" ht="18.5" customHeight="1" s="32">
       <c r="B21" s="1" t="n"/>
       <c r="C21" s="38" t="n"/>
       <c r="D21" s="39" t="n"/>
@@ -4461,7 +4469,7 @@
       <c r="K21" s="41" t="n"/>
       <c r="L21" s="42" t="n"/>
     </row>
-    <row r="22" ht="19" customHeight="1" s="32">
+    <row r="22" ht="18.5" customHeight="1" s="32">
       <c r="B22" s="1" t="n"/>
       <c r="C22" s="38" t="n"/>
       <c r="D22" s="39" t="n"/>
@@ -4474,7 +4482,7 @@
       <c r="K22" s="41" t="n"/>
       <c r="L22" s="42" t="n"/>
     </row>
-    <row r="23" ht="19" customHeight="1" s="32">
+    <row r="23" ht="18.5" customHeight="1" s="32">
       <c r="B23" s="1" t="n"/>
       <c r="C23" s="38" t="n"/>
       <c r="D23" s="39" t="n"/>
@@ -4487,7 +4495,7 @@
       <c r="K23" s="41" t="n"/>
       <c r="L23" s="42" t="n"/>
     </row>
-    <row r="24" ht="19" customHeight="1" s="32">
+    <row r="24" ht="18.5" customHeight="1" s="32">
       <c r="B24" s="1" t="n"/>
       <c r="C24" s="38" t="n"/>
       <c r="D24" s="39" t="n"/>
@@ -4500,7 +4508,7 @@
       <c r="K24" s="41" t="n"/>
       <c r="L24" s="42" t="n"/>
     </row>
-    <row r="25" ht="19" customHeight="1" s="32">
+    <row r="25" ht="18.5" customHeight="1" s="32">
       <c r="B25" s="1" t="n"/>
       <c r="C25" s="38" t="n"/>
       <c r="D25" s="39" t="n"/>
@@ -4513,7 +4521,7 @@
       <c r="K25" s="41" t="n"/>
       <c r="L25" s="42" t="n"/>
     </row>
-    <row r="26" ht="19" customHeight="1" s="32">
+    <row r="26" ht="18.5" customHeight="1" s="32">
       <c r="B26" s="1" t="n"/>
       <c r="C26" s="38" t="n"/>
       <c r="D26" s="39" t="n"/>
@@ -4526,7 +4534,7 @@
       <c r="K26" s="41" t="n"/>
       <c r="L26" s="42" t="n"/>
     </row>
-    <row r="27" ht="19" customHeight="1" s="32">
+    <row r="27" ht="18.5" customHeight="1" s="32">
       <c r="B27" s="1" t="n"/>
       <c r="C27" s="38" t="n"/>
       <c r="D27" s="39" t="n"/>
@@ -4539,7 +4547,7 @@
       <c r="K27" s="41" t="n"/>
       <c r="L27" s="42" t="n"/>
     </row>
-    <row r="28" ht="19" customHeight="1" s="32">
+    <row r="28" ht="18.5" customHeight="1" s="32">
       <c r="B28" s="1" t="n"/>
       <c r="C28" s="38" t="n"/>
       <c r="D28" s="39" t="n"/>
@@ -4552,7 +4560,7 @@
       <c r="K28" s="41" t="n"/>
       <c r="L28" s="42" t="n"/>
     </row>
-    <row r="29" ht="19" customHeight="1" s="32">
+    <row r="29" ht="18.5" customHeight="1" s="32">
       <c r="B29" s="1" t="n"/>
       <c r="C29" s="67" t="n"/>
       <c r="D29" s="39" t="n"/>
@@ -4565,7 +4573,7 @@
       <c r="K29" s="41" t="n"/>
       <c r="L29" s="42" t="n"/>
     </row>
-    <row r="30" ht="19" customHeight="1" s="32">
+    <row r="30" ht="18.5" customHeight="1" s="32">
       <c r="B30" s="1" t="n"/>
       <c r="C30" s="67" t="n"/>
       <c r="D30" s="39" t="n"/>
@@ -4578,7 +4586,7 @@
       <c r="K30" s="41" t="n"/>
       <c r="L30" s="42" t="n"/>
     </row>
-    <row r="31" ht="19" customHeight="1" s="32">
+    <row r="31" ht="18.5" customHeight="1" s="32">
       <c r="B31" s="1" t="n"/>
       <c r="C31" s="67" t="n"/>
       <c r="D31" s="39" t="n"/>
@@ -4591,7 +4599,7 @@
       <c r="K31" s="41" t="n"/>
       <c r="L31" s="42" t="n"/>
     </row>
-    <row r="32" ht="19" customHeight="1" s="32">
+    <row r="32" ht="18.5" customHeight="1" s="32">
       <c r="B32" s="1" t="n"/>
       <c r="C32" s="67" t="n"/>
       <c r="D32" s="39" t="n"/>
@@ -4604,7 +4612,7 @@
       <c r="K32" s="41" t="n"/>
       <c r="L32" s="42" t="n"/>
     </row>
-    <row r="33" ht="19" customHeight="1" s="32">
+    <row r="33" ht="18.5" customHeight="1" s="32">
       <c r="B33" s="1" t="n"/>
       <c r="C33" s="67" t="n"/>
       <c r="D33" s="39" t="n"/>
@@ -4617,7 +4625,7 @@
       <c r="K33" s="41" t="n"/>
       <c r="L33" s="42" t="n"/>
     </row>
-    <row r="34" ht="19" customHeight="1" s="32">
+    <row r="34" ht="18.5" customHeight="1" s="32">
       <c r="B34" s="1" t="n"/>
       <c r="C34" s="67" t="n"/>
       <c r="D34" s="39" t="n"/>
@@ -4630,7 +4638,7 @@
       <c r="K34" s="41" t="n"/>
       <c r="L34" s="42" t="n"/>
     </row>
-    <row r="35" ht="19" customHeight="1" s="32">
+    <row r="35" ht="18.5" customHeight="1" s="32">
       <c r="B35" s="1" t="n"/>
       <c r="C35" s="38" t="n"/>
       <c r="D35" s="39" t="n"/>
@@ -4643,7 +4651,7 @@
       <c r="K35" s="41" t="n"/>
       <c r="L35" s="42" t="n"/>
     </row>
-    <row r="36" ht="19" customHeight="1" s="32">
+    <row r="36" ht="18.5" customHeight="1" s="32">
       <c r="B36" s="1" t="n"/>
       <c r="C36" s="38" t="n"/>
       <c r="D36" s="39" t="n"/>
@@ -4656,7 +4664,7 @@
       <c r="K36" s="41" t="n"/>
       <c r="L36" s="42" t="n"/>
     </row>
-    <row r="37" ht="19" customHeight="1" s="32">
+    <row r="37" ht="18.5" customHeight="1" s="32">
       <c r="B37" s="1" t="n"/>
       <c r="C37" s="38" t="n"/>
       <c r="D37" s="39" t="n"/>
@@ -4669,7 +4677,7 @@
       <c r="K37" s="41" t="n"/>
       <c r="L37" s="42" t="n"/>
     </row>
-    <row r="38" ht="19" customHeight="1" s="32">
+    <row r="38" ht="18.5" customHeight="1" s="32">
       <c r="B38" s="1" t="n"/>
       <c r="C38" s="38" t="n"/>
       <c r="D38" s="39" t="n"/>
@@ -4682,7 +4690,7 @@
       <c r="K38" s="41" t="n"/>
       <c r="L38" s="42" t="n"/>
     </row>
-    <row r="39" ht="19" customHeight="1" s="32">
+    <row r="39" ht="18.5" customHeight="1" s="32">
       <c r="B39" s="1" t="n"/>
       <c r="C39" s="38" t="n"/>
       <c r="D39" s="39" t="n"/>
@@ -4695,7 +4703,7 @@
       <c r="K39" s="41" t="n"/>
       <c r="L39" s="42" t="n"/>
     </row>
-    <row r="40" ht="19" customHeight="1" s="32">
+    <row r="40" ht="18.5" customHeight="1" s="32">
       <c r="B40" s="1" t="n"/>
       <c r="C40" s="38" t="n"/>
       <c r="D40" s="39" t="n"/>
@@ -4708,7 +4716,7 @@
       <c r="K40" s="41" t="n"/>
       <c r="L40" s="42" t="n"/>
     </row>
-    <row r="41" ht="19" customHeight="1" s="32">
+    <row r="41" ht="18.5" customHeight="1" s="32">
       <c r="B41" s="1" t="n"/>
       <c r="C41" s="38" t="n"/>
       <c r="D41" s="39" t="n"/>
@@ -4721,7 +4729,7 @@
       <c r="K41" s="41" t="n"/>
       <c r="L41" s="42" t="n"/>
     </row>
-    <row r="42" ht="19" customHeight="1" s="32">
+    <row r="42" ht="18.5" customHeight="1" s="32">
       <c r="B42" s="1" t="n"/>
       <c r="C42" s="38" t="n"/>
       <c r="D42" s="39" t="n"/>
@@ -4734,7 +4742,7 @@
       <c r="K42" s="41" t="n"/>
       <c r="L42" s="42" t="n"/>
     </row>
-    <row r="43" ht="19" customHeight="1" s="32">
+    <row r="43" ht="18.5" customHeight="1" s="32">
       <c r="B43" s="1" t="n"/>
       <c r="C43" s="38" t="n"/>
       <c r="D43" s="39" t="n"/>
@@ -4747,7 +4755,7 @@
       <c r="K43" s="41" t="n"/>
       <c r="L43" s="42" t="n"/>
     </row>
-    <row r="44" ht="19" customHeight="1" s="32">
+    <row r="44" ht="18.5" customHeight="1" s="32">
       <c r="B44" s="1" t="n"/>
       <c r="C44" s="38" t="n"/>
       <c r="D44" s="39" t="n"/>
@@ -4760,7 +4768,7 @@
       <c r="K44" s="41" t="n"/>
       <c r="L44" s="42" t="n"/>
     </row>
-    <row r="45" ht="19" customHeight="1" s="32">
+    <row r="45" ht="18.5" customHeight="1" s="32">
       <c r="B45" s="1" t="n"/>
       <c r="C45" s="38" t="n"/>
       <c r="D45" s="39" t="n"/>
@@ -4987,7 +4995,7 @@
       </c>
       <c r="L4" s="30" t="n"/>
     </row>
-    <row r="5" ht="19" customHeight="1" s="32">
+    <row r="5" ht="18.5" customHeight="1" s="32">
       <c r="B5" s="1" t="n"/>
       <c r="C5" s="38" t="n"/>
       <c r="D5" s="39" t="n"/>
@@ -5000,7 +5008,7 @@
       <c r="K5" s="41" t="n"/>
       <c r="L5" s="42" t="n"/>
     </row>
-    <row r="6" ht="19" customHeight="1" s="32">
+    <row r="6" ht="18.5" customHeight="1" s="32">
       <c r="B6" s="1" t="n"/>
       <c r="C6" s="38" t="n"/>
       <c r="D6" s="39" t="n"/>
@@ -5013,7 +5021,7 @@
       <c r="K6" s="41" t="n"/>
       <c r="L6" s="42" t="n"/>
     </row>
-    <row r="7" ht="19" customHeight="1" s="32">
+    <row r="7" ht="18.5" customHeight="1" s="32">
       <c r="B7" s="1" t="n"/>
       <c r="C7" s="38" t="n"/>
       <c r="D7" s="39" t="n"/>
@@ -5026,7 +5034,7 @@
       <c r="K7" s="41" t="n"/>
       <c r="L7" s="42" t="n"/>
     </row>
-    <row r="8" ht="19" customHeight="1" s="32">
+    <row r="8" ht="18.5" customHeight="1" s="32">
       <c r="B8" s="1" t="n"/>
       <c r="C8" s="38" t="n"/>
       <c r="D8" s="39" t="n"/>
@@ -5039,7 +5047,7 @@
       <c r="K8" s="41" t="n"/>
       <c r="L8" s="42" t="n"/>
     </row>
-    <row r="9" ht="19" customHeight="1" s="32">
+    <row r="9" ht="18.5" customHeight="1" s="32">
       <c r="B9" s="1" t="n"/>
       <c r="C9" s="38" t="n"/>
       <c r="D9" s="39" t="n"/>
@@ -5052,7 +5060,7 @@
       <c r="K9" s="41" t="n"/>
       <c r="L9" s="42" t="n"/>
     </row>
-    <row r="10" ht="19" customHeight="1" s="32">
+    <row r="10" ht="18.5" customHeight="1" s="32">
       <c r="B10" s="1" t="n"/>
       <c r="C10" s="38" t="n"/>
       <c r="D10" s="39" t="n"/>
@@ -5065,7 +5073,7 @@
       <c r="K10" s="41" t="n"/>
       <c r="L10" s="42" t="n"/>
     </row>
-    <row r="11" ht="19" customHeight="1" s="32">
+    <row r="11" ht="18.5" customHeight="1" s="32">
       <c r="B11" s="1" t="n"/>
       <c r="C11" s="38" t="n"/>
       <c r="D11" s="39" t="n"/>
@@ -5078,7 +5086,7 @@
       <c r="K11" s="41" t="n"/>
       <c r="L11" s="42" t="n"/>
     </row>
-    <row r="12" ht="19" customHeight="1" s="32">
+    <row r="12" ht="18.5" customHeight="1" s="32">
       <c r="B12" s="1" t="n"/>
       <c r="C12" s="38" t="n"/>
       <c r="D12" s="39" t="n"/>
@@ -5091,7 +5099,7 @@
       <c r="K12" s="41" t="n"/>
       <c r="L12" s="42" t="n"/>
     </row>
-    <row r="13" ht="19" customHeight="1" s="32">
+    <row r="13" ht="18.5" customHeight="1" s="32">
       <c r="B13" s="1" t="n"/>
       <c r="C13" s="38" t="n"/>
       <c r="D13" s="39" t="n"/>
@@ -5104,7 +5112,7 @@
       <c r="K13" s="41" t="n"/>
       <c r="L13" s="42" t="n"/>
     </row>
-    <row r="14" ht="19" customHeight="1" s="32">
+    <row r="14" ht="18.5" customHeight="1" s="32">
       <c r="B14" s="1" t="n"/>
       <c r="C14" s="38" t="n"/>
       <c r="D14" s="39" t="n"/>
@@ -5117,7 +5125,7 @@
       <c r="K14" s="41" t="n"/>
       <c r="L14" s="42" t="n"/>
     </row>
-    <row r="15" ht="19" customHeight="1" s="32">
+    <row r="15" ht="18.5" customHeight="1" s="32">
       <c r="B15" s="1" t="n"/>
       <c r="C15" s="38" t="n"/>
       <c r="D15" s="39" t="n"/>
@@ -5130,7 +5138,7 @@
       <c r="K15" s="41" t="n"/>
       <c r="L15" s="42" t="n"/>
     </row>
-    <row r="16" ht="19" customHeight="1" s="32">
+    <row r="16" ht="18.5" customHeight="1" s="32">
       <c r="B16" s="1" t="n"/>
       <c r="C16" s="38" t="n"/>
       <c r="D16" s="39" t="n"/>
@@ -5143,7 +5151,7 @@
       <c r="K16" s="41" t="n"/>
       <c r="L16" s="42" t="n"/>
     </row>
-    <row r="17" ht="19" customHeight="1" s="32">
+    <row r="17" ht="18.5" customHeight="1" s="32">
       <c r="B17" s="1" t="n"/>
       <c r="C17" s="38" t="n"/>
       <c r="D17" s="39" t="n"/>
@@ -5156,7 +5164,7 @@
       <c r="K17" s="41" t="n"/>
       <c r="L17" s="42" t="n"/>
     </row>
-    <row r="18" ht="19" customHeight="1" s="32">
+    <row r="18" ht="18.5" customHeight="1" s="32">
       <c r="B18" s="1" t="n"/>
       <c r="C18" s="38" t="n"/>
       <c r="D18" s="39" t="n"/>
@@ -5169,7 +5177,7 @@
       <c r="K18" s="41" t="n"/>
       <c r="L18" s="42" t="n"/>
     </row>
-    <row r="19" ht="19" customHeight="1" s="32">
+    <row r="19" ht="18.5" customHeight="1" s="32">
       <c r="B19" s="1" t="n"/>
       <c r="C19" s="38" t="n"/>
       <c r="D19" s="39" t="n"/>
@@ -5182,7 +5190,7 @@
       <c r="K19" s="41" t="n"/>
       <c r="L19" s="42" t="n"/>
     </row>
-    <row r="20" ht="19" customHeight="1" s="32">
+    <row r="20" ht="18.5" customHeight="1" s="32">
       <c r="B20" s="1" t="n"/>
       <c r="C20" s="38" t="n"/>
       <c r="D20" s="39" t="n"/>
@@ -5195,7 +5203,7 @@
       <c r="K20" s="41" t="n"/>
       <c r="L20" s="42" t="n"/>
     </row>
-    <row r="21" ht="19" customHeight="1" s="32">
+    <row r="21" ht="18.5" customHeight="1" s="32">
       <c r="B21" s="1" t="n"/>
       <c r="C21" s="38" t="n"/>
       <c r="D21" s="39" t="n"/>
@@ -5208,7 +5216,7 @@
       <c r="K21" s="41" t="n"/>
       <c r="L21" s="42" t="n"/>
     </row>
-    <row r="22" ht="19" customHeight="1" s="32">
+    <row r="22" ht="18.5" customHeight="1" s="32">
       <c r="B22" s="1" t="n"/>
       <c r="C22" s="38" t="n"/>
       <c r="D22" s="39" t="n"/>
@@ -5221,7 +5229,7 @@
       <c r="K22" s="41" t="n"/>
       <c r="L22" s="42" t="n"/>
     </row>
-    <row r="23" ht="19" customHeight="1" s="32">
+    <row r="23" ht="18.5" customHeight="1" s="32">
       <c r="B23" s="1" t="n"/>
       <c r="C23" s="38" t="n"/>
       <c r="D23" s="39" t="n"/>
@@ -5234,7 +5242,7 @@
       <c r="K23" s="41" t="n"/>
       <c r="L23" s="42" t="n"/>
     </row>
-    <row r="24" ht="19" customHeight="1" s="32">
+    <row r="24" ht="18.5" customHeight="1" s="32">
       <c r="B24" s="1" t="n"/>
       <c r="C24" s="38" t="n"/>
       <c r="D24" s="39" t="n"/>
@@ -5247,7 +5255,7 @@
       <c r="K24" s="41" t="n"/>
       <c r="L24" s="42" t="n"/>
     </row>
-    <row r="25" ht="19" customHeight="1" s="32">
+    <row r="25" ht="18.5" customHeight="1" s="32">
       <c r="B25" s="1" t="n"/>
       <c r="C25" s="38" t="n"/>
       <c r="D25" s="39" t="n"/>
@@ -5260,7 +5268,7 @@
       <c r="K25" s="41" t="n"/>
       <c r="L25" s="42" t="n"/>
     </row>
-    <row r="26" ht="19" customHeight="1" s="32">
+    <row r="26" ht="18.5" customHeight="1" s="32">
       <c r="B26" s="1" t="n"/>
       <c r="C26" s="38" t="n"/>
       <c r="D26" s="39" t="n"/>
@@ -5273,7 +5281,7 @@
       <c r="K26" s="41" t="n"/>
       <c r="L26" s="42" t="n"/>
     </row>
-    <row r="27" ht="19" customHeight="1" s="32">
+    <row r="27" ht="18.5" customHeight="1" s="32">
       <c r="B27" s="1" t="n"/>
       <c r="C27" s="38" t="n"/>
       <c r="D27" s="39" t="n"/>
@@ -5286,7 +5294,7 @@
       <c r="K27" s="41" t="n"/>
       <c r="L27" s="42" t="n"/>
     </row>
-    <row r="28" ht="19" customHeight="1" s="32">
+    <row r="28" ht="18.5" customHeight="1" s="32">
       <c r="B28" s="1" t="n"/>
       <c r="C28" s="38" t="n"/>
       <c r="D28" s="39" t="n"/>
@@ -5299,7 +5307,7 @@
       <c r="K28" s="41" t="n"/>
       <c r="L28" s="42" t="n"/>
     </row>
-    <row r="29" ht="19" customHeight="1" s="32">
+    <row r="29" ht="18.5" customHeight="1" s="32">
       <c r="B29" s="1" t="n"/>
       <c r="C29" s="67" t="n"/>
       <c r="D29" s="39" t="n"/>
@@ -5312,7 +5320,7 @@
       <c r="K29" s="41" t="n"/>
       <c r="L29" s="42" t="n"/>
     </row>
-    <row r="30" ht="19" customHeight="1" s="32">
+    <row r="30" ht="18.5" customHeight="1" s="32">
       <c r="B30" s="1" t="n"/>
       <c r="C30" s="67" t="n"/>
       <c r="D30" s="39" t="n"/>
@@ -5325,7 +5333,7 @@
       <c r="K30" s="41" t="n"/>
       <c r="L30" s="42" t="n"/>
     </row>
-    <row r="31" ht="19" customHeight="1" s="32">
+    <row r="31" ht="18.5" customHeight="1" s="32">
       <c r="B31" s="1" t="n"/>
       <c r="C31" s="67" t="n"/>
       <c r="D31" s="39" t="n"/>
@@ -5338,7 +5346,7 @@
       <c r="K31" s="41" t="n"/>
       <c r="L31" s="42" t="n"/>
     </row>
-    <row r="32" ht="19" customHeight="1" s="32">
+    <row r="32" ht="18.5" customHeight="1" s="32">
       <c r="B32" s="1" t="n"/>
       <c r="C32" s="67" t="n"/>
       <c r="D32" s="39" t="n"/>
@@ -5351,7 +5359,7 @@
       <c r="K32" s="41" t="n"/>
       <c r="L32" s="42" t="n"/>
     </row>
-    <row r="33" ht="19" customHeight="1" s="32">
+    <row r="33" ht="18.5" customHeight="1" s="32">
       <c r="B33" s="1" t="n"/>
       <c r="C33" s="67" t="n"/>
       <c r="D33" s="39" t="n"/>
@@ -5364,7 +5372,7 @@
       <c r="K33" s="41" t="n"/>
       <c r="L33" s="42" t="n"/>
     </row>
-    <row r="34" ht="19" customHeight="1" s="32">
+    <row r="34" ht="18.5" customHeight="1" s="32">
       <c r="B34" s="1" t="n"/>
       <c r="C34" s="67" t="n"/>
       <c r="D34" s="39" t="n"/>
@@ -5377,7 +5385,7 @@
       <c r="K34" s="41" t="n"/>
       <c r="L34" s="42" t="n"/>
     </row>
-    <row r="35" ht="19" customHeight="1" s="32">
+    <row r="35" ht="18.5" customHeight="1" s="32">
       <c r="B35" s="1" t="n"/>
       <c r="C35" s="38" t="n"/>
       <c r="D35" s="39" t="n"/>
@@ -5390,7 +5398,7 @@
       <c r="K35" s="41" t="n"/>
       <c r="L35" s="42" t="n"/>
     </row>
-    <row r="36" ht="19" customHeight="1" s="32">
+    <row r="36" ht="18.5" customHeight="1" s="32">
       <c r="B36" s="1" t="n"/>
       <c r="C36" s="38" t="n"/>
       <c r="D36" s="39" t="n"/>
@@ -5403,7 +5411,7 @@
       <c r="K36" s="41" t="n"/>
       <c r="L36" s="42" t="n"/>
     </row>
-    <row r="37" ht="19" customHeight="1" s="32">
+    <row r="37" ht="18.5" customHeight="1" s="32">
       <c r="B37" s="1" t="n"/>
       <c r="C37" s="38" t="n"/>
       <c r="D37" s="39" t="n"/>
@@ -5416,7 +5424,7 @@
       <c r="K37" s="41" t="n"/>
       <c r="L37" s="42" t="n"/>
     </row>
-    <row r="38" ht="19" customHeight="1" s="32">
+    <row r="38" ht="18.5" customHeight="1" s="32">
       <c r="B38" s="1" t="n"/>
       <c r="C38" s="38" t="n"/>
       <c r="D38" s="39" t="n"/>
@@ -5429,7 +5437,7 @@
       <c r="K38" s="41" t="n"/>
       <c r="L38" s="42" t="n"/>
     </row>
-    <row r="39" ht="19" customHeight="1" s="32">
+    <row r="39" ht="18.5" customHeight="1" s="32">
       <c r="B39" s="1" t="n"/>
       <c r="C39" s="38" t="n"/>
       <c r="D39" s="39" t="n"/>
@@ -5442,7 +5450,7 @@
       <c r="K39" s="41" t="n"/>
       <c r="L39" s="42" t="n"/>
     </row>
-    <row r="40" ht="19" customHeight="1" s="32">
+    <row r="40" ht="18.5" customHeight="1" s="32">
       <c r="B40" s="1" t="n"/>
       <c r="C40" s="38" t="n"/>
       <c r="D40" s="39" t="n"/>
@@ -5455,7 +5463,7 @@
       <c r="K40" s="41" t="n"/>
       <c r="L40" s="42" t="n"/>
     </row>
-    <row r="41" ht="19" customHeight="1" s="32">
+    <row r="41" ht="18.5" customHeight="1" s="32">
       <c r="B41" s="1" t="n"/>
       <c r="C41" s="38" t="n"/>
       <c r="D41" s="39" t="n"/>
@@ -5468,7 +5476,7 @@
       <c r="K41" s="41" t="n"/>
       <c r="L41" s="42" t="n"/>
     </row>
-    <row r="42" ht="19" customHeight="1" s="32">
+    <row r="42" ht="18.5" customHeight="1" s="32">
       <c r="B42" s="1" t="n"/>
       <c r="C42" s="38" t="n"/>
       <c r="D42" s="39" t="n"/>
@@ -5481,7 +5489,7 @@
       <c r="K42" s="41" t="n"/>
       <c r="L42" s="42" t="n"/>
     </row>
-    <row r="43" ht="19" customHeight="1" s="32">
+    <row r="43" ht="18.5" customHeight="1" s="32">
       <c r="B43" s="1" t="n"/>
       <c r="C43" s="38" t="n"/>
       <c r="D43" s="39" t="n"/>
@@ -5494,7 +5502,7 @@
       <c r="K43" s="41" t="n"/>
       <c r="L43" s="42" t="n"/>
     </row>
-    <row r="44" ht="19" customHeight="1" s="32">
+    <row r="44" ht="18.5" customHeight="1" s="32">
       <c r="B44" s="1" t="n"/>
       <c r="C44" s="38" t="n"/>
       <c r="D44" s="39" t="n"/>
@@ -5507,7 +5515,7 @@
       <c r="K44" s="41" t="n"/>
       <c r="L44" s="42" t="n"/>
     </row>
-    <row r="45" ht="19" customHeight="1" s="32">
+    <row r="45" ht="18.5" customHeight="1" s="32">
       <c r="B45" s="1" t="n"/>
       <c r="C45" s="38" t="n"/>
       <c r="D45" s="39" t="n"/>
@@ -5734,7 +5742,7 @@
       </c>
       <c r="L4" s="30" t="n"/>
     </row>
-    <row r="5" ht="19" customHeight="1" s="32">
+    <row r="5" ht="18.5" customHeight="1" s="32">
       <c r="B5" s="1" t="n"/>
       <c r="C5" s="38" t="n"/>
       <c r="D5" s="39" t="n"/>
@@ -5747,7 +5755,7 @@
       <c r="K5" s="41" t="n"/>
       <c r="L5" s="42" t="n"/>
     </row>
-    <row r="6" ht="19" customHeight="1" s="32">
+    <row r="6" ht="18.5" customHeight="1" s="32">
       <c r="B6" s="1" t="n"/>
       <c r="C6" s="38" t="n"/>
       <c r="D6" s="39" t="n"/>
@@ -5760,7 +5768,7 @@
       <c r="K6" s="41" t="n"/>
       <c r="L6" s="42" t="n"/>
     </row>
-    <row r="7" ht="19" customHeight="1" s="32">
+    <row r="7" ht="18.5" customHeight="1" s="32">
       <c r="B7" s="1" t="n"/>
       <c r="C7" s="38" t="n"/>
       <c r="D7" s="39" t="n"/>
@@ -5773,7 +5781,7 @@
       <c r="K7" s="41" t="n"/>
       <c r="L7" s="42" t="n"/>
     </row>
-    <row r="8" ht="19" customHeight="1" s="32">
+    <row r="8" ht="18.5" customHeight="1" s="32">
       <c r="B8" s="1" t="n"/>
       <c r="C8" s="38" t="n"/>
       <c r="D8" s="39" t="n"/>
@@ -5786,7 +5794,7 @@
       <c r="K8" s="41" t="n"/>
       <c r="L8" s="42" t="n"/>
     </row>
-    <row r="9" ht="19" customHeight="1" s="32">
+    <row r="9" ht="18.5" customHeight="1" s="32">
       <c r="B9" s="1" t="n"/>
       <c r="C9" s="38" t="n"/>
       <c r="D9" s="39" t="n"/>
@@ -5799,7 +5807,7 @@
       <c r="K9" s="41" t="n"/>
       <c r="L9" s="42" t="n"/>
     </row>
-    <row r="10" ht="19" customHeight="1" s="32">
+    <row r="10" ht="18.5" customHeight="1" s="32">
       <c r="B10" s="1" t="n"/>
       <c r="C10" s="38" t="n"/>
       <c r="D10" s="39" t="n"/>
@@ -5812,7 +5820,7 @@
       <c r="K10" s="41" t="n"/>
       <c r="L10" s="42" t="n"/>
     </row>
-    <row r="11" ht="19" customHeight="1" s="32">
+    <row r="11" ht="18.5" customHeight="1" s="32">
       <c r="B11" s="1" t="n"/>
       <c r="C11" s="38" t="n"/>
       <c r="D11" s="39" t="n"/>
@@ -5825,7 +5833,7 @@
       <c r="K11" s="41" t="n"/>
       <c r="L11" s="42" t="n"/>
     </row>
-    <row r="12" ht="19" customHeight="1" s="32">
+    <row r="12" ht="18.5" customHeight="1" s="32">
       <c r="B12" s="1" t="n"/>
       <c r="C12" s="38" t="n"/>
       <c r="D12" s="39" t="n"/>
@@ -5838,7 +5846,7 @@
       <c r="K12" s="41" t="n"/>
       <c r="L12" s="42" t="n"/>
     </row>
-    <row r="13" ht="19" customHeight="1" s="32">
+    <row r="13" ht="18.5" customHeight="1" s="32">
       <c r="B13" s="1" t="n"/>
       <c r="C13" s="38" t="n"/>
       <c r="D13" s="39" t="n"/>
@@ -5851,7 +5859,7 @@
       <c r="K13" s="41" t="n"/>
       <c r="L13" s="42" t="n"/>
     </row>
-    <row r="14" ht="19" customHeight="1" s="32">
+    <row r="14" ht="18.5" customHeight="1" s="32">
       <c r="B14" s="1" t="n"/>
       <c r="C14" s="38" t="n"/>
       <c r="D14" s="39" t="n"/>
@@ -5864,7 +5872,7 @@
       <c r="K14" s="41" t="n"/>
       <c r="L14" s="42" t="n"/>
     </row>
-    <row r="15" ht="19" customHeight="1" s="32">
+    <row r="15" ht="18.5" customHeight="1" s="32">
       <c r="B15" s="1" t="n"/>
       <c r="C15" s="38" t="n"/>
       <c r="D15" s="39" t="n"/>
@@ -5877,7 +5885,7 @@
       <c r="K15" s="41" t="n"/>
       <c r="L15" s="42" t="n"/>
     </row>
-    <row r="16" ht="19" customHeight="1" s="32">
+    <row r="16" ht="18.5" customHeight="1" s="32">
       <c r="B16" s="1" t="n"/>
       <c r="C16" s="38" t="n"/>
       <c r="D16" s="39" t="n"/>
@@ -5890,7 +5898,7 @@
       <c r="K16" s="41" t="n"/>
       <c r="L16" s="42" t="n"/>
     </row>
-    <row r="17" ht="19" customHeight="1" s="32">
+    <row r="17" ht="18.5" customHeight="1" s="32">
       <c r="B17" s="1" t="n"/>
       <c r="C17" s="38" t="n"/>
       <c r="D17" s="39" t="n"/>
@@ -5903,7 +5911,7 @@
       <c r="K17" s="41" t="n"/>
       <c r="L17" s="42" t="n"/>
     </row>
-    <row r="18" ht="19" customHeight="1" s="32">
+    <row r="18" ht="18.5" customHeight="1" s="32">
       <c r="B18" s="1" t="n"/>
       <c r="C18" s="38" t="n"/>
       <c r="D18" s="39" t="n"/>
@@ -5916,7 +5924,7 @@
       <c r="K18" s="41" t="n"/>
       <c r="L18" s="42" t="n"/>
     </row>
-    <row r="19" ht="19" customHeight="1" s="32">
+    <row r="19" ht="18.5" customHeight="1" s="32">
       <c r="B19" s="1" t="n"/>
       <c r="C19" s="38" t="n"/>
       <c r="D19" s="39" t="n"/>
@@ -5929,7 +5937,7 @@
       <c r="K19" s="41" t="n"/>
       <c r="L19" s="42" t="n"/>
     </row>
-    <row r="20" ht="19" customHeight="1" s="32">
+    <row r="20" ht="18.5" customHeight="1" s="32">
       <c r="B20" s="1" t="n"/>
       <c r="C20" s="38" t="n"/>
       <c r="D20" s="39" t="n"/>
@@ -5942,7 +5950,7 @@
       <c r="K20" s="41" t="n"/>
       <c r="L20" s="42" t="n"/>
     </row>
-    <row r="21" ht="19" customHeight="1" s="32">
+    <row r="21" ht="18.5" customHeight="1" s="32">
       <c r="B21" s="1" t="n"/>
       <c r="C21" s="38" t="n"/>
       <c r="D21" s="39" t="n"/>
@@ -5955,7 +5963,7 @@
       <c r="K21" s="41" t="n"/>
       <c r="L21" s="42" t="n"/>
     </row>
-    <row r="22" ht="19" customHeight="1" s="32">
+    <row r="22" ht="18.5" customHeight="1" s="32">
       <c r="B22" s="1" t="n"/>
       <c r="C22" s="38" t="n"/>
       <c r="D22" s="39" t="n"/>
@@ -5968,7 +5976,7 @@
       <c r="K22" s="41" t="n"/>
       <c r="L22" s="42" t="n"/>
     </row>
-    <row r="23" ht="19" customHeight="1" s="32">
+    <row r="23" ht="18.5" customHeight="1" s="32">
       <c r="B23" s="1" t="n"/>
       <c r="C23" s="38" t="n"/>
       <c r="D23" s="39" t="n"/>
@@ -5981,7 +5989,7 @@
       <c r="K23" s="41" t="n"/>
       <c r="L23" s="42" t="n"/>
     </row>
-    <row r="24" ht="19" customHeight="1" s="32">
+    <row r="24" ht="18.5" customHeight="1" s="32">
       <c r="B24" s="1" t="n"/>
       <c r="C24" s="38" t="n"/>
       <c r="D24" s="39" t="n"/>
@@ -5994,7 +6002,7 @@
       <c r="K24" s="41" t="n"/>
       <c r="L24" s="42" t="n"/>
     </row>
-    <row r="25" ht="19" customHeight="1" s="32">
+    <row r="25" ht="18.5" customHeight="1" s="32">
       <c r="B25" s="1" t="n"/>
       <c r="C25" s="38" t="n"/>
       <c r="D25" s="39" t="n"/>
@@ -6007,7 +6015,7 @@
       <c r="K25" s="41" t="n"/>
       <c r="L25" s="42" t="n"/>
     </row>
-    <row r="26" ht="19" customHeight="1" s="32">
+    <row r="26" ht="18.5" customHeight="1" s="32">
       <c r="B26" s="1" t="n"/>
       <c r="C26" s="38" t="n"/>
       <c r="D26" s="39" t="n"/>
@@ -6020,7 +6028,7 @@
       <c r="K26" s="41" t="n"/>
       <c r="L26" s="42" t="n"/>
     </row>
-    <row r="27" ht="19" customHeight="1" s="32">
+    <row r="27" ht="18.5" customHeight="1" s="32">
       <c r="B27" s="1" t="n"/>
       <c r="C27" s="38" t="n"/>
       <c r="D27" s="39" t="n"/>
@@ -6033,7 +6041,7 @@
       <c r="K27" s="41" t="n"/>
       <c r="L27" s="42" t="n"/>
     </row>
-    <row r="28" ht="19" customHeight="1" s="32">
+    <row r="28" ht="18.5" customHeight="1" s="32">
       <c r="B28" s="1" t="n"/>
       <c r="C28" s="38" t="n"/>
       <c r="D28" s="39" t="n"/>
@@ -6046,7 +6054,7 @@
       <c r="K28" s="41" t="n"/>
       <c r="L28" s="42" t="n"/>
     </row>
-    <row r="29" ht="19" customHeight="1" s="32">
+    <row r="29" ht="18.5" customHeight="1" s="32">
       <c r="B29" s="1" t="n"/>
       <c r="C29" s="67" t="n"/>
       <c r="D29" s="39" t="n"/>
@@ -6059,7 +6067,7 @@
       <c r="K29" s="41" t="n"/>
       <c r="L29" s="42" t="n"/>
     </row>
-    <row r="30" ht="19" customHeight="1" s="32">
+    <row r="30" ht="18.5" customHeight="1" s="32">
       <c r="B30" s="1" t="n"/>
       <c r="C30" s="67" t="n"/>
       <c r="D30" s="39" t="n"/>
@@ -6072,7 +6080,7 @@
       <c r="K30" s="41" t="n"/>
       <c r="L30" s="42" t="n"/>
     </row>
-    <row r="31" ht="19" customHeight="1" s="32">
+    <row r="31" ht="18.5" customHeight="1" s="32">
       <c r="B31" s="1" t="n"/>
       <c r="C31" s="67" t="n"/>
       <c r="D31" s="39" t="n"/>
@@ -6085,7 +6093,7 @@
       <c r="K31" s="41" t="n"/>
       <c r="L31" s="42" t="n"/>
     </row>
-    <row r="32" ht="19" customHeight="1" s="32">
+    <row r="32" ht="18.5" customHeight="1" s="32">
       <c r="B32" s="1" t="n"/>
       <c r="C32" s="67" t="n"/>
       <c r="D32" s="39" t="n"/>
@@ -6098,7 +6106,7 @@
       <c r="K32" s="41" t="n"/>
       <c r="L32" s="42" t="n"/>
     </row>
-    <row r="33" ht="19" customHeight="1" s="32">
+    <row r="33" ht="18.5" customHeight="1" s="32">
       <c r="B33" s="1" t="n"/>
       <c r="C33" s="67" t="n"/>
       <c r="D33" s="39" t="n"/>
@@ -6111,7 +6119,7 @@
       <c r="K33" s="41" t="n"/>
       <c r="L33" s="42" t="n"/>
     </row>
-    <row r="34" ht="19" customHeight="1" s="32">
+    <row r="34" ht="18.5" customHeight="1" s="32">
       <c r="B34" s="1" t="n"/>
       <c r="C34" s="67" t="n"/>
       <c r="D34" s="39" t="n"/>
@@ -6124,7 +6132,7 @@
       <c r="K34" s="41" t="n"/>
       <c r="L34" s="42" t="n"/>
     </row>
-    <row r="35" ht="19" customHeight="1" s="32">
+    <row r="35" ht="18.5" customHeight="1" s="32">
       <c r="B35" s="1" t="n"/>
       <c r="C35" s="38" t="n"/>
       <c r="D35" s="39" t="n"/>
@@ -6137,7 +6145,7 @@
       <c r="K35" s="41" t="n"/>
       <c r="L35" s="42" t="n"/>
     </row>
-    <row r="36" ht="19" customHeight="1" s="32">
+    <row r="36" ht="18.5" customHeight="1" s="32">
       <c r="B36" s="1" t="n"/>
       <c r="C36" s="38" t="n"/>
       <c r="D36" s="39" t="n"/>
@@ -6150,7 +6158,7 @@
       <c r="K36" s="41" t="n"/>
       <c r="L36" s="42" t="n"/>
     </row>
-    <row r="37" ht="19" customHeight="1" s="32">
+    <row r="37" ht="18.5" customHeight="1" s="32">
       <c r="B37" s="1" t="n"/>
       <c r="C37" s="38" t="n"/>
       <c r="D37" s="39" t="n"/>
@@ -6163,7 +6171,7 @@
       <c r="K37" s="41" t="n"/>
       <c r="L37" s="42" t="n"/>
     </row>
-    <row r="38" ht="19" customHeight="1" s="32">
+    <row r="38" ht="18.5" customHeight="1" s="32">
       <c r="B38" s="1" t="n"/>
       <c r="C38" s="38" t="n"/>
       <c r="D38" s="39" t="n"/>
@@ -6176,7 +6184,7 @@
       <c r="K38" s="41" t="n"/>
       <c r="L38" s="42" t="n"/>
     </row>
-    <row r="39" ht="19" customHeight="1" s="32">
+    <row r="39" ht="18.5" customHeight="1" s="32">
       <c r="B39" s="1" t="n"/>
       <c r="C39" s="38" t="n"/>
       <c r="D39" s="39" t="n"/>
@@ -6189,7 +6197,7 @@
       <c r="K39" s="41" t="n"/>
       <c r="L39" s="42" t="n"/>
     </row>
-    <row r="40" ht="19" customHeight="1" s="32">
+    <row r="40" ht="18.5" customHeight="1" s="32">
       <c r="B40" s="1" t="n"/>
       <c r="C40" s="38" t="n"/>
       <c r="D40" s="39" t="n"/>
@@ -6202,7 +6210,7 @@
       <c r="K40" s="41" t="n"/>
       <c r="L40" s="42" t="n"/>
     </row>
-    <row r="41" ht="19" customHeight="1" s="32">
+    <row r="41" ht="18.5" customHeight="1" s="32">
       <c r="B41" s="1" t="n"/>
       <c r="C41" s="38" t="n"/>
       <c r="D41" s="39" t="n"/>
@@ -6215,7 +6223,7 @@
       <c r="K41" s="41" t="n"/>
       <c r="L41" s="42" t="n"/>
     </row>
-    <row r="42" ht="19" customHeight="1" s="32">
+    <row r="42" ht="18.5" customHeight="1" s="32">
       <c r="B42" s="1" t="n"/>
       <c r="C42" s="38" t="n"/>
       <c r="D42" s="39" t="n"/>
@@ -6228,7 +6236,7 @@
       <c r="K42" s="41" t="n"/>
       <c r="L42" s="42" t="n"/>
     </row>
-    <row r="43" ht="19" customHeight="1" s="32">
+    <row r="43" ht="18.5" customHeight="1" s="32">
       <c r="B43" s="1" t="n"/>
       <c r="C43" s="38" t="n"/>
       <c r="D43" s="39" t="n"/>
@@ -6241,7 +6249,7 @@
       <c r="K43" s="41" t="n"/>
       <c r="L43" s="42" t="n"/>
     </row>
-    <row r="44" ht="19" customHeight="1" s="32">
+    <row r="44" ht="18.5" customHeight="1" s="32">
       <c r="B44" s="1" t="n"/>
       <c r="C44" s="38" t="n"/>
       <c r="D44" s="39" t="n"/>
@@ -6254,7 +6262,7 @@
       <c r="K44" s="41" t="n"/>
       <c r="L44" s="42" t="n"/>
     </row>
-    <row r="45" ht="19" customHeight="1" s="32">
+    <row r="45" ht="18.5" customHeight="1" s="32">
       <c r="B45" s="1" t="n"/>
       <c r="C45" s="38" t="n"/>
       <c r="D45" s="39" t="n"/>

--- a/template_estimate.xlsx
+++ b/template_estimate.xlsx
@@ -149,7 +149,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="38">
+  <borders count="39">
     <border>
       <left/>
       <right/>
@@ -542,6 +542,10 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <right style="hair"/>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
@@ -554,7 +558,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -753,6 +757,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1283,7 +1288,7 @@
       <c r="G12" s="1" t="n"/>
       <c r="H12" s="3" t="n"/>
       <c r="I12" s="1" t="n"/>
-      <c r="J12" s="77" t="n"/>
+      <c r="J12" s="79" t="n"/>
       <c r="K12" s="75" t="n"/>
       <c r="L12" s="75" t="n"/>
     </row>
@@ -1894,7 +1899,7 @@
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.4724409448818898" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
+  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.4724409448818898" bottom="0.5118110236220472" header="0.1968503937007874" footer="0.1968503937007874"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
@@ -2652,7 +2657,7 @@
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.4724409448818898" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
+  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.4724409448818898" bottom="0.5118110236220472" header="0.1968503937007874" footer="0.1968503937007874"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
@@ -3399,7 +3404,7 @@
     <mergeCell ref="K4:L4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.4724409448818898" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
+  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.4724409448818898" bottom="0.5118110236220472" header="0.1968503937007874" footer="0.1968503937007874"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
@@ -4146,7 +4151,7 @@
     <mergeCell ref="K4:L4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.4724409448818898" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
+  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.4724409448818898" bottom="0.5118110236220472" header="0.1968503937007874" footer="0.1968503937007874"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
@@ -4893,7 +4898,7 @@
     <mergeCell ref="K4:L4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.4724409448818898" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
+  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.4724409448818898" bottom="0.5118110236220472" header="0.1968503937007874" footer="0.1968503937007874"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
@@ -5640,7 +5645,7 @@
     <mergeCell ref="K4:L4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.4724409448818898" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
+  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.4724409448818898" bottom="0.5118110236220472" header="0.1968503937007874" footer="0.1968503937007874"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
@@ -6387,7 +6392,7 @@
     <mergeCell ref="K4:L4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.4724409448818898" bottom="0.3937007874015748" header="0.1968503937007874" footer="0.1968503937007874"/>
+  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.4724409448818898" bottom="0.5118110236220472" header="0.1968503937007874" footer="0.1968503937007874"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/template_estimate.xlsx
+++ b/template_estimate.xlsx
@@ -46,95 +46,95 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="BIZ UDP明朝 Medium"/>
       <charset val="128"/>
       <family val="1"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="BIZ UDP明朝 Medium"/>
       <charset val="128"/>
       <family val="1"/>
       <sz val="11"/>
       <u val="single"/>
     </font>
     <font>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="BIZ UDP明朝 Medium"/>
       <charset val="128"/>
       <family val="1"/>
       <sz val="14"/>
     </font>
     <font>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="BIZ UDP明朝 Medium"/>
       <charset val="128"/>
       <family val="1"/>
       <sz val="8"/>
     </font>
     <font>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="BIZ UDP明朝 Medium"/>
       <charset val="128"/>
       <family val="1"/>
       <b val="1"/>
       <sz val="16"/>
     </font>
     <font>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="BIZ UDP明朝 Medium"/>
       <charset val="128"/>
       <family val="1"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="BIZ UDP明朝 Medium"/>
       <charset val="128"/>
       <family val="1"/>
       <sz val="16"/>
     </font>
     <font>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="BIZ UDP明朝 Medium"/>
       <charset val="128"/>
       <family val="1"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="BIZ UDP明朝 Medium"/>
       <charset val="128"/>
       <family val="1"/>
       <sz val="24"/>
       <u val="single"/>
     </font>
     <font>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="BIZ UDP明朝 Medium"/>
       <charset val="128"/>
       <family val="1"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="BIZ UDP明朝 Medium"/>
       <charset val="128"/>
       <family val="1"/>
       <sz val="17"/>
     </font>
     <font>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="BIZ UDPゴシック"/>
       <charset val="128"/>
       <family val="3"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="ＭＳ Ｐゴシック"/>
+      <name val="BIZ UDPゴシック"/>
       <charset val="128"/>
       <family val="3"/>
       <sz val="6"/>
     </font>
     <font>
-      <name val="ＭＳ 明朝"/>
+      <name val="BIZ UD明朝 Medium"/>
       <charset val="128"/>
       <family val="1"/>
       <b val="1"/>
       <sz val="18"/>
     </font>
     <font>
-      <name val="ＭＳ Ｐ明朝"/>
+      <name val="BIZ UDP明朝 Medium"/>
       <charset val="128"/>
       <family val="1"/>
       <sz val="26"/>
